--- a/artfynd/A 64499-2023 artfynd.xlsx
+++ b/artfynd/A 64499-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64499-2023 artfynd.xlsx
+++ b/artfynd/A 64499-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>126838823</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126836484</v>
+        <v>126839973</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>78770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680665</v>
+        <v>680751</v>
       </c>
       <c r="R4" t="n">
-        <v>7087214</v>
+        <v>7087100</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,12 +990,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1006,32 +1006,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126836552</v>
+        <v>126836506</v>
       </c>
       <c r="B5" t="n">
-        <v>78647</v>
+        <v>92609</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680642</v>
+        <v>680723</v>
       </c>
       <c r="R5" t="n">
-        <v>7087273</v>
+        <v>7087114</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,32 +1107,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126836489</v>
+        <v>126836504</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>92609</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680647</v>
+        <v>680697</v>
       </c>
       <c r="R6" t="n">
-        <v>7087267</v>
+        <v>7087147</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126836523</v>
+        <v>126836552</v>
       </c>
       <c r="B7" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680728</v>
+        <v>680642</v>
       </c>
       <c r="R7" t="n">
-        <v>7087114</v>
+        <v>7087273</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,10 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126825730</v>
+        <v>126836523</v>
       </c>
       <c r="B8" t="n">
-        <v>79598</v>
+        <v>78678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1320,34 +1320,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680666</v>
+        <v>680728</v>
       </c>
       <c r="R8" t="n">
-        <v>7087235</v>
+        <v>7087114</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,22 +1374,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,12 +1394,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1420,10 +1410,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126839973</v>
+        <v>126825730</v>
       </c>
       <c r="B9" t="n">
-        <v>78739</v>
+        <v>79629</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1431,34 +1421,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680751</v>
+        <v>680666</v>
       </c>
       <c r="R9" t="n">
-        <v>7087100</v>
+        <v>7087235</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,12 +1475,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,12 +1505,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1521,32 +1521,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126836506</v>
+        <v>126836489</v>
       </c>
       <c r="B10" t="n">
-        <v>92535</v>
+        <v>79011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680723</v>
+        <v>680647</v>
       </c>
       <c r="R10" t="n">
-        <v>7087114</v>
+        <v>7087267</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,32 +1622,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126836504</v>
+        <v>126836484</v>
       </c>
       <c r="B11" t="n">
-        <v>92535</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680697</v>
+        <v>680665</v>
       </c>
       <c r="R11" t="n">
-        <v>7087147</v>
+        <v>7087214</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,10 +1723,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126837233</v>
+        <v>126837190</v>
       </c>
       <c r="B12" t="n">
-        <v>78647</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1734,34 +1734,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680698</v>
+        <v>680778</v>
       </c>
       <c r="R12" t="n">
-        <v>7087108</v>
+        <v>7087007</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1794,6 +1802,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1824,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126837190</v>
+        <v>126836546</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>78678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1835,42 +1848,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680778</v>
+        <v>680660</v>
       </c>
       <c r="R13" t="n">
-        <v>7087007</v>
+        <v>7087210</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,11 +1910,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1922,12 +1922,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1941,7 +1941,7 @@
         <v>126836520</v>
       </c>
       <c r="B14" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126839974</v>
+        <v>126837233</v>
       </c>
       <c r="B15" t="n">
-        <v>78738</v>
+        <v>78678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2050,21 +2050,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680751</v>
+        <v>680698</v>
       </c>
       <c r="R15" t="n">
-        <v>7087100</v>
+        <v>7087108</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,12 +2124,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2140,10 +2140,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126836546</v>
+        <v>126840004</v>
       </c>
       <c r="B16" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680660</v>
+        <v>680639</v>
       </c>
       <c r="R16" t="n">
-        <v>7087210</v>
+        <v>7087277</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,12 +2225,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2241,10 +2241,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126840004</v>
+        <v>126839974</v>
       </c>
       <c r="B17" t="n">
-        <v>78647</v>
+        <v>78769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,21 +2252,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680639</v>
+        <v>680751</v>
       </c>
       <c r="R17" t="n">
-        <v>7087277</v>
+        <v>7087100</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2345,7 +2345,7 @@
         <v>126837083</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>126836555</v>
       </c>
       <c r="B19" t="n">
-        <v>78386</v>
+        <v>78417</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126837085</v>
+        <v>126836351</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2575,14 +2575,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680698</v>
+        <v>680723</v>
       </c>
       <c r="R20" t="n">
-        <v>7087214</v>
+        <v>7087114</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2629,12 +2629,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2645,10 +2645,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126837227</v>
+        <v>126837085</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2676,14 +2676,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680693</v>
+        <v>680698</v>
       </c>
       <c r="R21" t="n">
-        <v>7087147</v>
+        <v>7087214</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,12 +2730,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2746,10 +2746,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126836351</v>
+        <v>126837227</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>680723</v>
+        <v>680693</v>
       </c>
       <c r="R22" t="n">
-        <v>7087114</v>
+        <v>7087147</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2831,12 +2831,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2850,7 +2850,7 @@
         <v>126836547</v>
       </c>
       <c r="B23" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>126837232</v>
       </c>
       <c r="B24" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3049,10 +3049,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126838825</v>
+        <v>126840003</v>
       </c>
       <c r="B25" t="n">
-        <v>78980</v>
+        <v>78678</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3060,34 +3060,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680759</v>
+        <v>680729</v>
       </c>
       <c r="R25" t="n">
-        <v>7087282</v>
+        <v>7087103</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3134,12 +3134,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3153,7 +3153,7 @@
         <v>126836551</v>
       </c>
       <c r="B26" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3251,10 +3251,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126840003</v>
+        <v>126838825</v>
       </c>
       <c r="B27" t="n">
-        <v>78647</v>
+        <v>79011</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3262,34 +3262,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680729</v>
+        <v>680759</v>
       </c>
       <c r="R27" t="n">
-        <v>7087103</v>
+        <v>7087282</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,12 +3336,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3352,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126839989</v>
+        <v>126838821</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3383,14 +3383,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680774</v>
+        <v>680775</v>
       </c>
       <c r="R28" t="n">
-        <v>7087124</v>
+        <v>7087121</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3437,12 +3437,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3453,10 +3453,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126838821</v>
+        <v>126837228</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3484,14 +3484,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680775</v>
+        <v>680658</v>
       </c>
       <c r="R29" t="n">
-        <v>7087121</v>
+        <v>7087213</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3538,12 +3538,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3554,10 +3554,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126840000</v>
+        <v>126839971</v>
       </c>
       <c r="B30" t="n">
-        <v>78980</v>
+        <v>78769</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3565,21 +3565,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680643</v>
+        <v>680772</v>
       </c>
       <c r="R30" t="n">
-        <v>7087277</v>
+        <v>7087124</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3655,10 +3655,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126837228</v>
+        <v>126840000</v>
       </c>
       <c r="B31" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680658</v>
+        <v>680643</v>
       </c>
       <c r="R31" t="n">
-        <v>7087213</v>
+        <v>7087277</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3740,12 +3740,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3756,10 +3756,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126839971</v>
+        <v>126839989</v>
       </c>
       <c r="B32" t="n">
-        <v>78738</v>
+        <v>79011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3767,21 +3767,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680772</v>
+        <v>680774</v>
       </c>
       <c r="R32" t="n">
         <v>7087124</v>
@@ -3971,10 +3971,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126839997</v>
+        <v>126836543</v>
       </c>
       <c r="B34" t="n">
-        <v>78980</v>
+        <v>78678</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3982,21 +3982,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680676</v>
+        <v>680708</v>
       </c>
       <c r="R34" t="n">
-        <v>7087207</v>
+        <v>7087204</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4056,12 +4056,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4072,45 +4072,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126836463</v>
+        <v>126837192</v>
       </c>
       <c r="B35" t="n">
-        <v>78980</v>
+        <v>56849</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>680773</v>
+        <v>680665</v>
       </c>
       <c r="R35" t="n">
-        <v>7087233</v>
+        <v>7087191</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,6 +4153,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4157,12 +4170,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4173,10 +4186,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126836543</v>
+        <v>126838798</v>
       </c>
       <c r="B36" t="n">
-        <v>78647</v>
+        <v>57817</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4184,34 +4197,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>680708</v>
+        <v>680781</v>
       </c>
       <c r="R36" t="n">
-        <v>7087204</v>
+        <v>7087170</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4258,26 +4271,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126838798</v>
+        <v>126839997</v>
       </c>
       <c r="B37" t="n">
-        <v>57817</v>
+        <v>79011</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4285,34 +4294,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>680781</v>
+        <v>680676</v>
       </c>
       <c r="R37" t="n">
-        <v>7087170</v>
+        <v>7087207</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4359,22 +4368,26 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>126837084</v>
       </c>
       <c r="B38" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4472,10 +4485,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126836477</v>
+        <v>126836460</v>
       </c>
       <c r="B39" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4507,10 +4520,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>680709</v>
+        <v>680779</v>
       </c>
       <c r="R39" t="n">
-        <v>7087204</v>
+        <v>7087200</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4573,10 +4586,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126836460</v>
+        <v>126836463</v>
       </c>
       <c r="B40" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4608,10 +4621,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>680779</v>
+        <v>680773</v>
       </c>
       <c r="R40" t="n">
-        <v>7087200</v>
+        <v>7087233</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4674,53 +4687,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126837192</v>
+        <v>126836477</v>
       </c>
       <c r="B41" t="n">
-        <v>56849</v>
+        <v>79011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>680665</v>
+        <v>680709</v>
       </c>
       <c r="R41" t="n">
-        <v>7087191</v>
+        <v>7087204</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4755,11 +4760,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4772,12 +4772,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4788,10 +4788,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126836516</v>
+        <v>126839937</v>
       </c>
       <c r="B42" t="n">
-        <v>78647</v>
+        <v>79629</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4799,21 +4799,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>680654</v>
+        <v>680761</v>
       </c>
       <c r="R42" t="n">
-        <v>7087188</v>
+        <v>7087124</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4873,12 +4873,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4889,10 +4889,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126839937</v>
+        <v>126839994</v>
       </c>
       <c r="B43" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4900,21 +4900,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>680761</v>
+        <v>680650</v>
       </c>
       <c r="R43" t="n">
-        <v>7087124</v>
+        <v>7087238</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4993,7 +4993,7 @@
         <v>126836483</v>
       </c>
       <c r="B44" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5091,10 +5091,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126839994</v>
+        <v>126836516</v>
       </c>
       <c r="B45" t="n">
-        <v>78980</v>
+        <v>78678</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5102,21 +5102,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>680650</v>
+        <v>680654</v>
       </c>
       <c r="R45" t="n">
-        <v>7087238</v>
+        <v>7087188</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5176,12 +5176,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5192,32 +5192,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126839976</v>
+        <v>126836198</v>
       </c>
       <c r="B46" t="n">
-        <v>58027</v>
+        <v>79629</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>680693</v>
+        <v>680721</v>
       </c>
       <c r="R46" t="n">
-        <v>7087162</v>
+        <v>7087133</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5277,12 +5277,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5293,10 +5293,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126837223</v>
+        <v>126838822</v>
       </c>
       <c r="B47" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5324,14 +5324,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>680772</v>
+        <v>680783</v>
       </c>
       <c r="R47" t="n">
-        <v>7087024</v>
+        <v>7087170</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5378,12 +5378,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5394,10 +5394,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126836517</v>
+        <v>126836338</v>
       </c>
       <c r="B48" t="n">
-        <v>78647</v>
+        <v>79011</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5405,21 +5405,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>680662</v>
+        <v>680648</v>
       </c>
       <c r="R48" t="n">
-        <v>7087179</v>
+        <v>7087260</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5495,10 +5495,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126836198</v>
+        <v>126839998</v>
       </c>
       <c r="B49" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5506,21 +5506,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>680721</v>
+        <v>680673</v>
       </c>
       <c r="R49" t="n">
-        <v>7087133</v>
+        <v>7087211</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5580,12 +5580,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5596,10 +5596,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126838822</v>
+        <v>126837223</v>
       </c>
       <c r="B50" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5627,14 +5627,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>680783</v>
+        <v>680772</v>
       </c>
       <c r="R50" t="n">
-        <v>7087170</v>
+        <v>7087024</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5681,12 +5681,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5697,10 +5697,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126836548</v>
+        <v>126836517</v>
       </c>
       <c r="B51" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>680662</v>
       </c>
       <c r="R51" t="n">
-        <v>7087231</v>
+        <v>7087179</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5798,10 +5798,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126836338</v>
+        <v>126836548</v>
       </c>
       <c r="B52" t="n">
-        <v>78980</v>
+        <v>78678</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5809,21 +5809,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5833,10 +5833,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>680648</v>
+        <v>680662</v>
       </c>
       <c r="R52" t="n">
-        <v>7087260</v>
+        <v>7087231</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5899,32 +5899,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126839998</v>
+        <v>126839976</v>
       </c>
       <c r="B53" t="n">
-        <v>78980</v>
+        <v>58027</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5934,10 +5934,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>680673</v>
+        <v>680693</v>
       </c>
       <c r="R53" t="n">
-        <v>7087211</v>
+        <v>7087162</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6000,10 +6000,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126836486</v>
+        <v>126836519</v>
       </c>
       <c r="B54" t="n">
-        <v>78980</v>
+        <v>78678</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6011,21 +6011,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6035,10 +6035,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>680663</v>
+        <v>680693</v>
       </c>
       <c r="R54" t="n">
-        <v>7087231</v>
+        <v>7087159</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6101,10 +6101,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126837225</v>
+        <v>126837234</v>
       </c>
       <c r="B55" t="n">
-        <v>78980</v>
+        <v>78678</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6112,21 +6112,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6136,10 +6136,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>680729</v>
+        <v>680694</v>
       </c>
       <c r="R55" t="n">
-        <v>7087081</v>
+        <v>7087158</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6202,50 +6202,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126839949</v>
+        <v>126836541</v>
       </c>
       <c r="B56" t="n">
-        <v>56849</v>
+        <v>78678</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>680726</v>
+        <v>680708</v>
       </c>
       <c r="R56" t="n">
-        <v>7087219</v>
+        <v>7087251</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6292,12 +6287,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6308,45 +6303,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126836541</v>
+        <v>126839949</v>
       </c>
       <c r="B57" t="n">
-        <v>78647</v>
+        <v>56849</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>680708</v>
+        <v>680726</v>
       </c>
       <c r="R57" t="n">
-        <v>7087251</v>
+        <v>7087219</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6393,12 +6393,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6409,10 +6409,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126837234</v>
+        <v>126840919</v>
       </c>
       <c r="B58" t="n">
-        <v>78647</v>
+        <v>79629</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6420,34 +6420,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>680694</v>
+        <v>680640</v>
       </c>
       <c r="R58" t="n">
-        <v>7087158</v>
+        <v>7087261</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6477,29 +6480,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6510,10 +6524,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126836519</v>
+        <v>126836490</v>
       </c>
       <c r="B59" t="n">
-        <v>78647</v>
+        <v>79011</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6521,21 +6535,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6545,10 +6559,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>680693</v>
+        <v>680645</v>
       </c>
       <c r="R59" t="n">
-        <v>7087159</v>
+        <v>7087280</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6611,10 +6625,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126836490</v>
+        <v>126837225</v>
       </c>
       <c r="B60" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6646,10 +6660,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>680645</v>
+        <v>680729</v>
       </c>
       <c r="R60" t="n">
-        <v>7087280</v>
+        <v>7087081</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6696,12 +6710,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6712,10 +6726,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126839996</v>
+        <v>126836469</v>
       </c>
       <c r="B61" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6747,10 +6761,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>680745</v>
+        <v>680728</v>
       </c>
       <c r="R61" t="n">
-        <v>7087170</v>
+        <v>7087278</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6797,12 +6811,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6813,10 +6827,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126840919</v>
+        <v>126839996</v>
       </c>
       <c r="B62" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6824,37 +6838,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>680640</v>
+        <v>680745</v>
       </c>
       <c r="R62" t="n">
-        <v>7087261</v>
+        <v>7087170</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6884,40 +6895,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>10:17</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>10:17</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6928,10 +6928,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126836469</v>
+        <v>126836486</v>
       </c>
       <c r="B63" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6963,10 +6963,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>680728</v>
+        <v>680663</v>
       </c>
       <c r="R63" t="n">
-        <v>7087278</v>
+        <v>7087231</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7029,10 +7029,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126836302</v>
+        <v>126836542</v>
       </c>
       <c r="B64" t="n">
-        <v>78739</v>
+        <v>78678</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7040,21 +7040,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>680677</v>
+        <v>680710</v>
       </c>
       <c r="R64" t="n">
-        <v>7087201</v>
+        <v>7087232</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7130,45 +7130,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126837038</v>
+        <v>126836515</v>
       </c>
       <c r="B65" t="n">
-        <v>91210</v>
+        <v>78678</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>680783</v>
+        <v>680644</v>
       </c>
       <c r="R65" t="n">
-        <v>7087069</v>
+        <v>7087195</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7215,12 +7215,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7234,7 +7234,7 @@
         <v>126839938</v>
       </c>
       <c r="B66" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7332,10 +7332,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126836515</v>
+        <v>126838804</v>
       </c>
       <c r="B67" t="n">
-        <v>78647</v>
+        <v>78769</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7343,34 +7343,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>680644</v>
+        <v>680765</v>
       </c>
       <c r="R67" t="n">
-        <v>7087195</v>
+        <v>7087124</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7417,12 +7417,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7433,10 +7433,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126838804</v>
+        <v>126836302</v>
       </c>
       <c r="B68" t="n">
-        <v>78738</v>
+        <v>78770</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7444,34 +7444,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>680765</v>
+        <v>680677</v>
       </c>
       <c r="R68" t="n">
-        <v>7087124</v>
+        <v>7087201</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7518,12 +7518,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7534,45 +7534,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126836482</v>
+        <v>126837038</v>
       </c>
       <c r="B69" t="n">
-        <v>78980</v>
+        <v>91284</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>680673</v>
+        <v>680783</v>
       </c>
       <c r="R69" t="n">
-        <v>7087202</v>
+        <v>7087069</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7619,12 +7619,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7638,7 +7638,7 @@
         <v>126836474</v>
       </c>
       <c r="B70" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7736,10 +7736,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126836542</v>
+        <v>126836482</v>
       </c>
       <c r="B71" t="n">
-        <v>78647</v>
+        <v>79011</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7747,21 +7747,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7771,10 +7771,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>680710</v>
+        <v>680673</v>
       </c>
       <c r="R71" t="n">
-        <v>7087232</v>
+        <v>7087202</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7837,10 +7837,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126836336</v>
+        <v>126840002</v>
       </c>
       <c r="B72" t="n">
-        <v>78980</v>
+        <v>78678</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7848,21 +7848,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7872,10 +7872,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>680653</v>
+        <v>680724</v>
       </c>
       <c r="R72" t="n">
-        <v>7087252</v>
+        <v>7087119</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7922,12 +7922,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7938,10 +7938,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126837052</v>
+        <v>126836524</v>
       </c>
       <c r="B73" t="n">
-        <v>57817</v>
+        <v>78678</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7949,34 +7949,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>680740</v>
+        <v>680720</v>
       </c>
       <c r="R73" t="n">
-        <v>7087222</v>
+        <v>7087100</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8023,12 +8023,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8039,10 +8039,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126836475</v>
+        <v>126836544</v>
       </c>
       <c r="B74" t="n">
-        <v>78980</v>
+        <v>78678</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8050,21 +8050,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8074,10 +8074,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>680708</v>
+        <v>680681</v>
       </c>
       <c r="R74" t="n">
-        <v>7087220</v>
+        <v>7087195</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8140,10 +8140,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126837069</v>
+        <v>126836475</v>
       </c>
       <c r="B75" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8151,34 +8151,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>680673</v>
+        <v>680708</v>
       </c>
       <c r="R75" t="n">
-        <v>7087276</v>
+        <v>7087220</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8225,12 +8225,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8241,10 +8241,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126836524</v>
+        <v>126836336</v>
       </c>
       <c r="B76" t="n">
-        <v>78647</v>
+        <v>79011</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8252,21 +8252,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8276,10 +8276,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>680720</v>
+        <v>680653</v>
       </c>
       <c r="R76" t="n">
-        <v>7087100</v>
+        <v>7087252</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8342,10 +8342,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126836473</v>
+        <v>126836464</v>
       </c>
       <c r="B77" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8377,10 +8377,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>680710</v>
+        <v>680772</v>
       </c>
       <c r="R77" t="n">
-        <v>7087232</v>
+        <v>7087252</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8443,10 +8443,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126839999</v>
+        <v>126836473</v>
       </c>
       <c r="B78" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>680651</v>
+        <v>680710</v>
       </c>
       <c r="R78" t="n">
-        <v>7087231</v>
+        <v>7087232</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8528,12 +8528,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8544,10 +8544,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126840002</v>
+        <v>126839999</v>
       </c>
       <c r="B79" t="n">
-        <v>78647</v>
+        <v>79011</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8555,21 +8555,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8579,10 +8579,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>680724</v>
+        <v>680651</v>
       </c>
       <c r="R79" t="n">
-        <v>7087119</v>
+        <v>7087231</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8645,10 +8645,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126836544</v>
+        <v>126837052</v>
       </c>
       <c r="B80" t="n">
-        <v>78647</v>
+        <v>57817</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8656,34 +8656,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>680681</v>
+        <v>680740</v>
       </c>
       <c r="R80" t="n">
-        <v>7087195</v>
+        <v>7087222</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8730,12 +8730,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8746,10 +8746,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126836464</v>
+        <v>126837069</v>
       </c>
       <c r="B81" t="n">
-        <v>78980</v>
+        <v>78770</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8757,34 +8757,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>680772</v>
+        <v>680673</v>
       </c>
       <c r="R81" t="n">
-        <v>7087252</v>
+        <v>7087276</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8831,12 +8831,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8850,7 +8850,7 @@
         <v>126837053</v>
       </c>
       <c r="B82" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8948,10 +8948,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126836468</v>
+        <v>126836472</v>
       </c>
       <c r="B83" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8983,10 +8983,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>680752</v>
+        <v>680714</v>
       </c>
       <c r="R83" t="n">
-        <v>7087262</v>
+        <v>7087268</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9052,7 +9052,7 @@
         <v>126836470</v>
       </c>
       <c r="B84" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9150,10 +9150,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126836472</v>
+        <v>126836468</v>
       </c>
       <c r="B85" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9185,10 +9185,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>680714</v>
+        <v>680752</v>
       </c>
       <c r="R85" t="n">
-        <v>7087268</v>
+        <v>7087262</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9251,32 +9251,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126837231</v>
+        <v>126836503</v>
       </c>
       <c r="B86" t="n">
-        <v>78980</v>
+        <v>92609</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9286,10 +9286,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>680642</v>
+        <v>680682</v>
       </c>
       <c r="R86" t="n">
-        <v>7087222</v>
+        <v>7087164</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9336,12 +9336,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9352,10 +9352,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126840864</v>
+        <v>126836481</v>
       </c>
       <c r="B87" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9363,37 +9363,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>680671</v>
+        <v>680670</v>
       </c>
       <c r="R87" t="n">
-        <v>7087236</v>
+        <v>7087199</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9423,40 +9420,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9467,10 +9453,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126839992</v>
+        <v>126837231</v>
       </c>
       <c r="B88" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9502,10 +9488,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>680767</v>
+        <v>680642</v>
       </c>
       <c r="R88" t="n">
-        <v>7087114</v>
+        <v>7087222</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9552,12 +9538,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9568,10 +9554,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126836481</v>
+        <v>126836480</v>
       </c>
       <c r="B89" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9603,10 +9589,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>680670</v>
+        <v>680660</v>
       </c>
       <c r="R89" t="n">
-        <v>7087199</v>
+        <v>7087210</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9669,10 +9655,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126837082</v>
+        <v>126836357</v>
       </c>
       <c r="B90" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9700,14 +9686,14 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>680771</v>
+        <v>680784</v>
       </c>
       <c r="R90" t="n">
-        <v>7087091</v>
+        <v>7087010</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9754,12 +9740,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9770,10 +9756,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126836199</v>
+        <v>126837082</v>
       </c>
       <c r="B91" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9781,34 +9767,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>680719</v>
+        <v>680771</v>
       </c>
       <c r="R91" t="n">
-        <v>7087133</v>
+        <v>7087091</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9855,12 +9841,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -9871,10 +9857,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126836357</v>
+        <v>126839992</v>
       </c>
       <c r="B92" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9906,10 +9892,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>680784</v>
+        <v>680767</v>
       </c>
       <c r="R92" t="n">
-        <v>7087010</v>
+        <v>7087114</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9956,12 +9942,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -9975,7 +9961,7 @@
         <v>126836309</v>
       </c>
       <c r="B93" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10073,32 +10059,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126836503</v>
+        <v>126836199</v>
       </c>
       <c r="B94" t="n">
-        <v>92535</v>
+        <v>79629</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10108,10 +10094,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>680682</v>
+        <v>680719</v>
       </c>
       <c r="R94" t="n">
-        <v>7087164</v>
+        <v>7087133</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10174,10 +10160,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126836480</v>
+        <v>126840864</v>
       </c>
       <c r="B95" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10185,34 +10171,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>680660</v>
+        <v>680671</v>
       </c>
       <c r="R95" t="n">
-        <v>7087210</v>
+        <v>7087236</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10242,29 +10231,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10278,7 +10278,7 @@
         <v>126836226</v>
       </c>
       <c r="B96" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>126836505</v>
       </c>
       <c r="B97" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10477,10 +10477,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126838824</v>
+        <v>126836471</v>
       </c>
       <c r="B98" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10508,14 +10508,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>680778</v>
+        <v>680715</v>
       </c>
       <c r="R98" t="n">
-        <v>7087226</v>
+        <v>7087274</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10562,12 +10562,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10578,10 +10578,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126826458</v>
+        <v>126838824</v>
       </c>
       <c r="B99" t="n">
-        <v>78738</v>
+        <v>79011</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10589,34 +10589,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>680755</v>
+        <v>680778</v>
       </c>
       <c r="R99" t="n">
-        <v>7087104</v>
+        <v>7087226</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10646,19 +10646,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10673,12 +10663,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10689,10 +10679,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126836471</v>
+        <v>126826458</v>
       </c>
       <c r="B100" t="n">
-        <v>78980</v>
+        <v>78769</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10700,34 +10690,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>680715</v>
+        <v>680755</v>
       </c>
       <c r="R100" t="n">
-        <v>7087274</v>
+        <v>7087104</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10757,9 +10747,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10774,12 +10774,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10790,10 +10790,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126836487</v>
+        <v>126836352</v>
       </c>
       <c r="B101" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10825,10 +10825,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>680663</v>
+        <v>680753</v>
       </c>
       <c r="R101" t="n">
-        <v>7087244</v>
+        <v>7087043</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10891,10 +10891,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126836259</v>
+        <v>126836487</v>
       </c>
       <c r="B102" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10902,39 +10902,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>680665</v>
+        <v>680663</v>
       </c>
       <c r="R102" t="n">
-        <v>7087214</v>
+        <v>7087244</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10967,11 +10962,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11002,10 +10992,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126836242</v>
+        <v>126836522</v>
       </c>
       <c r="B103" t="n">
-        <v>91195</v>
+        <v>78678</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11013,21 +11003,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>112</v>
+        <v>353</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11037,10 +11027,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>680744</v>
+        <v>680726</v>
       </c>
       <c r="R103" t="n">
-        <v>7087264</v>
+        <v>7087132</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11106,7 +11096,7 @@
         <v>126837236</v>
       </c>
       <c r="B104" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11204,10 +11194,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126836522</v>
+        <v>126836242</v>
       </c>
       <c r="B105" t="n">
-        <v>78647</v>
+        <v>91269</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11215,21 +11205,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>353</v>
+        <v>112</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11239,10 +11229,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>680726</v>
+        <v>680744</v>
       </c>
       <c r="R105" t="n">
-        <v>7087132</v>
+        <v>7087264</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11305,10 +11295,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126836352</v>
+        <v>126836259</v>
       </c>
       <c r="B106" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11316,34 +11306,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>680753</v>
+        <v>680665</v>
       </c>
       <c r="R106" t="n">
-        <v>7087043</v>
+        <v>7087214</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11376,6 +11371,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11409,7 +11409,7 @@
         <v>126836458</v>
       </c>
       <c r="B107" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>126836353</v>
       </c>
       <c r="B108" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11608,32 +11608,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126836507</v>
+        <v>126836491</v>
       </c>
       <c r="B109" t="n">
-        <v>92535</v>
+        <v>79011</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11643,10 +11643,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>680724</v>
+        <v>680645</v>
       </c>
       <c r="R109" t="n">
-        <v>7087106</v>
+        <v>7087283</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11712,7 +11712,7 @@
         <v>126836462</v>
       </c>
       <c r="B110" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11810,32 +11810,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126836230</v>
+        <v>126836485</v>
       </c>
       <c r="B111" t="n">
-        <v>57479</v>
+        <v>79011</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11845,10 +11845,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>680774</v>
+        <v>680660</v>
       </c>
       <c r="R111" t="n">
-        <v>7087234</v>
+        <v>7087229</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11911,10 +11911,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126836303</v>
+        <v>126836355</v>
       </c>
       <c r="B112" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11922,21 +11922,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11946,10 +11946,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>680654</v>
+        <v>680779</v>
       </c>
       <c r="R112" t="n">
-        <v>7087239</v>
+        <v>7087023</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12012,45 +12012,50 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126836485</v>
+        <v>126839946</v>
       </c>
       <c r="B113" t="n">
-        <v>78980</v>
+        <v>56849</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>680660</v>
+        <v>680662</v>
       </c>
       <c r="R113" t="n">
-        <v>7087229</v>
+        <v>7087219</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12097,12 +12102,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12113,50 +12118,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126839946</v>
+        <v>126836230</v>
       </c>
       <c r="B114" t="n">
-        <v>56849</v>
+        <v>57479</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100138</v>
+        <v>102976</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>680662</v>
+        <v>680774</v>
       </c>
       <c r="R114" t="n">
-        <v>7087219</v>
+        <v>7087234</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12203,12 +12203,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12219,32 +12219,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126836491</v>
+        <v>126836507</v>
       </c>
       <c r="B115" t="n">
-        <v>78980</v>
+        <v>92609</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12254,10 +12254,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>680645</v>
+        <v>680724</v>
       </c>
       <c r="R115" t="n">
-        <v>7087283</v>
+        <v>7087106</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12320,10 +12320,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126836355</v>
+        <v>126836303</v>
       </c>
       <c r="B116" t="n">
-        <v>78980</v>
+        <v>78770</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12331,21 +12331,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12355,10 +12355,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>680779</v>
+        <v>680654</v>
       </c>
       <c r="R116" t="n">
-        <v>7087023</v>
+        <v>7087239</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12421,10 +12421,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126836356</v>
+        <v>126836461</v>
       </c>
       <c r="B117" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12456,10 +12456,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>680782</v>
+        <v>680774</v>
       </c>
       <c r="R117" t="n">
-        <v>7087012</v>
+        <v>7087204</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12522,10 +12522,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126836461</v>
+        <v>126836476</v>
       </c>
       <c r="B118" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>680774</v>
+        <v>680712</v>
       </c>
       <c r="R118" t="n">
-        <v>7087204</v>
+        <v>7087209</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12623,10 +12623,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126836550</v>
+        <v>126836356</v>
       </c>
       <c r="B119" t="n">
-        <v>78647</v>
+        <v>79011</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12634,21 +12634,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12658,10 +12658,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>680667</v>
+        <v>680782</v>
       </c>
       <c r="R119" t="n">
-        <v>7087238</v>
+        <v>7087012</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12724,10 +12724,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126836476</v>
+        <v>126836550</v>
       </c>
       <c r="B120" t="n">
-        <v>78980</v>
+        <v>78678</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12735,21 +12735,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12759,10 +12759,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>680712</v>
+        <v>680667</v>
       </c>
       <c r="R120" t="n">
-        <v>7087209</v>
+        <v>7087238</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12825,10 +12825,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126836559</v>
+        <v>126825809</v>
       </c>
       <c r="B121" t="n">
-        <v>91652</v>
+        <v>78678</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12836,29 +12836,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6040186</v>
+        <v>353</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>680744</v>
+        <v>680666</v>
       </c>
       <c r="R121" t="n">
-        <v>7087264</v>
+        <v>7087235</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12888,30 +12893,39 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -12922,10 +12936,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126825809</v>
+        <v>126836545</v>
       </c>
       <c r="B122" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12953,14 +12967,14 @@
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>680666</v>
+        <v>680657</v>
       </c>
       <c r="R122" t="n">
-        <v>7087235</v>
+        <v>7087201</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12990,19 +13004,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>10:27</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>10:27</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13017,12 +13021,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -13033,10 +13037,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126836545</v>
+        <v>126839970</v>
       </c>
       <c r="B123" t="n">
-        <v>78647</v>
+        <v>78770</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13044,21 +13048,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13068,10 +13072,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>680657</v>
+        <v>680772</v>
       </c>
       <c r="R123" t="n">
-        <v>7087201</v>
+        <v>7087124</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13118,12 +13122,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -13134,10 +13138,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126836466</v>
+        <v>126836559</v>
       </c>
       <c r="B124" t="n">
-        <v>78980</v>
+        <v>91726</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13145,21 +13149,16 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13169,10 +13168,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>680756</v>
+        <v>680744</v>
       </c>
       <c r="R124" t="n">
-        <v>7087273</v>
+        <v>7087264</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13213,6 +13212,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13235,10 +13235,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126836478</v>
+        <v>126836354</v>
       </c>
       <c r="B125" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13270,10 +13270,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>680711</v>
+        <v>680771</v>
       </c>
       <c r="R125" t="n">
-        <v>7087181</v>
+        <v>7087030</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13336,10 +13336,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126836479</v>
+        <v>126836466</v>
       </c>
       <c r="B126" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13371,10 +13371,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>680684</v>
+        <v>680756</v>
       </c>
       <c r="R126" t="n">
-        <v>7087202</v>
+        <v>7087273</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13437,10 +13437,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126836488</v>
+        <v>126836479</v>
       </c>
       <c r="B127" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13472,10 +13472,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>680655</v>
+        <v>680684</v>
       </c>
       <c r="R127" t="n">
-        <v>7087246</v>
+        <v>7087202</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13538,10 +13538,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126836354</v>
+        <v>126836488</v>
       </c>
       <c r="B128" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13573,10 +13573,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>680771</v>
+        <v>680655</v>
       </c>
       <c r="R128" t="n">
-        <v>7087030</v>
+        <v>7087246</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13639,10 +13639,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126839970</v>
+        <v>126836478</v>
       </c>
       <c r="B129" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13650,21 +13650,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13674,10 +13674,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>680772</v>
+        <v>680711</v>
       </c>
       <c r="R129" t="n">
-        <v>7087124</v>
+        <v>7087181</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13724,12 +13724,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -13740,10 +13740,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126838826</v>
+        <v>126836467</v>
       </c>
       <c r="B130" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13771,14 +13771,14 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>680675</v>
+        <v>680758</v>
       </c>
       <c r="R130" t="n">
-        <v>7087310</v>
+        <v>7087267</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13825,12 +13825,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -13844,7 +13844,7 @@
         <v>126838827</v>
       </c>
       <c r="B131" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13942,10 +13942,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126836467</v>
+        <v>126838826</v>
       </c>
       <c r="B132" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13973,14 +13973,14 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>680758</v>
+        <v>680675</v>
       </c>
       <c r="R132" t="n">
-        <v>7087267</v>
+        <v>7087310</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14027,12 +14027,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">

--- a/artfynd/A 64499-2023 artfynd.xlsx
+++ b/artfynd/A 64499-2023 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126838823</v>
+        <v>126836523</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>78681</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,34 +815,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680767</v>
+        <v>680728</v>
       </c>
       <c r="R3" t="n">
-        <v>7087204</v>
+        <v>7087114</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,12 +889,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126839973</v>
+        <v>126836552</v>
       </c>
       <c r="B4" t="n">
-        <v>78770</v>
+        <v>78681</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680751</v>
+        <v>680642</v>
       </c>
       <c r="R4" t="n">
-        <v>7087100</v>
+        <v>7087273</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,12 +990,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1006,32 +1006,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126836506</v>
+        <v>126839973</v>
       </c>
       <c r="B5" t="n">
-        <v>92609</v>
+        <v>78773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680723</v>
+        <v>680751</v>
       </c>
       <c r="R5" t="n">
-        <v>7087114</v>
+        <v>7087100</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,12 +1091,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126836504</v>
+        <v>126836506</v>
       </c>
       <c r="B6" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680697</v>
+        <v>680723</v>
       </c>
       <c r="R6" t="n">
-        <v>7087147</v>
+        <v>7087114</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,32 +1208,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126836552</v>
+        <v>126836504</v>
       </c>
       <c r="B7" t="n">
-        <v>78678</v>
+        <v>92615</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680642</v>
+        <v>680697</v>
       </c>
       <c r="R7" t="n">
-        <v>7087273</v>
+        <v>7087147</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,10 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126836523</v>
+        <v>126825730</v>
       </c>
       <c r="B8" t="n">
-        <v>78678</v>
+        <v>79632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1320,34 +1320,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680728</v>
+        <v>680666</v>
       </c>
       <c r="R8" t="n">
-        <v>7087114</v>
+        <v>7087235</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,12 +1374,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,12 +1404,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1410,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126825730</v>
+        <v>126836489</v>
       </c>
       <c r="B9" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1421,34 +1431,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680666</v>
+        <v>680647</v>
       </c>
       <c r="R9" t="n">
-        <v>7087235</v>
+        <v>7087267</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,22 +1485,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,12 +1505,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126836489</v>
+        <v>126836484</v>
       </c>
       <c r="B10" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680647</v>
+        <v>680665</v>
       </c>
       <c r="R10" t="n">
-        <v>7087267</v>
+        <v>7087214</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126836484</v>
+        <v>126838823</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,14 +1653,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680665</v>
+        <v>680767</v>
       </c>
       <c r="R11" t="n">
-        <v>7087214</v>
+        <v>7087204</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,12 +1707,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126836546</v>
+        <v>126836520</v>
       </c>
       <c r="B13" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680660</v>
+        <v>680716</v>
       </c>
       <c r="R13" t="n">
-        <v>7087210</v>
+        <v>7087135</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,10 +1938,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126836520</v>
+        <v>126840004</v>
       </c>
       <c r="B14" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680716</v>
+        <v>680639</v>
       </c>
       <c r="R14" t="n">
-        <v>7087135</v>
+        <v>7087277</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2023,12 +2023,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2039,10 +2039,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126837233</v>
+        <v>126836546</v>
       </c>
       <c r="B15" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680698</v>
+        <v>680660</v>
       </c>
       <c r="R15" t="n">
-        <v>7087108</v>
+        <v>7087210</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,12 +2124,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2140,10 +2140,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126840004</v>
+        <v>126837233</v>
       </c>
       <c r="B16" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680639</v>
+        <v>680698</v>
       </c>
       <c r="R16" t="n">
-        <v>7087277</v>
+        <v>7087108</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,12 +2225,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2244,7 +2244,7 @@
         <v>126839974</v>
       </c>
       <c r="B17" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>126837083</v>
       </c>
       <c r="B18" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>126836555</v>
       </c>
       <c r="B19" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126836351</v>
+        <v>126837085</v>
       </c>
       <c r="B20" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2575,14 +2575,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680723</v>
+        <v>680698</v>
       </c>
       <c r="R20" t="n">
-        <v>7087114</v>
+        <v>7087214</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2629,12 +2629,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2645,10 +2645,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126837085</v>
+        <v>126836351</v>
       </c>
       <c r="B21" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2676,14 +2676,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680698</v>
+        <v>680723</v>
       </c>
       <c r="R21" t="n">
-        <v>7087214</v>
+        <v>7087114</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,12 +2730,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2749,7 +2749,7 @@
         <v>126837227</v>
       </c>
       <c r="B22" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>126836547</v>
       </c>
       <c r="B23" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>126837232</v>
       </c>
       <c r="B24" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3049,10 +3049,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126840003</v>
+        <v>126836551</v>
       </c>
       <c r="B25" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680729</v>
+        <v>680654</v>
       </c>
       <c r="R25" t="n">
-        <v>7087103</v>
+        <v>7087239</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3134,12 +3134,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3150,10 +3150,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126836551</v>
+        <v>126840003</v>
       </c>
       <c r="B26" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680654</v>
+        <v>680729</v>
       </c>
       <c r="R26" t="n">
-        <v>7087239</v>
+        <v>7087103</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,12 +3235,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126838825</v>
+        <v>126839989</v>
       </c>
       <c r="B27" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3282,14 +3282,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680759</v>
+        <v>680774</v>
       </c>
       <c r="R27" t="n">
-        <v>7087282</v>
+        <v>7087124</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,12 +3336,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3352,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126838821</v>
+        <v>126838825</v>
       </c>
       <c r="B28" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680775</v>
+        <v>680759</v>
       </c>
       <c r="R28" t="n">
-        <v>7087121</v>
+        <v>7087282</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126837228</v>
+        <v>126838821</v>
       </c>
       <c r="B29" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3484,14 +3484,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680658</v>
+        <v>680775</v>
       </c>
       <c r="R29" t="n">
-        <v>7087213</v>
+        <v>7087121</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3538,12 +3538,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3554,10 +3554,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126839971</v>
+        <v>126837228</v>
       </c>
       <c r="B30" t="n">
-        <v>78769</v>
+        <v>79014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3565,21 +3565,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680772</v>
+        <v>680658</v>
       </c>
       <c r="R30" t="n">
-        <v>7087124</v>
+        <v>7087213</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3639,12 +3639,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3655,10 +3655,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126840000</v>
+        <v>126839971</v>
       </c>
       <c r="B31" t="n">
-        <v>79011</v>
+        <v>78772</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3666,21 +3666,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680643</v>
+        <v>680772</v>
       </c>
       <c r="R31" t="n">
-        <v>7087277</v>
+        <v>7087124</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3756,10 +3756,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126839989</v>
+        <v>126840000</v>
       </c>
       <c r="B32" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680774</v>
+        <v>680643</v>
       </c>
       <c r="R32" t="n">
-        <v>7087124</v>
+        <v>7087277</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3974,7 +3974,7 @@
         <v>126836543</v>
       </c>
       <c r="B34" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4072,53 +4072,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126837192</v>
+        <v>126839997</v>
       </c>
       <c r="B35" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>680665</v>
+        <v>680676</v>
       </c>
       <c r="R35" t="n">
-        <v>7087191</v>
+        <v>7087207</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4153,11 +4145,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4170,12 +4157,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4186,10 +4173,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126838798</v>
+        <v>126837084</v>
       </c>
       <c r="B36" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4197,34 +4184,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>680781</v>
+        <v>680731</v>
       </c>
       <c r="R36" t="n">
-        <v>7087170</v>
+        <v>7087201</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4271,22 +4258,26 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126839997</v>
+        <v>126836460</v>
       </c>
       <c r="B37" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4318,10 +4309,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>680676</v>
+        <v>680779</v>
       </c>
       <c r="R37" t="n">
-        <v>7087207</v>
+        <v>7087200</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4368,12 +4359,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4384,10 +4375,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126837084</v>
+        <v>126836463</v>
       </c>
       <c r="B38" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4415,14 +4406,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>680731</v>
+        <v>680773</v>
       </c>
       <c r="R38" t="n">
-        <v>7087201</v>
+        <v>7087233</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4469,12 +4460,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4485,10 +4476,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126836460</v>
+        <v>126836477</v>
       </c>
       <c r="B39" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4520,10 +4511,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>680779</v>
+        <v>680709</v>
       </c>
       <c r="R39" t="n">
-        <v>7087200</v>
+        <v>7087204</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4586,45 +4577,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126836463</v>
+        <v>126837192</v>
       </c>
       <c r="B40" t="n">
-        <v>79011</v>
+        <v>56849</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>680773</v>
+        <v>680665</v>
       </c>
       <c r="R40" t="n">
-        <v>7087233</v>
+        <v>7087191</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4659,6 +4658,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4671,12 +4675,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4687,10 +4691,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126836477</v>
+        <v>126838798</v>
       </c>
       <c r="B41" t="n">
-        <v>79011</v>
+        <v>57817</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4698,34 +4702,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>680709</v>
+        <v>680781</v>
       </c>
       <c r="R41" t="n">
-        <v>7087204</v>
+        <v>7087170</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4772,26 +4776,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126839937</v>
+        <v>126836516</v>
       </c>
       <c r="B42" t="n">
-        <v>79629</v>
+        <v>78681</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4799,21 +4799,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>680761</v>
+        <v>680654</v>
       </c>
       <c r="R42" t="n">
-        <v>7087124</v>
+        <v>7087188</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4873,12 +4873,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4889,10 +4889,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126839994</v>
+        <v>126839937</v>
       </c>
       <c r="B43" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4900,21 +4900,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>680650</v>
+        <v>680761</v>
       </c>
       <c r="R43" t="n">
-        <v>7087238</v>
+        <v>7087124</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4990,10 +4990,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126836483</v>
+        <v>126839994</v>
       </c>
       <c r="B44" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>680673</v>
+        <v>680650</v>
       </c>
       <c r="R44" t="n">
-        <v>7087210</v>
+        <v>7087238</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5075,12 +5075,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5091,10 +5091,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126836516</v>
+        <v>126836483</v>
       </c>
       <c r="B45" t="n">
-        <v>78678</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5102,21 +5102,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>680654</v>
+        <v>680673</v>
       </c>
       <c r="R45" t="n">
-        <v>7087188</v>
+        <v>7087210</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5192,10 +5192,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126836198</v>
+        <v>126838822</v>
       </c>
       <c r="B46" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5203,34 +5203,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>680721</v>
+        <v>680783</v>
       </c>
       <c r="R46" t="n">
-        <v>7087133</v>
+        <v>7087170</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5277,12 +5277,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5293,10 +5293,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126838822</v>
+        <v>126836338</v>
       </c>
       <c r="B47" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5324,14 +5324,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>680783</v>
+        <v>680648</v>
       </c>
       <c r="R47" t="n">
-        <v>7087170</v>
+        <v>7087260</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5378,12 +5378,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5394,10 +5394,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126836338</v>
+        <v>126836198</v>
       </c>
       <c r="B48" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5405,21 +5405,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>680648</v>
+        <v>680721</v>
       </c>
       <c r="R48" t="n">
-        <v>7087260</v>
+        <v>7087133</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5498,7 +5498,7 @@
         <v>126839998</v>
       </c>
       <c r="B49" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>126837223</v>
       </c>
       <c r="B50" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5697,10 +5697,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126836517</v>
+        <v>126836548</v>
       </c>
       <c r="B51" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>680662</v>
       </c>
       <c r="R51" t="n">
-        <v>7087179</v>
+        <v>7087231</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5798,10 +5798,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126836548</v>
+        <v>126836517</v>
       </c>
       <c r="B52" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>680662</v>
       </c>
       <c r="R52" t="n">
-        <v>7087231</v>
+        <v>7087179</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6000,45 +6000,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126836519</v>
+        <v>126839949</v>
       </c>
       <c r="B54" t="n">
-        <v>78678</v>
+        <v>56849</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>680693</v>
+        <v>680726</v>
       </c>
       <c r="R54" t="n">
-        <v>7087159</v>
+        <v>7087219</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6085,12 +6090,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6104,7 +6109,7 @@
         <v>126837234</v>
       </c>
       <c r="B55" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6205,7 +6210,7 @@
         <v>126836541</v>
       </c>
       <c r="B56" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6303,50 +6308,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126839949</v>
+        <v>126836519</v>
       </c>
       <c r="B57" t="n">
-        <v>56849</v>
+        <v>78681</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>680726</v>
+        <v>680693</v>
       </c>
       <c r="R57" t="n">
-        <v>7087219</v>
+        <v>7087159</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6393,12 +6393,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6409,10 +6409,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126840919</v>
+        <v>126836490</v>
       </c>
       <c r="B58" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6420,37 +6420,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>680640</v>
+        <v>680645</v>
       </c>
       <c r="R58" t="n">
-        <v>7087261</v>
+        <v>7087280</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6480,40 +6477,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>10:17</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>10:17</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6524,10 +6510,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126836490</v>
+        <v>126837225</v>
       </c>
       <c r="B59" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6559,10 +6545,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>680645</v>
+        <v>680729</v>
       </c>
       <c r="R59" t="n">
-        <v>7087280</v>
+        <v>7087081</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6609,12 +6595,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6625,10 +6611,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126837225</v>
+        <v>126836469</v>
       </c>
       <c r="B60" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6660,10 +6646,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>680729</v>
+        <v>680728</v>
       </c>
       <c r="R60" t="n">
-        <v>7087081</v>
+        <v>7087278</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6710,12 +6696,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6726,10 +6712,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126836469</v>
+        <v>126840919</v>
       </c>
       <c r="B61" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6737,34 +6723,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>680728</v>
+        <v>680640</v>
       </c>
       <c r="R61" t="n">
-        <v>7087278</v>
+        <v>7087261</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6794,29 +6783,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6830,7 +6830,7 @@
         <v>126839996</v>
       </c>
       <c r="B62" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>126836486</v>
       </c>
       <c r="B63" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7029,10 +7029,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126836542</v>
+        <v>126836515</v>
       </c>
       <c r="B64" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>680710</v>
+        <v>680644</v>
       </c>
       <c r="R64" t="n">
-        <v>7087232</v>
+        <v>7087195</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7130,10 +7130,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126836515</v>
+        <v>126836542</v>
       </c>
       <c r="B65" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7165,10 +7165,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>680644</v>
+        <v>680710</v>
       </c>
       <c r="R65" t="n">
-        <v>7087195</v>
+        <v>7087232</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7234,7 +7234,7 @@
         <v>126839938</v>
       </c>
       <c r="B66" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>126838804</v>
       </c>
       <c r="B67" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7433,10 +7433,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126836302</v>
+        <v>126836474</v>
       </c>
       <c r="B68" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7444,21 +7444,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7468,10 +7468,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>680677</v>
+        <v>680712</v>
       </c>
       <c r="R68" t="n">
-        <v>7087201</v>
+        <v>7087225</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7534,45 +7534,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126837038</v>
+        <v>126836482</v>
       </c>
       <c r="B69" t="n">
-        <v>91284</v>
+        <v>79014</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>680783</v>
+        <v>680673</v>
       </c>
       <c r="R69" t="n">
-        <v>7087069</v>
+        <v>7087202</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7619,12 +7619,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7635,10 +7635,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126836474</v>
+        <v>126836302</v>
       </c>
       <c r="B70" t="n">
-        <v>79011</v>
+        <v>78773</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7646,21 +7646,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7670,10 +7670,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>680712</v>
+        <v>680677</v>
       </c>
       <c r="R70" t="n">
-        <v>7087225</v>
+        <v>7087201</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7736,45 +7736,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126836482</v>
+        <v>126837038</v>
       </c>
       <c r="B71" t="n">
-        <v>79011</v>
+        <v>91290</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>680673</v>
+        <v>680783</v>
       </c>
       <c r="R71" t="n">
-        <v>7087202</v>
+        <v>7087069</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7821,12 +7821,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7837,10 +7837,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126840002</v>
+        <v>126836524</v>
       </c>
       <c r="B72" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7872,10 +7872,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>680724</v>
+        <v>680720</v>
       </c>
       <c r="R72" t="n">
-        <v>7087119</v>
+        <v>7087100</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7922,12 +7922,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7938,10 +7938,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126836524</v>
+        <v>126836544</v>
       </c>
       <c r="B73" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7973,10 +7973,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>680720</v>
+        <v>680681</v>
       </c>
       <c r="R73" t="n">
-        <v>7087100</v>
+        <v>7087195</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8039,10 +8039,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126836544</v>
+        <v>126840002</v>
       </c>
       <c r="B74" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8074,10 +8074,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>680681</v>
+        <v>680724</v>
       </c>
       <c r="R74" t="n">
-        <v>7087195</v>
+        <v>7087119</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8124,12 +8124,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8140,10 +8140,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126836475</v>
+        <v>126839999</v>
       </c>
       <c r="B75" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>680708</v>
+        <v>680651</v>
       </c>
       <c r="R75" t="n">
-        <v>7087220</v>
+        <v>7087231</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8225,12 +8225,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8241,10 +8241,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126836336</v>
+        <v>126836475</v>
       </c>
       <c r="B76" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8276,10 +8276,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>680653</v>
+        <v>680708</v>
       </c>
       <c r="R76" t="n">
-        <v>7087252</v>
+        <v>7087220</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8342,10 +8342,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126836464</v>
+        <v>126836336</v>
       </c>
       <c r="B77" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>680772</v>
+        <v>680653</v>
       </c>
       <c r="R77" t="n">
         <v>7087252</v>
@@ -8443,10 +8443,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126836473</v>
+        <v>126836464</v>
       </c>
       <c r="B78" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>680710</v>
+        <v>680772</v>
       </c>
       <c r="R78" t="n">
-        <v>7087232</v>
+        <v>7087252</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8544,10 +8544,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126839999</v>
+        <v>126836473</v>
       </c>
       <c r="B79" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8579,10 +8579,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>680651</v>
+        <v>680710</v>
       </c>
       <c r="R79" t="n">
-        <v>7087231</v>
+        <v>7087232</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8629,12 +8629,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8749,7 +8749,7 @@
         <v>126837069</v>
       </c>
       <c r="B81" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>126837053</v>
       </c>
       <c r="B82" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>126836472</v>
       </c>
       <c r="B83" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>126836470</v>
       </c>
       <c r="B84" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>126836468</v>
       </c>
       <c r="B85" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9251,32 +9251,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126836503</v>
+        <v>126836481</v>
       </c>
       <c r="B86" t="n">
-        <v>92609</v>
+        <v>79014</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9286,10 +9286,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>680682</v>
+        <v>680670</v>
       </c>
       <c r="R86" t="n">
-        <v>7087164</v>
+        <v>7087199</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9352,10 +9352,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126836481</v>
+        <v>126836480</v>
       </c>
       <c r="B87" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9387,10 +9387,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>680670</v>
+        <v>680660</v>
       </c>
       <c r="R87" t="n">
-        <v>7087199</v>
+        <v>7087210</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9453,32 +9453,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126837231</v>
+        <v>126836503</v>
       </c>
       <c r="B88" t="n">
-        <v>79011</v>
+        <v>92615</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9488,10 +9488,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>680642</v>
+        <v>680682</v>
       </c>
       <c r="R88" t="n">
-        <v>7087222</v>
+        <v>7087164</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9538,12 +9538,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9554,10 +9554,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126836480</v>
+        <v>126837082</v>
       </c>
       <c r="B89" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9585,14 +9585,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>680660</v>
+        <v>680771</v>
       </c>
       <c r="R89" t="n">
-        <v>7087210</v>
+        <v>7087091</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9639,12 +9639,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9655,10 +9655,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126836357</v>
+        <v>126836309</v>
       </c>
       <c r="B90" t="n">
-        <v>79011</v>
+        <v>78772</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9666,21 +9666,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9690,10 +9690,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>680784</v>
+        <v>680720</v>
       </c>
       <c r="R90" t="n">
-        <v>7087010</v>
+        <v>7087133</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9756,10 +9756,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126837082</v>
+        <v>126836199</v>
       </c>
       <c r="B91" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9767,34 +9767,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>680771</v>
+        <v>680719</v>
       </c>
       <c r="R91" t="n">
-        <v>7087091</v>
+        <v>7087133</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9841,12 +9841,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -9857,10 +9857,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126839992</v>
+        <v>126840864</v>
       </c>
       <c r="B92" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9868,34 +9868,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>680767</v>
+        <v>680671</v>
       </c>
       <c r="R92" t="n">
-        <v>7087114</v>
+        <v>7087236</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9925,29 +9928,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -9958,10 +9972,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126836309</v>
+        <v>126837231</v>
       </c>
       <c r="B93" t="n">
-        <v>78769</v>
+        <v>79014</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9969,21 +9983,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9993,10 +10007,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>680720</v>
+        <v>680642</v>
       </c>
       <c r="R93" t="n">
-        <v>7087133</v>
+        <v>7087222</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10043,12 +10057,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10059,10 +10073,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126836199</v>
+        <v>126836357</v>
       </c>
       <c r="B94" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10070,21 +10084,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10094,10 +10108,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>680719</v>
+        <v>680784</v>
       </c>
       <c r="R94" t="n">
-        <v>7087133</v>
+        <v>7087010</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10160,10 +10174,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126840864</v>
+        <v>126839992</v>
       </c>
       <c r="B95" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10171,37 +10185,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>680671</v>
+        <v>680767</v>
       </c>
       <c r="R95" t="n">
-        <v>7087236</v>
+        <v>7087114</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10231,40 +10242,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10278,7 +10278,7 @@
         <v>126836226</v>
       </c>
       <c r="B96" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>126836505</v>
       </c>
       <c r="B97" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>126836471</v>
       </c>
       <c r="B98" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>126838824</v>
       </c>
       <c r="B99" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>126826458</v>
       </c>
       <c r="B100" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10790,10 +10790,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126836352</v>
+        <v>126836242</v>
       </c>
       <c r="B101" t="n">
-        <v>79011</v>
+        <v>91275</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10801,21 +10801,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10825,10 +10825,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>680753</v>
+        <v>680744</v>
       </c>
       <c r="R101" t="n">
-        <v>7087043</v>
+        <v>7087264</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10891,10 +10891,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126836487</v>
+        <v>126837236</v>
       </c>
       <c r="B102" t="n">
-        <v>79011</v>
+        <v>78681</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10902,21 +10902,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10926,10 +10926,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>680663</v>
+        <v>680673</v>
       </c>
       <c r="R102" t="n">
-        <v>7087244</v>
+        <v>7087186</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10976,12 +10976,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -10995,7 +10995,7 @@
         <v>126836522</v>
       </c>
       <c r="B103" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11093,10 +11093,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126837236</v>
+        <v>126836352</v>
       </c>
       <c r="B104" t="n">
-        <v>78678</v>
+        <v>79014</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11104,21 +11104,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11128,10 +11128,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>680673</v>
+        <v>680753</v>
       </c>
       <c r="R104" t="n">
-        <v>7087186</v>
+        <v>7087043</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11178,12 +11178,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11194,10 +11194,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126836242</v>
+        <v>126836487</v>
       </c>
       <c r="B105" t="n">
-        <v>91269</v>
+        <v>79014</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11205,21 +11205,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11229,10 +11229,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>680744</v>
+        <v>680663</v>
       </c>
       <c r="R105" t="n">
-        <v>7087264</v>
+        <v>7087244</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11409,7 +11409,7 @@
         <v>126836458</v>
       </c>
       <c r="B107" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>126836353</v>
       </c>
       <c r="B108" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>126836491</v>
       </c>
       <c r="B109" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11709,10 +11709,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126836462</v>
+        <v>126836485</v>
       </c>
       <c r="B110" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11744,10 +11744,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>680777</v>
+        <v>680660</v>
       </c>
       <c r="R110" t="n">
-        <v>7087215</v>
+        <v>7087229</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11810,10 +11810,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126836485</v>
+        <v>126836355</v>
       </c>
       <c r="B111" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11845,10 +11845,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>680660</v>
+        <v>680779</v>
       </c>
       <c r="R111" t="n">
-        <v>7087229</v>
+        <v>7087023</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11911,32 +11911,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126836355</v>
+        <v>126836230</v>
       </c>
       <c r="B112" t="n">
-        <v>79011</v>
+        <v>57479</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11946,10 +11946,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>680779</v>
+        <v>680774</v>
       </c>
       <c r="R112" t="n">
-        <v>7087023</v>
+        <v>7087234</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12012,50 +12012,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126839946</v>
+        <v>126836303</v>
       </c>
       <c r="B113" t="n">
-        <v>56849</v>
+        <v>78773</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>680662</v>
+        <v>680654</v>
       </c>
       <c r="R113" t="n">
-        <v>7087219</v>
+        <v>7087239</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12102,12 +12097,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12118,32 +12113,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126836230</v>
+        <v>126836462</v>
       </c>
       <c r="B114" t="n">
-        <v>57479</v>
+        <v>79014</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12153,10 +12148,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>680774</v>
+        <v>680777</v>
       </c>
       <c r="R114" t="n">
-        <v>7087234</v>
+        <v>7087215</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12222,7 +12217,7 @@
         <v>126836507</v>
       </c>
       <c r="B115" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12320,45 +12315,50 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126836303</v>
+        <v>126839946</v>
       </c>
       <c r="B116" t="n">
-        <v>78770</v>
+        <v>56849</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>680654</v>
+        <v>680662</v>
       </c>
       <c r="R116" t="n">
-        <v>7087239</v>
+        <v>7087219</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12405,12 +12405,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12421,10 +12421,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126836461</v>
+        <v>126836550</v>
       </c>
       <c r="B117" t="n">
-        <v>79011</v>
+        <v>78681</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12432,21 +12432,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12456,10 +12456,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>680774</v>
+        <v>680667</v>
       </c>
       <c r="R117" t="n">
-        <v>7087204</v>
+        <v>7087238</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12525,7 +12525,7 @@
         <v>126836476</v>
       </c>
       <c r="B118" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12623,10 +12623,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126836356</v>
+        <v>126836461</v>
       </c>
       <c r="B119" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12658,10 +12658,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>680782</v>
+        <v>680774</v>
       </c>
       <c r="R119" t="n">
-        <v>7087012</v>
+        <v>7087204</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12724,10 +12724,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126836550</v>
+        <v>126836356</v>
       </c>
       <c r="B120" t="n">
-        <v>78678</v>
+        <v>79014</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12735,21 +12735,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12759,10 +12759,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>680667</v>
+        <v>680782</v>
       </c>
       <c r="R120" t="n">
-        <v>7087238</v>
+        <v>7087012</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12825,10 +12825,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126825809</v>
+        <v>126839970</v>
       </c>
       <c r="B121" t="n">
-        <v>78678</v>
+        <v>78773</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12836,34 +12836,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>680666</v>
+        <v>680772</v>
       </c>
       <c r="R121" t="n">
-        <v>7087235</v>
+        <v>7087124</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12893,19 +12893,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>10:27</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>10:27</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12920,12 +12910,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -12936,10 +12926,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126836545</v>
+        <v>126836559</v>
       </c>
       <c r="B122" t="n">
-        <v>78678</v>
+        <v>91732</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12947,21 +12937,16 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>353</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12971,10 +12956,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>680657</v>
+        <v>680744</v>
       </c>
       <c r="R122" t="n">
-        <v>7087201</v>
+        <v>7087264</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13015,6 +13000,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13037,10 +13023,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126839970</v>
+        <v>126836545</v>
       </c>
       <c r="B123" t="n">
-        <v>78770</v>
+        <v>78681</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13048,21 +13034,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13072,10 +13058,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>680772</v>
+        <v>680657</v>
       </c>
       <c r="R123" t="n">
-        <v>7087124</v>
+        <v>7087201</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13122,12 +13108,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -13138,10 +13124,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126836559</v>
+        <v>126825809</v>
       </c>
       <c r="B124" t="n">
-        <v>91726</v>
+        <v>78681</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13149,29 +13135,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6040186</v>
+        <v>353</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>680744</v>
+        <v>680666</v>
       </c>
       <c r="R124" t="n">
-        <v>7087264</v>
+        <v>7087235</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13201,30 +13192,39 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13238,7 +13238,7 @@
         <v>126836354</v>
       </c>
       <c r="B125" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>126836466</v>
       </c>
       <c r="B126" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>126836479</v>
       </c>
       <c r="B127" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>126836488</v>
       </c>
       <c r="B128" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>126836478</v>
       </c>
       <c r="B129" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>126836467</v>
       </c>
       <c r="B130" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         <v>126838827</v>
       </c>
       <c r="B131" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>126838826</v>
       </c>
       <c r="B132" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/A 64499-2023 artfynd.xlsx
+++ b/artfynd/A 64499-2023 artfynd.xlsx
@@ -804,32 +804,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126836523</v>
+        <v>126836504</v>
       </c>
       <c r="B3" t="n">
-        <v>78681</v>
+        <v>92615</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680728</v>
+        <v>680697</v>
       </c>
       <c r="R3" t="n">
-        <v>7087114</v>
+        <v>7087147</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126836552</v>
+        <v>126825730</v>
       </c>
       <c r="B4" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,34 +916,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680642</v>
+        <v>680666</v>
       </c>
       <c r="R4" t="n">
-        <v>7087273</v>
+        <v>7087235</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,12 +970,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,12 +1000,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1006,32 +1016,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126839973</v>
+        <v>126836506</v>
       </c>
       <c r="B5" t="n">
-        <v>78773</v>
+        <v>92615</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680751</v>
+        <v>680723</v>
       </c>
       <c r="R5" t="n">
-        <v>7087100</v>
+        <v>7087114</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,12 +1101,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1107,32 +1117,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126836506</v>
+        <v>126836523</v>
       </c>
       <c r="B6" t="n">
-        <v>92615</v>
+        <v>78681</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,7 +1152,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680723</v>
+        <v>680728</v>
       </c>
       <c r="R6" t="n">
         <v>7087114</v>
@@ -1208,32 +1218,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126836504</v>
+        <v>126836552</v>
       </c>
       <c r="B7" t="n">
-        <v>92615</v>
+        <v>78681</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680697</v>
+        <v>680642</v>
       </c>
       <c r="R7" t="n">
-        <v>7087147</v>
+        <v>7087273</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126825730</v>
+        <v>126836489</v>
       </c>
       <c r="B8" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1320,34 +1330,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680666</v>
+        <v>680647</v>
       </c>
       <c r="R8" t="n">
-        <v>7087235</v>
+        <v>7087267</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,22 +1384,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,12 +1404,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1420,7 +1420,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126836489</v>
+        <v>126836484</v>
       </c>
       <c r="B9" t="n">
         <v>79014</v>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680647</v>
+        <v>680665</v>
       </c>
       <c r="R9" t="n">
-        <v>7087267</v>
+        <v>7087214</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126836484</v>
+        <v>126838823</v>
       </c>
       <c r="B10" t="n">
         <v>79014</v>
@@ -1552,14 +1552,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680665</v>
+        <v>680767</v>
       </c>
       <c r="R10" t="n">
-        <v>7087214</v>
+        <v>7087204</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,12 +1606,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1622,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126838823</v>
+        <v>126839973</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,34 +1633,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680767</v>
+        <v>680751</v>
       </c>
       <c r="R11" t="n">
-        <v>7087204</v>
+        <v>7087100</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,12 +1707,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1723,10 +1723,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126837190</v>
+        <v>126836520</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>78681</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1734,42 +1734,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680778</v>
+        <v>680716</v>
       </c>
       <c r="R12" t="n">
-        <v>7087007</v>
+        <v>7087135</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,11 +1796,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1821,12 +1808,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1837,7 +1824,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126836520</v>
+        <v>126840004</v>
       </c>
       <c r="B13" t="n">
         <v>78681</v>
@@ -1872,10 +1859,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680716</v>
+        <v>680639</v>
       </c>
       <c r="R13" t="n">
-        <v>7087135</v>
+        <v>7087277</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,12 +1909,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1938,7 +1925,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126840004</v>
+        <v>126836546</v>
       </c>
       <c r="B14" t="n">
         <v>78681</v>
@@ -1973,10 +1960,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680639</v>
+        <v>680660</v>
       </c>
       <c r="R14" t="n">
-        <v>7087277</v>
+        <v>7087210</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2023,12 +2010,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2039,7 +2026,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126836546</v>
+        <v>126837233</v>
       </c>
       <c r="B15" t="n">
         <v>78681</v>
@@ -2074,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680660</v>
+        <v>680698</v>
       </c>
       <c r="R15" t="n">
-        <v>7087210</v>
+        <v>7087108</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,12 +2111,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2140,10 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126837233</v>
+        <v>126837083</v>
       </c>
       <c r="B16" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2151,34 +2138,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680698</v>
+        <v>680743</v>
       </c>
       <c r="R16" t="n">
-        <v>7087108</v>
+        <v>7087104</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,12 +2212,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2241,10 +2228,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126839974</v>
+        <v>126836555</v>
       </c>
       <c r="B17" t="n">
-        <v>78772</v>
+        <v>78420</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,21 +2239,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2276,10 +2263,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680751</v>
+        <v>680660</v>
       </c>
       <c r="R17" t="n">
-        <v>7087100</v>
+        <v>7087210</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2326,12 +2313,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2342,10 +2329,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126837083</v>
+        <v>126839974</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,34 +2340,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680743</v>
+        <v>680751</v>
       </c>
       <c r="R18" t="n">
-        <v>7087104</v>
+        <v>7087100</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,12 +2414,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2443,10 +2430,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126836555</v>
+        <v>126837190</v>
       </c>
       <c r="B19" t="n">
-        <v>78420</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,34 +2441,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680660</v>
+        <v>680778</v>
       </c>
       <c r="R19" t="n">
-        <v>7087210</v>
+        <v>7087007</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,6 +2511,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2528,12 +2528,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2544,7 +2544,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126837085</v>
+        <v>126836351</v>
       </c>
       <c r="B20" t="n">
         <v>79014</v>
@@ -2575,14 +2575,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680698</v>
+        <v>680723</v>
       </c>
       <c r="R20" t="n">
-        <v>7087214</v>
+        <v>7087114</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2629,12 +2629,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2645,7 +2645,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126836351</v>
+        <v>126837227</v>
       </c>
       <c r="B21" t="n">
         <v>79014</v>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680723</v>
+        <v>680693</v>
       </c>
       <c r="R21" t="n">
-        <v>7087114</v>
+        <v>7087147</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,12 +2730,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2746,7 +2746,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126837227</v>
+        <v>126837085</v>
       </c>
       <c r="B22" t="n">
         <v>79014</v>
@@ -2777,14 +2777,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>680693</v>
+        <v>680698</v>
       </c>
       <c r="R22" t="n">
-        <v>7087147</v>
+        <v>7087214</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2831,12 +2831,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3251,7 +3251,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126839989</v>
+        <v>126838825</v>
       </c>
       <c r="B27" t="n">
         <v>79014</v>
@@ -3282,14 +3282,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680774</v>
+        <v>680759</v>
       </c>
       <c r="R27" t="n">
-        <v>7087124</v>
+        <v>7087282</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,12 +3336,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3352,7 +3352,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126838825</v>
+        <v>126838821</v>
       </c>
       <c r="B28" t="n">
         <v>79014</v>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680759</v>
+        <v>680775</v>
       </c>
       <c r="R28" t="n">
-        <v>7087282</v>
+        <v>7087121</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3453,7 +3453,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126838821</v>
+        <v>126837228</v>
       </c>
       <c r="B29" t="n">
         <v>79014</v>
@@ -3484,14 +3484,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680775</v>
+        <v>680658</v>
       </c>
       <c r="R29" t="n">
-        <v>7087121</v>
+        <v>7087213</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3538,12 +3538,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3554,7 +3554,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126837228</v>
+        <v>126840000</v>
       </c>
       <c r="B30" t="n">
         <v>79014</v>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680658</v>
+        <v>680643</v>
       </c>
       <c r="R30" t="n">
-        <v>7087213</v>
+        <v>7087277</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3639,12 +3639,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3655,10 +3655,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126839971</v>
+        <v>126839989</v>
       </c>
       <c r="B31" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3666,21 +3666,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680772</v>
+        <v>680774</v>
       </c>
       <c r="R31" t="n">
         <v>7087124</v>
@@ -3756,10 +3756,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126840000</v>
+        <v>126839971</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3767,21 +3767,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680643</v>
+        <v>680772</v>
       </c>
       <c r="R32" t="n">
-        <v>7087277</v>
+        <v>7087124</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4788,10 +4788,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126836516</v>
+        <v>126839994</v>
       </c>
       <c r="B42" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4799,21 +4799,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>680654</v>
+        <v>680650</v>
       </c>
       <c r="R42" t="n">
-        <v>7087188</v>
+        <v>7087238</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4873,12 +4873,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4889,10 +4889,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126839937</v>
+        <v>126836483</v>
       </c>
       <c r="B43" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4900,21 +4900,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>680761</v>
+        <v>680673</v>
       </c>
       <c r="R43" t="n">
-        <v>7087124</v>
+        <v>7087210</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4974,12 +4974,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -4990,10 +4990,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126839994</v>
+        <v>126839937</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5001,21 +5001,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>680650</v>
+        <v>680761</v>
       </c>
       <c r="R44" t="n">
-        <v>7087238</v>
+        <v>7087124</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5091,10 +5091,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126836483</v>
+        <v>126836516</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5102,21 +5102,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>680673</v>
+        <v>680654</v>
       </c>
       <c r="R45" t="n">
-        <v>7087210</v>
+        <v>7087188</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5394,10 +5394,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126836198</v>
+        <v>126839998</v>
       </c>
       <c r="B48" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5405,21 +5405,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>680721</v>
+        <v>680673</v>
       </c>
       <c r="R48" t="n">
-        <v>7087133</v>
+        <v>7087211</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5479,12 +5479,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5495,7 +5495,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126839998</v>
+        <v>126837223</v>
       </c>
       <c r="B49" t="n">
         <v>79014</v>
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>680673</v>
+        <v>680772</v>
       </c>
       <c r="R49" t="n">
-        <v>7087211</v>
+        <v>7087024</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5580,12 +5580,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5596,10 +5596,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126837223</v>
+        <v>126836198</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5607,21 +5607,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>680772</v>
+        <v>680721</v>
       </c>
       <c r="R50" t="n">
-        <v>7087024</v>
+        <v>7087133</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5681,12 +5681,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6000,50 +6000,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126839949</v>
+        <v>126836490</v>
       </c>
       <c r="B54" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>680726</v>
+        <v>680645</v>
       </c>
       <c r="R54" t="n">
-        <v>7087219</v>
+        <v>7087280</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6090,12 +6085,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6106,10 +6101,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126837234</v>
+        <v>126837225</v>
       </c>
       <c r="B55" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6117,21 +6112,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6141,10 +6136,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>680694</v>
+        <v>680729</v>
       </c>
       <c r="R55" t="n">
-        <v>7087158</v>
+        <v>7087081</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6207,10 +6202,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126836541</v>
+        <v>126836469</v>
       </c>
       <c r="B56" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6218,21 +6213,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6242,10 +6237,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>680708</v>
+        <v>680728</v>
       </c>
       <c r="R56" t="n">
-        <v>7087251</v>
+        <v>7087278</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6308,10 +6303,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126836519</v>
+        <v>126839996</v>
       </c>
       <c r="B57" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6319,21 +6314,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6343,10 +6338,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>680693</v>
+        <v>680745</v>
       </c>
       <c r="R57" t="n">
-        <v>7087159</v>
+        <v>7087170</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6393,12 +6388,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6409,7 +6404,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126836490</v>
+        <v>126836486</v>
       </c>
       <c r="B58" t="n">
         <v>79014</v>
@@ -6444,10 +6439,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>680645</v>
+        <v>680663</v>
       </c>
       <c r="R58" t="n">
-        <v>7087280</v>
+        <v>7087231</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6510,10 +6505,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126837225</v>
+        <v>126840919</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6521,34 +6516,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>680729</v>
+        <v>680640</v>
       </c>
       <c r="R59" t="n">
-        <v>7087081</v>
+        <v>7087261</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6578,29 +6576,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6611,10 +6620,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126836469</v>
+        <v>126837234</v>
       </c>
       <c r="B60" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6622,21 +6631,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6646,10 +6655,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>680728</v>
+        <v>680694</v>
       </c>
       <c r="R60" t="n">
-        <v>7087278</v>
+        <v>7087158</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6696,12 +6705,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6712,10 +6721,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126840919</v>
+        <v>126836541</v>
       </c>
       <c r="B61" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6723,37 +6732,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>680640</v>
+        <v>680708</v>
       </c>
       <c r="R61" t="n">
-        <v>7087261</v>
+        <v>7087251</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6783,40 +6789,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>10:17</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>10:17</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6827,10 +6822,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126839996</v>
+        <v>126836519</v>
       </c>
       <c r="B62" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6838,21 +6833,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6862,10 +6857,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>680745</v>
+        <v>680693</v>
       </c>
       <c r="R62" t="n">
-        <v>7087170</v>
+        <v>7087159</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6912,12 +6907,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6928,45 +6923,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126836486</v>
+        <v>126839949</v>
       </c>
       <c r="B63" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>680663</v>
+        <v>680726</v>
       </c>
       <c r="R63" t="n">
-        <v>7087231</v>
+        <v>7087219</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7013,12 +7013,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7029,10 +7029,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126836515</v>
+        <v>126836302</v>
       </c>
       <c r="B64" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7040,21 +7040,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>680644</v>
+        <v>680677</v>
       </c>
       <c r="R64" t="n">
-        <v>7087195</v>
+        <v>7087201</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7130,45 +7130,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126836542</v>
+        <v>126837038</v>
       </c>
       <c r="B65" t="n">
-        <v>78681</v>
+        <v>91290</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>680710</v>
+        <v>680783</v>
       </c>
       <c r="R65" t="n">
-        <v>7087232</v>
+        <v>7087069</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7215,12 +7215,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7231,10 +7231,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126839938</v>
+        <v>126836474</v>
       </c>
       <c r="B66" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7242,21 +7242,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7266,10 +7266,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>680652</v>
+        <v>680712</v>
       </c>
       <c r="R66" t="n">
-        <v>7087271</v>
+        <v>7087225</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7316,12 +7316,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7332,10 +7332,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126838804</v>
+        <v>126836482</v>
       </c>
       <c r="B67" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7343,34 +7343,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>680765</v>
+        <v>680673</v>
       </c>
       <c r="R67" t="n">
-        <v>7087124</v>
+        <v>7087202</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7417,12 +7417,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7433,10 +7433,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126836474</v>
+        <v>126836515</v>
       </c>
       <c r="B68" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7444,21 +7444,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7468,10 +7468,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>680712</v>
+        <v>680644</v>
       </c>
       <c r="R68" t="n">
-        <v>7087225</v>
+        <v>7087195</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7534,10 +7534,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126836482</v>
+        <v>126836542</v>
       </c>
       <c r="B69" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7545,21 +7545,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>680673</v>
+        <v>680710</v>
       </c>
       <c r="R69" t="n">
-        <v>7087202</v>
+        <v>7087232</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7635,10 +7635,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126836302</v>
+        <v>126839938</v>
       </c>
       <c r="B70" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7646,21 +7646,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7670,10 +7670,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>680677</v>
+        <v>680652</v>
       </c>
       <c r="R70" t="n">
-        <v>7087201</v>
+        <v>7087271</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7720,12 +7720,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7736,45 +7736,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126837038</v>
+        <v>126838804</v>
       </c>
       <c r="B71" t="n">
-        <v>91290</v>
+        <v>78772</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>680783</v>
+        <v>680765</v>
       </c>
       <c r="R71" t="n">
-        <v>7087069</v>
+        <v>7087124</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7821,12 +7821,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7837,10 +7837,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126836524</v>
+        <v>126839999</v>
       </c>
       <c r="B72" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7848,21 +7848,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7872,10 +7872,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>680720</v>
+        <v>680651</v>
       </c>
       <c r="R72" t="n">
-        <v>7087100</v>
+        <v>7087231</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7922,12 +7922,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7938,7 +7938,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126836544</v>
+        <v>126836524</v>
       </c>
       <c r="B73" t="n">
         <v>78681</v>
@@ -7973,10 +7973,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>680681</v>
+        <v>680720</v>
       </c>
       <c r="R73" t="n">
-        <v>7087195</v>
+        <v>7087100</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8039,7 +8039,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126840002</v>
+        <v>126836544</v>
       </c>
       <c r="B74" t="n">
         <v>78681</v>
@@ -8074,10 +8074,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>680724</v>
+        <v>680681</v>
       </c>
       <c r="R74" t="n">
-        <v>7087119</v>
+        <v>7087195</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8124,12 +8124,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8140,10 +8140,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126839999</v>
+        <v>126840002</v>
       </c>
       <c r="B75" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8151,21 +8151,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>680651</v>
+        <v>680724</v>
       </c>
       <c r="R75" t="n">
-        <v>7087231</v>
+        <v>7087119</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9251,32 +9251,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126836481</v>
+        <v>126836503</v>
       </c>
       <c r="B86" t="n">
-        <v>79014</v>
+        <v>92615</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9286,10 +9286,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>680670</v>
+        <v>680682</v>
       </c>
       <c r="R86" t="n">
-        <v>7087199</v>
+        <v>7087164</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9352,7 +9352,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126836480</v>
+        <v>126837231</v>
       </c>
       <c r="B87" t="n">
         <v>79014</v>
@@ -9387,10 +9387,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>680660</v>
+        <v>680642</v>
       </c>
       <c r="R87" t="n">
-        <v>7087210</v>
+        <v>7087222</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9437,12 +9437,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9453,32 +9453,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126836503</v>
+        <v>126836480</v>
       </c>
       <c r="B88" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9488,10 +9488,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>680682</v>
+        <v>680660</v>
       </c>
       <c r="R88" t="n">
-        <v>7087164</v>
+        <v>7087210</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9554,7 +9554,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126837082</v>
+        <v>126836357</v>
       </c>
       <c r="B89" t="n">
         <v>79014</v>
@@ -9585,14 +9585,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>680771</v>
+        <v>680784</v>
       </c>
       <c r="R89" t="n">
-        <v>7087091</v>
+        <v>7087010</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9639,12 +9639,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9655,10 +9655,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126836309</v>
+        <v>126839992</v>
       </c>
       <c r="B90" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9666,21 +9666,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9690,10 +9690,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>680720</v>
+        <v>680767</v>
       </c>
       <c r="R90" t="n">
-        <v>7087133</v>
+        <v>7087114</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9740,12 +9740,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9756,10 +9756,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126836199</v>
+        <v>126836309</v>
       </c>
       <c r="B91" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9767,21 +9767,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9791,7 +9791,7 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>680719</v>
+        <v>680720</v>
       </c>
       <c r="R91" t="n">
         <v>7087133</v>
@@ -9857,7 +9857,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126840864</v>
+        <v>126836199</v>
       </c>
       <c r="B92" t="n">
         <v>79632</v>
@@ -9886,19 +9886,16 @@
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>680671</v>
+        <v>680719</v>
       </c>
       <c r="R92" t="n">
-        <v>7087236</v>
+        <v>7087133</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9928,40 +9925,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -9972,10 +9958,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126837231</v>
+        <v>126840864</v>
       </c>
       <c r="B93" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9983,34 +9969,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>680642</v>
+        <v>680671</v>
       </c>
       <c r="R93" t="n">
-        <v>7087222</v>
+        <v>7087236</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10040,29 +10029,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10073,7 +10073,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126836357</v>
+        <v>126836481</v>
       </c>
       <c r="B94" t="n">
         <v>79014</v>
@@ -10108,10 +10108,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>680784</v>
+        <v>680670</v>
       </c>
       <c r="R94" t="n">
-        <v>7087010</v>
+        <v>7087199</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10174,7 +10174,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126839992</v>
+        <v>126837082</v>
       </c>
       <c r="B95" t="n">
         <v>79014</v>
@@ -10205,14 +10205,14 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>680767</v>
+        <v>680771</v>
       </c>
       <c r="R95" t="n">
-        <v>7087114</v>
+        <v>7087091</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10259,12 +10259,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10376,45 +10376,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126836505</v>
+        <v>126826458</v>
       </c>
       <c r="B97" t="n">
-        <v>92615</v>
+        <v>78772</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>680711</v>
+        <v>680755</v>
       </c>
       <c r="R97" t="n">
-        <v>7087139</v>
+        <v>7087104</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10444,9 +10444,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10461,12 +10471,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10477,32 +10487,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126836471</v>
+        <v>126836505</v>
       </c>
       <c r="B98" t="n">
-        <v>79014</v>
+        <v>92615</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10512,10 +10522,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>680715</v>
+        <v>680711</v>
       </c>
       <c r="R98" t="n">
-        <v>7087274</v>
+        <v>7087139</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10578,7 +10588,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126838824</v>
+        <v>126836471</v>
       </c>
       <c r="B99" t="n">
         <v>79014</v>
@@ -10609,14 +10619,14 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>680778</v>
+        <v>680715</v>
       </c>
       <c r="R99" t="n">
-        <v>7087226</v>
+        <v>7087274</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10663,12 +10673,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10679,10 +10689,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126826458</v>
+        <v>126838824</v>
       </c>
       <c r="B100" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10690,34 +10700,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>680755</v>
+        <v>680778</v>
       </c>
       <c r="R100" t="n">
-        <v>7087104</v>
+        <v>7087226</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10747,19 +10757,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10774,12 +10774,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10790,10 +10790,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126836242</v>
+        <v>126836259</v>
       </c>
       <c r="B101" t="n">
-        <v>91275</v>
+        <v>57657</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10801,34 +10801,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>680744</v>
+        <v>680665</v>
       </c>
       <c r="R101" t="n">
-        <v>7087264</v>
+        <v>7087214</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10861,6 +10866,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10891,10 +10901,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126837236</v>
+        <v>126836242</v>
       </c>
       <c r="B102" t="n">
-        <v>78681</v>
+        <v>91275</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10902,21 +10912,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>353</v>
+        <v>112</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10926,10 +10936,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>680673</v>
+        <v>680744</v>
       </c>
       <c r="R102" t="n">
-        <v>7087186</v>
+        <v>7087264</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10976,12 +10986,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -10992,7 +11002,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126836522</v>
+        <v>126837236</v>
       </c>
       <c r="B103" t="n">
         <v>78681</v>
@@ -11027,10 +11037,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>680726</v>
+        <v>680673</v>
       </c>
       <c r="R103" t="n">
-        <v>7087132</v>
+        <v>7087186</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11077,12 +11087,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11093,10 +11103,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126836352</v>
+        <v>126836522</v>
       </c>
       <c r="B104" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11104,21 +11114,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11128,10 +11138,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>680753</v>
+        <v>680726</v>
       </c>
       <c r="R104" t="n">
-        <v>7087043</v>
+        <v>7087132</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11194,7 +11204,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126836487</v>
+        <v>126836352</v>
       </c>
       <c r="B105" t="n">
         <v>79014</v>
@@ -11229,10 +11239,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>680663</v>
+        <v>680753</v>
       </c>
       <c r="R105" t="n">
-        <v>7087244</v>
+        <v>7087043</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11295,10 +11305,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126836259</v>
+        <v>126836487</v>
       </c>
       <c r="B106" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11306,39 +11316,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>680665</v>
+        <v>680663</v>
       </c>
       <c r="R106" t="n">
-        <v>7087214</v>
+        <v>7087244</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11371,11 +11376,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11608,32 +11608,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126836491</v>
+        <v>126836507</v>
       </c>
       <c r="B109" t="n">
-        <v>79014</v>
+        <v>92615</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11643,10 +11643,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>680645</v>
+        <v>680724</v>
       </c>
       <c r="R109" t="n">
-        <v>7087283</v>
+        <v>7087106</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11709,7 +11709,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126836485</v>
+        <v>126836491</v>
       </c>
       <c r="B110" t="n">
         <v>79014</v>
@@ -11744,10 +11744,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>680660</v>
+        <v>680645</v>
       </c>
       <c r="R110" t="n">
-        <v>7087229</v>
+        <v>7087283</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11810,7 +11810,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126836355</v>
+        <v>126836462</v>
       </c>
       <c r="B111" t="n">
         <v>79014</v>
@@ -11845,10 +11845,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>680779</v>
+        <v>680777</v>
       </c>
       <c r="R111" t="n">
-        <v>7087023</v>
+        <v>7087215</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11911,32 +11911,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126836230</v>
+        <v>126836485</v>
       </c>
       <c r="B112" t="n">
-        <v>57479</v>
+        <v>79014</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11946,10 +11946,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>680774</v>
+        <v>680660</v>
       </c>
       <c r="R112" t="n">
-        <v>7087234</v>
+        <v>7087229</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12012,10 +12012,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126836303</v>
+        <v>126836355</v>
       </c>
       <c r="B113" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12023,21 +12023,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>680654</v>
+        <v>680779</v>
       </c>
       <c r="R113" t="n">
-        <v>7087239</v>
+        <v>7087023</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12113,32 +12113,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126836462</v>
+        <v>126836230</v>
       </c>
       <c r="B114" t="n">
-        <v>79014</v>
+        <v>57479</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12148,10 +12148,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>680777</v>
+        <v>680774</v>
       </c>
       <c r="R114" t="n">
-        <v>7087215</v>
+        <v>7087234</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12214,32 +12214,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126836507</v>
+        <v>126836303</v>
       </c>
       <c r="B115" t="n">
-        <v>92615</v>
+        <v>78773</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12249,10 +12249,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>680724</v>
+        <v>680654</v>
       </c>
       <c r="R115" t="n">
-        <v>7087106</v>
+        <v>7087239</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12522,7 +12522,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126836476</v>
+        <v>126836461</v>
       </c>
       <c r="B118" t="n">
         <v>79014</v>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>680712</v>
+        <v>680774</v>
       </c>
       <c r="R118" t="n">
-        <v>7087209</v>
+        <v>7087204</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12623,7 +12623,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126836461</v>
+        <v>126836356</v>
       </c>
       <c r="B119" t="n">
         <v>79014</v>
@@ -12658,10 +12658,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>680774</v>
+        <v>680782</v>
       </c>
       <c r="R119" t="n">
-        <v>7087204</v>
+        <v>7087012</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12724,7 +12724,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126836356</v>
+        <v>126836476</v>
       </c>
       <c r="B120" t="n">
         <v>79014</v>
@@ -12759,10 +12759,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>680782</v>
+        <v>680712</v>
       </c>
       <c r="R120" t="n">
-        <v>7087012</v>
+        <v>7087209</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12825,10 +12825,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126839970</v>
+        <v>126836354</v>
       </c>
       <c r="B121" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12836,21 +12836,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>680772</v>
+        <v>680771</v>
       </c>
       <c r="R121" t="n">
-        <v>7087124</v>
+        <v>7087030</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12910,12 +12910,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -12926,10 +12926,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126836559</v>
+        <v>126836466</v>
       </c>
       <c r="B122" t="n">
-        <v>91732</v>
+        <v>79014</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12937,16 +12937,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12956,10 +12961,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>680744</v>
+        <v>680756</v>
       </c>
       <c r="R122" t="n">
-        <v>7087264</v>
+        <v>7087273</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13000,7 +13005,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13023,10 +13027,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126836545</v>
+        <v>126836479</v>
       </c>
       <c r="B123" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13034,21 +13038,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13058,10 +13062,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>680657</v>
+        <v>680684</v>
       </c>
       <c r="R123" t="n">
-        <v>7087201</v>
+        <v>7087202</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13124,10 +13128,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126825809</v>
+        <v>126836488</v>
       </c>
       <c r="B124" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13135,34 +13139,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>680666</v>
+        <v>680655</v>
       </c>
       <c r="R124" t="n">
-        <v>7087235</v>
+        <v>7087246</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13192,19 +13196,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>10:27</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>10:27</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13219,12 +13213,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13235,7 +13229,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126836354</v>
+        <v>126836478</v>
       </c>
       <c r="B125" t="n">
         <v>79014</v>
@@ -13270,10 +13264,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>680771</v>
+        <v>680711</v>
       </c>
       <c r="R125" t="n">
-        <v>7087030</v>
+        <v>7087181</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13336,10 +13330,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126836466</v>
+        <v>126836545</v>
       </c>
       <c r="B126" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13347,21 +13341,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13371,10 +13365,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>680756</v>
+        <v>680657</v>
       </c>
       <c r="R126" t="n">
-        <v>7087273</v>
+        <v>7087201</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13437,10 +13431,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126836479</v>
+        <v>126825809</v>
       </c>
       <c r="B127" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13448,34 +13442,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>680684</v>
+        <v>680666</v>
       </c>
       <c r="R127" t="n">
-        <v>7087202</v>
+        <v>7087235</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13505,9 +13499,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13522,12 +13526,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13538,10 +13542,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126836488</v>
+        <v>126836559</v>
       </c>
       <c r="B128" t="n">
-        <v>79014</v>
+        <v>91732</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13549,21 +13553,16 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13573,10 +13572,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>680655</v>
+        <v>680744</v>
       </c>
       <c r="R128" t="n">
-        <v>7087246</v>
+        <v>7087264</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13617,6 +13616,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13639,10 +13639,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126836478</v>
+        <v>126839970</v>
       </c>
       <c r="B129" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13650,21 +13650,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13674,10 +13674,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>680711</v>
+        <v>680772</v>
       </c>
       <c r="R129" t="n">
-        <v>7087181</v>
+        <v>7087124</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13724,12 +13724,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">

--- a/artfynd/A 64499-2023 artfynd.xlsx
+++ b/artfynd/A 64499-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126836504</v>
+        <v>126836506</v>
       </c>
       <c r="B3" t="n">
         <v>92615</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680697</v>
+        <v>680723</v>
       </c>
       <c r="R3" t="n">
-        <v>7087147</v>
+        <v>7087114</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126825730</v>
+        <v>126836523</v>
       </c>
       <c r="B4" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,34 +916,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680666</v>
+        <v>680728</v>
       </c>
       <c r="R4" t="n">
-        <v>7087235</v>
+        <v>7087114</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,22 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,12 +990,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1016,32 +1006,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126836506</v>
+        <v>126836489</v>
       </c>
       <c r="B5" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680723</v>
+        <v>680647</v>
       </c>
       <c r="R5" t="n">
-        <v>7087114</v>
+        <v>7087267</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126836523</v>
+        <v>126836484</v>
       </c>
       <c r="B6" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,21 +1118,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1152,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680728</v>
+        <v>680665</v>
       </c>
       <c r="R6" t="n">
-        <v>7087114</v>
+        <v>7087214</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126836552</v>
+        <v>126838823</v>
       </c>
       <c r="B7" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,34 +1219,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680642</v>
+        <v>680767</v>
       </c>
       <c r="R7" t="n">
-        <v>7087273</v>
+        <v>7087204</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,12 +1293,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1319,10 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126836489</v>
+        <v>126825730</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1330,34 +1320,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680647</v>
+        <v>680666</v>
       </c>
       <c r="R8" t="n">
-        <v>7087267</v>
+        <v>7087235</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,12 +1374,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,12 +1404,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1420,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126836484</v>
+        <v>126839973</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1431,21 +1431,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680665</v>
+        <v>680751</v>
       </c>
       <c r="R9" t="n">
-        <v>7087214</v>
+        <v>7087100</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,12 +1505,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126838823</v>
+        <v>126836552</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,34 +1532,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680767</v>
+        <v>680642</v>
       </c>
       <c r="R10" t="n">
-        <v>7087204</v>
+        <v>7087273</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,12 +1606,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1622,32 +1622,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126839973</v>
+        <v>126836504</v>
       </c>
       <c r="B11" t="n">
-        <v>78773</v>
+        <v>92615</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680751</v>
+        <v>680697</v>
       </c>
       <c r="R11" t="n">
-        <v>7087100</v>
+        <v>7087147</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,12 +1707,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2544,7 +2544,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126836351</v>
+        <v>126837085</v>
       </c>
       <c r="B20" t="n">
         <v>79014</v>
@@ -2575,14 +2575,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680723</v>
+        <v>680698</v>
       </c>
       <c r="R20" t="n">
-        <v>7087114</v>
+        <v>7087214</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2629,12 +2629,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2645,7 +2645,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126837227</v>
+        <v>126836351</v>
       </c>
       <c r="B21" t="n">
         <v>79014</v>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680693</v>
+        <v>680723</v>
       </c>
       <c r="R21" t="n">
-        <v>7087147</v>
+        <v>7087114</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,12 +2730,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2746,7 +2746,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126837085</v>
+        <v>126837227</v>
       </c>
       <c r="B22" t="n">
         <v>79014</v>
@@ -2777,14 +2777,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>680698</v>
+        <v>680693</v>
       </c>
       <c r="R22" t="n">
-        <v>7087214</v>
+        <v>7087147</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2831,12 +2831,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3049,10 +3049,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126836551</v>
+        <v>126839971</v>
       </c>
       <c r="B25" t="n">
-        <v>78681</v>
+        <v>78772</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3060,21 +3060,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680654</v>
+        <v>680772</v>
       </c>
       <c r="R25" t="n">
-        <v>7087239</v>
+        <v>7087124</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3134,12 +3134,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3150,7 +3150,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126840003</v>
+        <v>126836551</v>
       </c>
       <c r="B26" t="n">
         <v>78681</v>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680729</v>
+        <v>680654</v>
       </c>
       <c r="R26" t="n">
-        <v>7087103</v>
+        <v>7087239</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,12 +3235,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126838825</v>
+        <v>126840003</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3262,34 +3262,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680759</v>
+        <v>680729</v>
       </c>
       <c r="R27" t="n">
-        <v>7087282</v>
+        <v>7087103</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,12 +3336,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3352,7 +3352,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126838821</v>
+        <v>126838825</v>
       </c>
       <c r="B28" t="n">
         <v>79014</v>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680775</v>
+        <v>680759</v>
       </c>
       <c r="R28" t="n">
-        <v>7087121</v>
+        <v>7087282</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3453,7 +3453,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126837228</v>
+        <v>126838821</v>
       </c>
       <c r="B29" t="n">
         <v>79014</v>
@@ -3484,14 +3484,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680658</v>
+        <v>680775</v>
       </c>
       <c r="R29" t="n">
-        <v>7087213</v>
+        <v>7087121</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3538,12 +3538,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3554,7 +3554,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126840000</v>
+        <v>126837228</v>
       </c>
       <c r="B30" t="n">
         <v>79014</v>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680643</v>
+        <v>680658</v>
       </c>
       <c r="R30" t="n">
-        <v>7087277</v>
+        <v>7087213</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3639,12 +3639,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3655,7 +3655,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126839989</v>
+        <v>126840000</v>
       </c>
       <c r="B31" t="n">
         <v>79014</v>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680774</v>
+        <v>680643</v>
       </c>
       <c r="R31" t="n">
-        <v>7087124</v>
+        <v>7087277</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3756,10 +3756,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126839971</v>
+        <v>126839989</v>
       </c>
       <c r="B32" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3767,21 +3767,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680772</v>
+        <v>680774</v>
       </c>
       <c r="R32" t="n">
         <v>7087124</v>
@@ -4788,10 +4788,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126839994</v>
+        <v>126836516</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4799,21 +4799,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>680650</v>
+        <v>680654</v>
       </c>
       <c r="R42" t="n">
-        <v>7087238</v>
+        <v>7087188</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4873,12 +4873,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4889,7 +4889,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126836483</v>
+        <v>126839994</v>
       </c>
       <c r="B43" t="n">
         <v>79014</v>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>680673</v>
+        <v>680650</v>
       </c>
       <c r="R43" t="n">
-        <v>7087210</v>
+        <v>7087238</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4974,12 +4974,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -4990,10 +4990,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126839937</v>
+        <v>126836483</v>
       </c>
       <c r="B44" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5001,21 +5001,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>680761</v>
+        <v>680673</v>
       </c>
       <c r="R44" t="n">
-        <v>7087124</v>
+        <v>7087210</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5075,12 +5075,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5091,10 +5091,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126836516</v>
+        <v>126839937</v>
       </c>
       <c r="B45" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5102,21 +5102,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>680654</v>
+        <v>680761</v>
       </c>
       <c r="R45" t="n">
-        <v>7087188</v>
+        <v>7087124</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5176,12 +5176,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5192,10 +5192,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126838822</v>
+        <v>126836548</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5203,34 +5203,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>680783</v>
+        <v>680662</v>
       </c>
       <c r="R46" t="n">
-        <v>7087170</v>
+        <v>7087231</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5277,12 +5277,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5293,10 +5293,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126836338</v>
+        <v>126836517</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5304,21 +5304,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5328,10 +5328,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>680648</v>
+        <v>680662</v>
       </c>
       <c r="R47" t="n">
-        <v>7087260</v>
+        <v>7087179</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5394,7 +5394,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126839998</v>
+        <v>126838822</v>
       </c>
       <c r="B48" t="n">
         <v>79014</v>
@@ -5425,14 +5425,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>680673</v>
+        <v>680783</v>
       </c>
       <c r="R48" t="n">
-        <v>7087211</v>
+        <v>7087170</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5479,12 +5479,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5495,7 +5495,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126837223</v>
+        <v>126836338</v>
       </c>
       <c r="B49" t="n">
         <v>79014</v>
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>680772</v>
+        <v>680648</v>
       </c>
       <c r="R49" t="n">
-        <v>7087024</v>
+        <v>7087260</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5580,12 +5580,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5697,10 +5697,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126836548</v>
+        <v>126839998</v>
       </c>
       <c r="B51" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5708,21 +5708,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>680662</v>
+        <v>680673</v>
       </c>
       <c r="R51" t="n">
-        <v>7087231</v>
+        <v>7087211</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5782,12 +5782,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5798,10 +5798,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126836517</v>
+        <v>126837223</v>
       </c>
       <c r="B52" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5809,21 +5809,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5833,10 +5833,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>680662</v>
+        <v>680772</v>
       </c>
       <c r="R52" t="n">
-        <v>7087179</v>
+        <v>7087024</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5883,12 +5883,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -7029,10 +7029,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126836302</v>
+        <v>126836474</v>
       </c>
       <c r="B64" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7040,21 +7040,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>680677</v>
+        <v>680712</v>
       </c>
       <c r="R64" t="n">
-        <v>7087201</v>
+        <v>7087225</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7130,45 +7130,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126837038</v>
+        <v>126836515</v>
       </c>
       <c r="B65" t="n">
-        <v>91290</v>
+        <v>78681</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>680783</v>
+        <v>680644</v>
       </c>
       <c r="R65" t="n">
-        <v>7087069</v>
+        <v>7087195</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7215,12 +7215,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7231,7 +7231,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126836474</v>
+        <v>126836482</v>
       </c>
       <c r="B66" t="n">
         <v>79014</v>
@@ -7266,10 +7266,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>680712</v>
+        <v>680673</v>
       </c>
       <c r="R66" t="n">
-        <v>7087225</v>
+        <v>7087202</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7332,10 +7332,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126836482</v>
+        <v>126839938</v>
       </c>
       <c r="B67" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7343,21 +7343,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>680673</v>
+        <v>680652</v>
       </c>
       <c r="R67" t="n">
-        <v>7087202</v>
+        <v>7087271</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7417,12 +7417,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7433,45 +7433,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126836515</v>
+        <v>126837038</v>
       </c>
       <c r="B68" t="n">
-        <v>78681</v>
+        <v>91290</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>680644</v>
+        <v>680783</v>
       </c>
       <c r="R68" t="n">
-        <v>7087195</v>
+        <v>7087069</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7518,12 +7518,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7635,10 +7635,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126839938</v>
+        <v>126838804</v>
       </c>
       <c r="B70" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7646,34 +7646,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>680652</v>
+        <v>680765</v>
       </c>
       <c r="R70" t="n">
-        <v>7087271</v>
+        <v>7087124</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7720,12 +7720,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7736,10 +7736,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126838804</v>
+        <v>126836302</v>
       </c>
       <c r="B71" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7747,34 +7747,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>680765</v>
+        <v>680677</v>
       </c>
       <c r="R71" t="n">
-        <v>7087124</v>
+        <v>7087201</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7821,12 +7821,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -9251,32 +9251,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126836503</v>
+        <v>126836481</v>
       </c>
       <c r="B86" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9286,10 +9286,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>680682</v>
+        <v>680670</v>
       </c>
       <c r="R86" t="n">
-        <v>7087164</v>
+        <v>7087199</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9352,7 +9352,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126837231</v>
+        <v>126837082</v>
       </c>
       <c r="B87" t="n">
         <v>79014</v>
@@ -9383,14 +9383,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>680642</v>
+        <v>680771</v>
       </c>
       <c r="R87" t="n">
-        <v>7087222</v>
+        <v>7087091</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9437,12 +9437,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9453,32 +9453,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126836480</v>
+        <v>126836503</v>
       </c>
       <c r="B88" t="n">
-        <v>79014</v>
+        <v>92615</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9488,10 +9488,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>680660</v>
+        <v>680682</v>
       </c>
       <c r="R88" t="n">
-        <v>7087210</v>
+        <v>7087164</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9554,7 +9554,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126836357</v>
+        <v>126837231</v>
       </c>
       <c r="B89" t="n">
         <v>79014</v>
@@ -9589,10 +9589,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>680784</v>
+        <v>680642</v>
       </c>
       <c r="R89" t="n">
-        <v>7087010</v>
+        <v>7087222</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9639,12 +9639,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9655,7 +9655,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126839992</v>
+        <v>126836480</v>
       </c>
       <c r="B90" t="n">
         <v>79014</v>
@@ -9690,10 +9690,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>680767</v>
+        <v>680660</v>
       </c>
       <c r="R90" t="n">
-        <v>7087114</v>
+        <v>7087210</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9740,12 +9740,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9756,10 +9756,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126836309</v>
+        <v>126836357</v>
       </c>
       <c r="B91" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9767,21 +9767,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9791,10 +9791,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>680720</v>
+        <v>680784</v>
       </c>
       <c r="R91" t="n">
-        <v>7087133</v>
+        <v>7087010</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9857,10 +9857,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126836199</v>
+        <v>126839992</v>
       </c>
       <c r="B92" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9868,21 +9868,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9892,10 +9892,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>680719</v>
+        <v>680767</v>
       </c>
       <c r="R92" t="n">
-        <v>7087133</v>
+        <v>7087114</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9942,12 +9942,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -9958,10 +9958,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126840864</v>
+        <v>126836309</v>
       </c>
       <c r="B93" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9969,37 +9969,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>680671</v>
+        <v>680720</v>
       </c>
       <c r="R93" t="n">
-        <v>7087236</v>
+        <v>7087133</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10029,40 +10026,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10073,10 +10059,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126836481</v>
+        <v>126836199</v>
       </c>
       <c r="B94" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10084,21 +10070,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10108,10 +10094,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>680670</v>
+        <v>680719</v>
       </c>
       <c r="R94" t="n">
-        <v>7087199</v>
+        <v>7087133</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10174,10 +10160,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126837082</v>
+        <v>126840864</v>
       </c>
       <c r="B95" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10185,34 +10171,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>680771</v>
+        <v>680671</v>
       </c>
       <c r="R95" t="n">
-        <v>7087091</v>
+        <v>7087236</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10242,29 +10231,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10275,32 +10275,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126836226</v>
+        <v>126836505</v>
       </c>
       <c r="B96" t="n">
-        <v>91325</v>
+        <v>92615</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10310,10 +10310,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>680802</v>
+        <v>680711</v>
       </c>
       <c r="R96" t="n">
-        <v>7086993</v>
+        <v>7087139</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10376,10 +10376,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126826458</v>
+        <v>126836226</v>
       </c>
       <c r="B97" t="n">
-        <v>78772</v>
+        <v>91325</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10387,34 +10387,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>680755</v>
+        <v>680802</v>
       </c>
       <c r="R97" t="n">
-        <v>7087104</v>
+        <v>7086993</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10444,19 +10444,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10471,12 +10461,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10487,32 +10477,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126836505</v>
+        <v>126836471</v>
       </c>
       <c r="B98" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10522,10 +10512,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>680711</v>
+        <v>680715</v>
       </c>
       <c r="R98" t="n">
-        <v>7087139</v>
+        <v>7087274</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10588,7 +10578,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126836471</v>
+        <v>126838824</v>
       </c>
       <c r="B99" t="n">
         <v>79014</v>
@@ -10619,14 +10609,14 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>680715</v>
+        <v>680778</v>
       </c>
       <c r="R99" t="n">
-        <v>7087274</v>
+        <v>7087226</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10673,12 +10663,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10689,10 +10679,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126838824</v>
+        <v>126826458</v>
       </c>
       <c r="B100" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10700,34 +10690,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>680778</v>
+        <v>680755</v>
       </c>
       <c r="R100" t="n">
-        <v>7087226</v>
+        <v>7087104</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10757,9 +10747,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10774,12 +10774,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11608,10 +11608,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126836507</v>
+        <v>126839946</v>
       </c>
       <c r="B109" t="n">
-        <v>92615</v>
+        <v>56849</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11619,34 +11619,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>680724</v>
+        <v>680662</v>
       </c>
       <c r="R109" t="n">
-        <v>7087106</v>
+        <v>7087219</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11693,12 +11698,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -11709,32 +11714,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126836491</v>
+        <v>126836230</v>
       </c>
       <c r="B110" t="n">
-        <v>79014</v>
+        <v>57479</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11744,10 +11749,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>680645</v>
+        <v>680774</v>
       </c>
       <c r="R110" t="n">
-        <v>7087283</v>
+        <v>7087234</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11810,32 +11815,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126836462</v>
+        <v>126836507</v>
       </c>
       <c r="B111" t="n">
-        <v>79014</v>
+        <v>92615</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11845,10 +11850,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>680777</v>
+        <v>680724</v>
       </c>
       <c r="R111" t="n">
-        <v>7087215</v>
+        <v>7087106</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11911,7 +11916,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126836485</v>
+        <v>126836491</v>
       </c>
       <c r="B112" t="n">
         <v>79014</v>
@@ -11946,10 +11951,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>680660</v>
+        <v>680645</v>
       </c>
       <c r="R112" t="n">
-        <v>7087229</v>
+        <v>7087283</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12012,7 +12017,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126836355</v>
+        <v>126836462</v>
       </c>
       <c r="B113" t="n">
         <v>79014</v>
@@ -12047,10 +12052,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>680779</v>
+        <v>680777</v>
       </c>
       <c r="R113" t="n">
-        <v>7087023</v>
+        <v>7087215</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12113,32 +12118,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126836230</v>
+        <v>126836485</v>
       </c>
       <c r="B114" t="n">
-        <v>57479</v>
+        <v>79014</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12148,10 +12153,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>680774</v>
+        <v>680660</v>
       </c>
       <c r="R114" t="n">
-        <v>7087234</v>
+        <v>7087229</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12214,10 +12219,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126836303</v>
+        <v>126836355</v>
       </c>
       <c r="B115" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12225,21 +12230,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12249,10 +12254,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>680654</v>
+        <v>680779</v>
       </c>
       <c r="R115" t="n">
-        <v>7087239</v>
+        <v>7087023</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12315,50 +12320,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126839946</v>
+        <v>126836303</v>
       </c>
       <c r="B116" t="n">
-        <v>56849</v>
+        <v>78773</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>680662</v>
+        <v>680654</v>
       </c>
       <c r="R116" t="n">
-        <v>7087219</v>
+        <v>7087239</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12405,12 +12405,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12421,10 +12421,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126836550</v>
+        <v>126836476</v>
       </c>
       <c r="B117" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12432,21 +12432,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12456,10 +12456,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>680667</v>
+        <v>680712</v>
       </c>
       <c r="R117" t="n">
-        <v>7087238</v>
+        <v>7087209</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12522,10 +12522,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126836461</v>
+        <v>126836550</v>
       </c>
       <c r="B118" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12533,21 +12533,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>680774</v>
+        <v>680667</v>
       </c>
       <c r="R118" t="n">
-        <v>7087204</v>
+        <v>7087238</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12623,7 +12623,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126836356</v>
+        <v>126836461</v>
       </c>
       <c r="B119" t="n">
         <v>79014</v>
@@ -12658,10 +12658,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>680782</v>
+        <v>680774</v>
       </c>
       <c r="R119" t="n">
-        <v>7087012</v>
+        <v>7087204</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12724,7 +12724,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126836476</v>
+        <v>126836356</v>
       </c>
       <c r="B120" t="n">
         <v>79014</v>
@@ -12759,10 +12759,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>680712</v>
+        <v>680782</v>
       </c>
       <c r="R120" t="n">
-        <v>7087209</v>
+        <v>7087012</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>

--- a/artfynd/A 64499-2023 artfynd.xlsx
+++ b/artfynd/A 64499-2023 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126836506</v>
+        <v>126836504</v>
       </c>
       <c r="B3" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680723</v>
+        <v>680697</v>
       </c>
       <c r="R3" t="n">
-        <v>7087114</v>
+        <v>7087147</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126836523</v>
+        <v>126836484</v>
       </c>
       <c r="B4" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680728</v>
+        <v>680665</v>
       </c>
       <c r="R4" t="n">
-        <v>7087114</v>
+        <v>7087214</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126836484</v>
+        <v>126838823</v>
       </c>
       <c r="B6" t="n">
         <v>79014</v>
@@ -1138,14 +1138,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680665</v>
+        <v>680767</v>
       </c>
       <c r="R6" t="n">
-        <v>7087214</v>
+        <v>7087204</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,12 +1192,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1208,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126838823</v>
+        <v>126825730</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1219,34 +1219,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680767</v>
+        <v>680666</v>
       </c>
       <c r="R7" t="n">
-        <v>7087204</v>
+        <v>7087235</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,12 +1273,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1293,12 +1303,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1309,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126825730</v>
+        <v>126836523</v>
       </c>
       <c r="B8" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1320,34 +1330,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680666</v>
+        <v>680728</v>
       </c>
       <c r="R8" t="n">
-        <v>7087235</v>
+        <v>7087114</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,22 +1384,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,12 +1404,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1420,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126839973</v>
+        <v>126836552</v>
       </c>
       <c r="B9" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1431,21 +1431,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680751</v>
+        <v>680642</v>
       </c>
       <c r="R9" t="n">
-        <v>7087100</v>
+        <v>7087273</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,12 +1505,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1521,32 +1521,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126836552</v>
+        <v>126836506</v>
       </c>
       <c r="B10" t="n">
-        <v>78681</v>
+        <v>92616</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680642</v>
+        <v>680723</v>
       </c>
       <c r="R10" t="n">
-        <v>7087273</v>
+        <v>7087114</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,32 +1622,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126836504</v>
+        <v>126839973</v>
       </c>
       <c r="B11" t="n">
-        <v>92615</v>
+        <v>78773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680697</v>
+        <v>680751</v>
       </c>
       <c r="R11" t="n">
-        <v>7087147</v>
+        <v>7087100</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,12 +1707,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1723,10 +1723,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126836520</v>
+        <v>126837083</v>
       </c>
       <c r="B12" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1734,34 +1734,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680716</v>
+        <v>680743</v>
       </c>
       <c r="R12" t="n">
-        <v>7087135</v>
+        <v>7087104</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1808,12 +1808,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1824,10 +1824,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126840004</v>
+        <v>126839974</v>
       </c>
       <c r="B13" t="n">
-        <v>78681</v>
+        <v>78772</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1835,21 +1835,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680639</v>
+        <v>680751</v>
       </c>
       <c r="R13" t="n">
-        <v>7087277</v>
+        <v>7087100</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126836546</v>
+        <v>126836520</v>
       </c>
       <c r="B14" t="n">
         <v>78681</v>
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680660</v>
+        <v>680716</v>
       </c>
       <c r="R14" t="n">
-        <v>7087210</v>
+        <v>7087135</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126837233</v>
+        <v>126840004</v>
       </c>
       <c r="B15" t="n">
         <v>78681</v>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680698</v>
+        <v>680639</v>
       </c>
       <c r="R15" t="n">
-        <v>7087108</v>
+        <v>7087277</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2111,12 +2111,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2127,10 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126837083</v>
+        <v>126836546</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,34 +2138,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680743</v>
+        <v>680660</v>
       </c>
       <c r="R16" t="n">
-        <v>7087104</v>
+        <v>7087210</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2212,12 +2212,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2228,10 +2228,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126836555</v>
+        <v>126837233</v>
       </c>
       <c r="B17" t="n">
-        <v>78420</v>
+        <v>78681</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2239,21 +2239,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680660</v>
+        <v>680698</v>
       </c>
       <c r="R17" t="n">
-        <v>7087210</v>
+        <v>7087108</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2313,12 +2313,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2329,10 +2329,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126839974</v>
+        <v>126836555</v>
       </c>
       <c r="B18" t="n">
-        <v>78772</v>
+        <v>78420</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2340,21 +2340,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680751</v>
+        <v>680660</v>
       </c>
       <c r="R18" t="n">
-        <v>7087100</v>
+        <v>7087210</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,12 +2414,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -3049,10 +3049,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126839971</v>
+        <v>126836551</v>
       </c>
       <c r="B25" t="n">
-        <v>78772</v>
+        <v>78681</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3060,21 +3060,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680772</v>
+        <v>680654</v>
       </c>
       <c r="R25" t="n">
-        <v>7087124</v>
+        <v>7087239</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3134,12 +3134,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3150,7 +3150,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126836551</v>
+        <v>126840003</v>
       </c>
       <c r="B26" t="n">
         <v>78681</v>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680654</v>
+        <v>680729</v>
       </c>
       <c r="R26" t="n">
-        <v>7087239</v>
+        <v>7087103</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,12 +3235,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126840003</v>
+        <v>126840000</v>
       </c>
       <c r="B27" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3262,21 +3262,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680729</v>
+        <v>680643</v>
       </c>
       <c r="R27" t="n">
-        <v>7087103</v>
+        <v>7087277</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3352,7 +3352,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126838825</v>
+        <v>126839989</v>
       </c>
       <c r="B28" t="n">
         <v>79014</v>
@@ -3383,14 +3383,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680759</v>
+        <v>680774</v>
       </c>
       <c r="R28" t="n">
-        <v>7087282</v>
+        <v>7087124</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3437,12 +3437,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3554,7 +3554,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126837228</v>
+        <v>126838825</v>
       </c>
       <c r="B30" t="n">
         <v>79014</v>
@@ -3585,14 +3585,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680658</v>
+        <v>680759</v>
       </c>
       <c r="R30" t="n">
-        <v>7087213</v>
+        <v>7087282</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3639,12 +3639,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3655,7 +3655,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126840000</v>
+        <v>126837228</v>
       </c>
       <c r="B31" t="n">
         <v>79014</v>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680643</v>
+        <v>680658</v>
       </c>
       <c r="R31" t="n">
-        <v>7087277</v>
+        <v>7087213</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3740,12 +3740,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3756,10 +3756,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126839989</v>
+        <v>126839971</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3767,21 +3767,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680774</v>
+        <v>680772</v>
       </c>
       <c r="R32" t="n">
         <v>7087124</v>
@@ -4072,45 +4072,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126839997</v>
+        <v>126837192</v>
       </c>
       <c r="B35" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>680676</v>
+        <v>680665</v>
       </c>
       <c r="R35" t="n">
-        <v>7087207</v>
+        <v>7087191</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,6 +4153,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4157,12 +4170,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4173,10 +4186,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126837084</v>
+        <v>126838798</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4184,34 +4197,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>680731</v>
+        <v>680781</v>
       </c>
       <c r="R36" t="n">
-        <v>7087201</v>
+        <v>7087170</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4258,23 +4271,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126836460</v>
+        <v>126837084</v>
       </c>
       <c r="B37" t="n">
         <v>79014</v>
@@ -4305,14 +4314,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>680779</v>
+        <v>680731</v>
       </c>
       <c r="R37" t="n">
-        <v>7087200</v>
+        <v>7087201</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4359,12 +4368,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4375,7 +4384,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126836463</v>
+        <v>126839997</v>
       </c>
       <c r="B38" t="n">
         <v>79014</v>
@@ -4410,10 +4419,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>680773</v>
+        <v>680676</v>
       </c>
       <c r="R38" t="n">
-        <v>7087233</v>
+        <v>7087207</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4460,12 +4469,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4476,7 +4485,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126836477</v>
+        <v>126836460</v>
       </c>
       <c r="B39" t="n">
         <v>79014</v>
@@ -4511,10 +4520,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>680709</v>
+        <v>680779</v>
       </c>
       <c r="R39" t="n">
-        <v>7087204</v>
+        <v>7087200</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4577,53 +4586,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126837192</v>
+        <v>126836477</v>
       </c>
       <c r="B40" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>680665</v>
+        <v>680709</v>
       </c>
       <c r="R40" t="n">
-        <v>7087191</v>
+        <v>7087204</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4658,11 +4659,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4675,12 +4671,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4691,10 +4687,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126838798</v>
+        <v>126836463</v>
       </c>
       <c r="B41" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4702,34 +4698,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>680781</v>
+        <v>680773</v>
       </c>
       <c r="R41" t="n">
-        <v>7087170</v>
+        <v>7087233</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4776,22 +4772,26 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126836516</v>
+        <v>126839937</v>
       </c>
       <c r="B42" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4799,21 +4799,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>680654</v>
+        <v>680761</v>
       </c>
       <c r="R42" t="n">
-        <v>7087188</v>
+        <v>7087124</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4873,12 +4873,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4889,10 +4889,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126839994</v>
+        <v>126836516</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4900,21 +4900,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>680650</v>
+        <v>680654</v>
       </c>
       <c r="R43" t="n">
-        <v>7087238</v>
+        <v>7087188</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4974,12 +4974,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5091,10 +5091,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126839937</v>
+        <v>126839994</v>
       </c>
       <c r="B45" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5102,21 +5102,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>680761</v>
+        <v>680650</v>
       </c>
       <c r="R45" t="n">
-        <v>7087124</v>
+        <v>7087238</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5192,10 +5192,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126836548</v>
+        <v>126838822</v>
       </c>
       <c r="B46" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5203,34 +5203,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>680662</v>
+        <v>680783</v>
       </c>
       <c r="R46" t="n">
-        <v>7087231</v>
+        <v>7087170</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5277,12 +5277,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5293,10 +5293,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126836517</v>
+        <v>126837223</v>
       </c>
       <c r="B47" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5304,21 +5304,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5328,10 +5328,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>680662</v>
+        <v>680772</v>
       </c>
       <c r="R47" t="n">
-        <v>7087179</v>
+        <v>7087024</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5378,12 +5378,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5394,7 +5394,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126838822</v>
+        <v>126836338</v>
       </c>
       <c r="B48" t="n">
         <v>79014</v>
@@ -5425,14 +5425,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>680783</v>
+        <v>680648</v>
       </c>
       <c r="R48" t="n">
-        <v>7087170</v>
+        <v>7087260</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5479,12 +5479,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5495,7 +5495,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126836338</v>
+        <v>126839998</v>
       </c>
       <c r="B49" t="n">
         <v>79014</v>
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>680648</v>
+        <v>680673</v>
       </c>
       <c r="R49" t="n">
-        <v>7087260</v>
+        <v>7087211</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5580,12 +5580,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5596,32 +5596,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126836198</v>
+        <v>126839976</v>
       </c>
       <c r="B50" t="n">
-        <v>79632</v>
+        <v>58027</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>680721</v>
+        <v>680693</v>
       </c>
       <c r="R50" t="n">
-        <v>7087133</v>
+        <v>7087162</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5681,12 +5681,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5697,10 +5697,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126839998</v>
+        <v>126836548</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5708,21 +5708,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>680673</v>
+        <v>680662</v>
       </c>
       <c r="R51" t="n">
-        <v>7087211</v>
+        <v>7087231</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5782,12 +5782,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5798,10 +5798,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126837223</v>
+        <v>126836517</v>
       </c>
       <c r="B52" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5809,21 +5809,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5833,10 +5833,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>680772</v>
+        <v>680662</v>
       </c>
       <c r="R52" t="n">
-        <v>7087024</v>
+        <v>7087179</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5883,12 +5883,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5899,32 +5899,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126839976</v>
+        <v>126836198</v>
       </c>
       <c r="B53" t="n">
-        <v>58027</v>
+        <v>79632</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5934,10 +5934,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>680693</v>
+        <v>680721</v>
       </c>
       <c r="R53" t="n">
-        <v>7087162</v>
+        <v>7087133</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5984,12 +5984,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6000,10 +6000,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126836490</v>
+        <v>126837234</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6011,21 +6011,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6035,10 +6035,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>680645</v>
+        <v>680694</v>
       </c>
       <c r="R54" t="n">
-        <v>7087280</v>
+        <v>7087158</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6085,12 +6085,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6101,10 +6101,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126837225</v>
+        <v>126836541</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6112,21 +6112,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6136,10 +6136,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>680729</v>
+        <v>680708</v>
       </c>
       <c r="R55" t="n">
-        <v>7087081</v>
+        <v>7087251</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6186,12 +6186,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6202,10 +6202,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126836469</v>
+        <v>126836519</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6213,21 +6213,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6237,10 +6237,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>680728</v>
+        <v>680693</v>
       </c>
       <c r="R56" t="n">
-        <v>7087278</v>
+        <v>7087159</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6303,7 +6303,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126839996</v>
+        <v>126836486</v>
       </c>
       <c r="B57" t="n">
         <v>79014</v>
@@ -6338,10 +6338,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>680745</v>
+        <v>680663</v>
       </c>
       <c r="R57" t="n">
-        <v>7087170</v>
+        <v>7087231</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6388,12 +6388,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6404,7 +6404,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126836486</v>
+        <v>126836469</v>
       </c>
       <c r="B58" t="n">
         <v>79014</v>
@@ -6439,10 +6439,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>680663</v>
+        <v>680728</v>
       </c>
       <c r="R58" t="n">
-        <v>7087231</v>
+        <v>7087278</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6505,10 +6505,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126840919</v>
+        <v>126836490</v>
       </c>
       <c r="B59" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6516,37 +6516,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>680640</v>
+        <v>680645</v>
       </c>
       <c r="R59" t="n">
-        <v>7087261</v>
+        <v>7087280</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6576,40 +6573,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>10:17</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>10:17</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6620,10 +6606,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126837234</v>
+        <v>126839996</v>
       </c>
       <c r="B60" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6631,21 +6617,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6655,10 +6641,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>680694</v>
+        <v>680745</v>
       </c>
       <c r="R60" t="n">
-        <v>7087158</v>
+        <v>7087170</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6705,12 +6691,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6721,10 +6707,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126836541</v>
+        <v>126837225</v>
       </c>
       <c r="B61" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6732,21 +6718,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6756,10 +6742,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>680708</v>
+        <v>680729</v>
       </c>
       <c r="R61" t="n">
-        <v>7087251</v>
+        <v>7087081</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6806,12 +6792,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6822,10 +6808,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126836519</v>
+        <v>126840919</v>
       </c>
       <c r="B62" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6833,34 +6819,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>680693</v>
+        <v>680640</v>
       </c>
       <c r="R62" t="n">
-        <v>7087159</v>
+        <v>7087261</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6890,29 +6879,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7029,10 +7029,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126836474</v>
+        <v>126836515</v>
       </c>
       <c r="B64" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7040,21 +7040,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>680712</v>
+        <v>680644</v>
       </c>
       <c r="R64" t="n">
-        <v>7087225</v>
+        <v>7087195</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7130,7 +7130,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126836515</v>
+        <v>126836542</v>
       </c>
       <c r="B65" t="n">
         <v>78681</v>
@@ -7165,10 +7165,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>680644</v>
+        <v>680710</v>
       </c>
       <c r="R65" t="n">
-        <v>7087195</v>
+        <v>7087232</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7332,45 +7332,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126839938</v>
+        <v>126837038</v>
       </c>
       <c r="B67" t="n">
-        <v>79632</v>
+        <v>91291</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>680652</v>
+        <v>680783</v>
       </c>
       <c r="R67" t="n">
-        <v>7087271</v>
+        <v>7087069</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7417,12 +7417,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7433,45 +7433,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126837038</v>
+        <v>126836474</v>
       </c>
       <c r="B68" t="n">
-        <v>91290</v>
+        <v>79014</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>680783</v>
+        <v>680712</v>
       </c>
       <c r="R68" t="n">
-        <v>7087069</v>
+        <v>7087225</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7518,12 +7518,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7534,10 +7534,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126836542</v>
+        <v>126839938</v>
       </c>
       <c r="B69" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7545,21 +7545,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>680710</v>
+        <v>680652</v>
       </c>
       <c r="R69" t="n">
-        <v>7087232</v>
+        <v>7087271</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7619,12 +7619,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7837,10 +7837,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126839999</v>
+        <v>126836524</v>
       </c>
       <c r="B72" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7848,21 +7848,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7872,10 +7872,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>680651</v>
+        <v>680720</v>
       </c>
       <c r="R72" t="n">
-        <v>7087231</v>
+        <v>7087100</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7922,12 +7922,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7938,7 +7938,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126836524</v>
+        <v>126836544</v>
       </c>
       <c r="B73" t="n">
         <v>78681</v>
@@ -7973,10 +7973,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>680720</v>
+        <v>680681</v>
       </c>
       <c r="R73" t="n">
-        <v>7087100</v>
+        <v>7087195</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8039,7 +8039,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126836544</v>
+        <v>126840002</v>
       </c>
       <c r="B74" t="n">
         <v>78681</v>
@@ -8074,10 +8074,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>680681</v>
+        <v>680724</v>
       </c>
       <c r="R74" t="n">
-        <v>7087195</v>
+        <v>7087119</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8124,12 +8124,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8140,10 +8140,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126840002</v>
+        <v>126836464</v>
       </c>
       <c r="B75" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8151,21 +8151,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>680724</v>
+        <v>680772</v>
       </c>
       <c r="R75" t="n">
-        <v>7087119</v>
+        <v>7087252</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8225,12 +8225,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8342,7 +8342,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126836336</v>
+        <v>126839999</v>
       </c>
       <c r="B77" t="n">
         <v>79014</v>
@@ -8377,10 +8377,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>680653</v>
+        <v>680651</v>
       </c>
       <c r="R77" t="n">
-        <v>7087252</v>
+        <v>7087231</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8427,12 +8427,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8443,7 +8443,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126836464</v>
+        <v>126836473</v>
       </c>
       <c r="B78" t="n">
         <v>79014</v>
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>680772</v>
+        <v>680710</v>
       </c>
       <c r="R78" t="n">
-        <v>7087252</v>
+        <v>7087232</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8544,7 +8544,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126836473</v>
+        <v>126836336</v>
       </c>
       <c r="B79" t="n">
         <v>79014</v>
@@ -8579,10 +8579,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>680710</v>
+        <v>680653</v>
       </c>
       <c r="R79" t="n">
-        <v>7087232</v>
+        <v>7087252</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8847,10 +8847,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126837053</v>
+        <v>126836470</v>
       </c>
       <c r="B82" t="n">
-        <v>91345</v>
+        <v>79014</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8858,34 +8858,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>680770</v>
+        <v>680718</v>
       </c>
       <c r="R82" t="n">
-        <v>7087092</v>
+        <v>7087288</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8932,12 +8932,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -8948,7 +8948,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126836472</v>
+        <v>126836468</v>
       </c>
       <c r="B83" t="n">
         <v>79014</v>
@@ -8983,10 +8983,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>680714</v>
+        <v>680752</v>
       </c>
       <c r="R83" t="n">
-        <v>7087268</v>
+        <v>7087262</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9049,7 +9049,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126836470</v>
+        <v>126836472</v>
       </c>
       <c r="B84" t="n">
         <v>79014</v>
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>680718</v>
+        <v>680714</v>
       </c>
       <c r="R84" t="n">
-        <v>7087288</v>
+        <v>7087268</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9150,10 +9150,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126836468</v>
+        <v>126837053</v>
       </c>
       <c r="B85" t="n">
-        <v>79014</v>
+        <v>91346</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9161,34 +9161,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>680752</v>
+        <v>680770</v>
       </c>
       <c r="R85" t="n">
-        <v>7087262</v>
+        <v>7087092</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9235,12 +9235,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9251,7 +9251,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126836481</v>
+        <v>126837231</v>
       </c>
       <c r="B86" t="n">
         <v>79014</v>
@@ -9286,10 +9286,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>680670</v>
+        <v>680642</v>
       </c>
       <c r="R86" t="n">
-        <v>7087199</v>
+        <v>7087222</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9336,12 +9336,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9352,7 +9352,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126837082</v>
+        <v>126839992</v>
       </c>
       <c r="B87" t="n">
         <v>79014</v>
@@ -9383,14 +9383,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>680771</v>
+        <v>680767</v>
       </c>
       <c r="R87" t="n">
-        <v>7087091</v>
+        <v>7087114</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9437,12 +9437,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9453,45 +9453,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126836503</v>
+        <v>126837082</v>
       </c>
       <c r="B88" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>680682</v>
+        <v>680771</v>
       </c>
       <c r="R88" t="n">
-        <v>7087164</v>
+        <v>7087091</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9538,12 +9538,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9554,7 +9554,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126837231</v>
+        <v>126836480</v>
       </c>
       <c r="B89" t="n">
         <v>79014</v>
@@ -9589,10 +9589,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>680642</v>
+        <v>680660</v>
       </c>
       <c r="R89" t="n">
-        <v>7087222</v>
+        <v>7087210</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9639,12 +9639,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9655,7 +9655,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126836480</v>
+        <v>126836481</v>
       </c>
       <c r="B90" t="n">
         <v>79014</v>
@@ -9690,10 +9690,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>680660</v>
+        <v>680670</v>
       </c>
       <c r="R90" t="n">
-        <v>7087210</v>
+        <v>7087199</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9857,32 +9857,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126839992</v>
+        <v>126836503</v>
       </c>
       <c r="B92" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9892,10 +9892,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>680767</v>
+        <v>680682</v>
       </c>
       <c r="R92" t="n">
-        <v>7087114</v>
+        <v>7087164</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9942,12 +9942,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -9958,10 +9958,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126836309</v>
+        <v>126836199</v>
       </c>
       <c r="B93" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9969,21 +9969,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9993,7 +9993,7 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>680720</v>
+        <v>680719</v>
       </c>
       <c r="R93" t="n">
         <v>7087133</v>
@@ -10059,7 +10059,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126836199</v>
+        <v>126840864</v>
       </c>
       <c r="B94" t="n">
         <v>79632</v>
@@ -10088,16 +10088,19 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>680719</v>
+        <v>680671</v>
       </c>
       <c r="R94" t="n">
-        <v>7087133</v>
+        <v>7087236</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10127,29 +10130,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10160,10 +10174,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126840864</v>
+        <v>126836309</v>
       </c>
       <c r="B95" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10171,37 +10185,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>680671</v>
+        <v>680720</v>
       </c>
       <c r="R95" t="n">
-        <v>7087236</v>
+        <v>7087133</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10231,40 +10242,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10275,45 +10275,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126836505</v>
+        <v>126838824</v>
       </c>
       <c r="B96" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>680711</v>
+        <v>680778</v>
       </c>
       <c r="R96" t="n">
-        <v>7087139</v>
+        <v>7087226</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10360,12 +10360,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10376,10 +10376,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126836226</v>
+        <v>126836471</v>
       </c>
       <c r="B97" t="n">
-        <v>91325</v>
+        <v>79014</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10387,21 +10387,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10411,10 +10411,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>680802</v>
+        <v>680715</v>
       </c>
       <c r="R97" t="n">
-        <v>7086993</v>
+        <v>7087274</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10477,10 +10477,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126836471</v>
+        <v>126826458</v>
       </c>
       <c r="B98" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10488,34 +10488,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>680715</v>
+        <v>680755</v>
       </c>
       <c r="R98" t="n">
-        <v>7087274</v>
+        <v>7087104</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10545,9 +10545,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10562,12 +10572,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10578,10 +10588,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126838824</v>
+        <v>126836226</v>
       </c>
       <c r="B99" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10589,34 +10599,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>680778</v>
+        <v>680802</v>
       </c>
       <c r="R99" t="n">
-        <v>7087226</v>
+        <v>7086993</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10663,12 +10673,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10679,45 +10689,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126826458</v>
+        <v>126836505</v>
       </c>
       <c r="B100" t="n">
-        <v>78772</v>
+        <v>92616</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>680755</v>
+        <v>680711</v>
       </c>
       <c r="R100" t="n">
-        <v>7087104</v>
+        <v>7087139</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10747,19 +10757,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10774,12 +10774,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10904,7 +10904,7 @@
         <v>126836242</v>
       </c>
       <c r="B102" t="n">
-        <v>91275</v>
+        <v>91276</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126836352</v>
+        <v>126836487</v>
       </c>
       <c r="B105" t="n">
         <v>79014</v>
@@ -11239,10 +11239,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>680753</v>
+        <v>680663</v>
       </c>
       <c r="R105" t="n">
-        <v>7087043</v>
+        <v>7087244</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11305,7 +11305,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126836487</v>
+        <v>126836352</v>
       </c>
       <c r="B106" t="n">
         <v>79014</v>
@@ -11340,10 +11340,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>680663</v>
+        <v>680753</v>
       </c>
       <c r="R106" t="n">
-        <v>7087244</v>
+        <v>7087043</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11608,50 +11608,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126839946</v>
+        <v>126836303</v>
       </c>
       <c r="B109" t="n">
-        <v>56849</v>
+        <v>78773</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>680662</v>
+        <v>680654</v>
       </c>
       <c r="R109" t="n">
-        <v>7087219</v>
+        <v>7087239</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11698,12 +11693,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -11714,32 +11709,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126836230</v>
+        <v>126836507</v>
       </c>
       <c r="B110" t="n">
-        <v>57479</v>
+        <v>92616</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>102976</v>
+        <v>4364</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11749,10 +11744,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>680774</v>
+        <v>680724</v>
       </c>
       <c r="R110" t="n">
-        <v>7087234</v>
+        <v>7087106</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11815,32 +11810,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126836507</v>
+        <v>126836355</v>
       </c>
       <c r="B111" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11850,10 +11845,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>680724</v>
+        <v>680779</v>
       </c>
       <c r="R111" t="n">
-        <v>7087106</v>
+        <v>7087023</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11916,7 +11911,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126836491</v>
+        <v>126836462</v>
       </c>
       <c r="B112" t="n">
         <v>79014</v>
@@ -11951,10 +11946,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>680645</v>
+        <v>680777</v>
       </c>
       <c r="R112" t="n">
-        <v>7087283</v>
+        <v>7087215</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12017,7 +12012,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126836462</v>
+        <v>126836491</v>
       </c>
       <c r="B113" t="n">
         <v>79014</v>
@@ -12052,10 +12047,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>680777</v>
+        <v>680645</v>
       </c>
       <c r="R113" t="n">
-        <v>7087215</v>
+        <v>7087283</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12219,45 +12214,50 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126836355</v>
+        <v>126839946</v>
       </c>
       <c r="B115" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>680779</v>
+        <v>680662</v>
       </c>
       <c r="R115" t="n">
-        <v>7087023</v>
+        <v>7087219</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12304,12 +12304,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12320,32 +12320,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126836303</v>
+        <v>126836230</v>
       </c>
       <c r="B116" t="n">
-        <v>78773</v>
+        <v>57479</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>102976</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12355,10 +12355,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>680654</v>
+        <v>680774</v>
       </c>
       <c r="R116" t="n">
-        <v>7087239</v>
+        <v>7087234</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12522,10 +12522,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126836550</v>
+        <v>126836461</v>
       </c>
       <c r="B118" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12533,21 +12533,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>680667</v>
+        <v>680774</v>
       </c>
       <c r="R118" t="n">
-        <v>7087238</v>
+        <v>7087204</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12623,7 +12623,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126836461</v>
+        <v>126836356</v>
       </c>
       <c r="B119" t="n">
         <v>79014</v>
@@ -12658,10 +12658,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>680774</v>
+        <v>680782</v>
       </c>
       <c r="R119" t="n">
-        <v>7087204</v>
+        <v>7087012</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12724,10 +12724,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126836356</v>
+        <v>126836550</v>
       </c>
       <c r="B120" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12735,21 +12735,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12759,10 +12759,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>680782</v>
+        <v>680667</v>
       </c>
       <c r="R120" t="n">
-        <v>7087012</v>
+        <v>7087238</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12825,10 +12825,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126836354</v>
+        <v>126839970</v>
       </c>
       <c r="B121" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12836,21 +12836,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>680771</v>
+        <v>680772</v>
       </c>
       <c r="R121" t="n">
-        <v>7087030</v>
+        <v>7087124</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12910,12 +12910,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -12926,10 +12926,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126836466</v>
+        <v>126836559</v>
       </c>
       <c r="B122" t="n">
-        <v>79014</v>
+        <v>91733</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12937,21 +12937,16 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12961,10 +12956,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>680756</v>
+        <v>680744</v>
       </c>
       <c r="R122" t="n">
-        <v>7087273</v>
+        <v>7087264</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13005,6 +13000,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13027,10 +13023,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126836479</v>
+        <v>126836545</v>
       </c>
       <c r="B123" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13038,21 +13034,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13062,10 +13058,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>680684</v>
+        <v>680657</v>
       </c>
       <c r="R123" t="n">
-        <v>7087202</v>
+        <v>7087201</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13128,10 +13124,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126836488</v>
+        <v>126825809</v>
       </c>
       <c r="B124" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13139,34 +13135,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>680655</v>
+        <v>680666</v>
       </c>
       <c r="R124" t="n">
-        <v>7087246</v>
+        <v>7087235</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13196,9 +13192,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13213,12 +13219,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13229,7 +13235,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126836478</v>
+        <v>126836354</v>
       </c>
       <c r="B125" t="n">
         <v>79014</v>
@@ -13264,10 +13270,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>680711</v>
+        <v>680771</v>
       </c>
       <c r="R125" t="n">
-        <v>7087181</v>
+        <v>7087030</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13330,10 +13336,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126836545</v>
+        <v>126836478</v>
       </c>
       <c r="B126" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13341,21 +13347,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13365,10 +13371,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>680657</v>
+        <v>680711</v>
       </c>
       <c r="R126" t="n">
-        <v>7087201</v>
+        <v>7087181</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13431,10 +13437,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126825809</v>
+        <v>126836479</v>
       </c>
       <c r="B127" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13442,34 +13448,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>680666</v>
+        <v>680684</v>
       </c>
       <c r="R127" t="n">
-        <v>7087235</v>
+        <v>7087202</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13499,19 +13505,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>10:27</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>10:27</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13526,12 +13522,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13542,10 +13538,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126836559</v>
+        <v>126836488</v>
       </c>
       <c r="B128" t="n">
-        <v>91732</v>
+        <v>79014</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13553,16 +13549,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13572,10 +13573,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>680744</v>
+        <v>680655</v>
       </c>
       <c r="R128" t="n">
-        <v>7087264</v>
+        <v>7087246</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13616,7 +13617,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13639,10 +13639,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126839970</v>
+        <v>126836466</v>
       </c>
       <c r="B129" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13650,21 +13650,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13674,10 +13674,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>680772</v>
+        <v>680756</v>
       </c>
       <c r="R129" t="n">
-        <v>7087124</v>
+        <v>7087273</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13724,12 +13724,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -13740,7 +13740,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126836467</v>
+        <v>126838826</v>
       </c>
       <c r="B130" t="n">
         <v>79014</v>
@@ -13771,14 +13771,14 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>680758</v>
+        <v>680675</v>
       </c>
       <c r="R130" t="n">
-        <v>7087267</v>
+        <v>7087310</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13825,12 +13825,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -13841,7 +13841,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126838827</v>
+        <v>126836467</v>
       </c>
       <c r="B131" t="n">
         <v>79014</v>
@@ -13872,14 +13872,14 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>680665</v>
+        <v>680758</v>
       </c>
       <c r="R131" t="n">
-        <v>7087288</v>
+        <v>7087267</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13926,12 +13926,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -13942,7 +13942,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126838826</v>
+        <v>126838827</v>
       </c>
       <c r="B132" t="n">
         <v>79014</v>
@@ -13977,10 +13977,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>680675</v>
+        <v>680665</v>
       </c>
       <c r="R132" t="n">
-        <v>7087310</v>
+        <v>7087288</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>

--- a/artfynd/A 64499-2023 artfynd.xlsx
+++ b/artfynd/A 64499-2023 artfynd.xlsx
@@ -804,32 +804,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126836504</v>
+        <v>126836523</v>
       </c>
       <c r="B3" t="n">
-        <v>92616</v>
+        <v>78681</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680697</v>
+        <v>680728</v>
       </c>
       <c r="R3" t="n">
-        <v>7087147</v>
+        <v>7087114</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126836484</v>
+        <v>126836552</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680665</v>
+        <v>680642</v>
       </c>
       <c r="R4" t="n">
-        <v>7087214</v>
+        <v>7087273</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,32 +1006,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126836489</v>
+        <v>126836504</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680647</v>
+        <v>680697</v>
       </c>
       <c r="R5" t="n">
-        <v>7087267</v>
+        <v>7087147</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126838823</v>
+        <v>126836484</v>
       </c>
       <c r="B6" t="n">
         <v>79014</v>
@@ -1138,14 +1138,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680767</v>
+        <v>680665</v>
       </c>
       <c r="R6" t="n">
-        <v>7087204</v>
+        <v>7087214</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,12 +1192,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1208,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126825730</v>
+        <v>126836489</v>
       </c>
       <c r="B7" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1219,34 +1219,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680666</v>
+        <v>680647</v>
       </c>
       <c r="R7" t="n">
-        <v>7087235</v>
+        <v>7087267</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,22 +1273,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1303,12 +1293,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1319,10 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126836523</v>
+        <v>126838823</v>
       </c>
       <c r="B8" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1330,34 +1320,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680728</v>
+        <v>680767</v>
       </c>
       <c r="R8" t="n">
-        <v>7087114</v>
+        <v>7087204</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,12 +1394,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1420,32 +1410,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126836552</v>
+        <v>126836506</v>
       </c>
       <c r="B9" t="n">
-        <v>78681</v>
+        <v>92616</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680642</v>
+        <v>680723</v>
       </c>
       <c r="R9" t="n">
-        <v>7087273</v>
+        <v>7087114</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,45 +1511,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126836506</v>
+        <v>126825730</v>
       </c>
       <c r="B10" t="n">
-        <v>92616</v>
+        <v>79632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680723</v>
+        <v>680666</v>
       </c>
       <c r="R10" t="n">
-        <v>7087114</v>
+        <v>7087235</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,12 +1576,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1606,12 +1606,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -4788,10 +4788,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126839937</v>
+        <v>126836516</v>
       </c>
       <c r="B42" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4799,21 +4799,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>680761</v>
+        <v>680654</v>
       </c>
       <c r="R42" t="n">
-        <v>7087124</v>
+        <v>7087188</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4873,12 +4873,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4889,10 +4889,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126836516</v>
+        <v>126836483</v>
       </c>
       <c r="B43" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4900,21 +4900,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>680654</v>
+        <v>680673</v>
       </c>
       <c r="R43" t="n">
-        <v>7087188</v>
+        <v>7087210</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4990,7 +4990,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126836483</v>
+        <v>126839994</v>
       </c>
       <c r="B44" t="n">
         <v>79014</v>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>680673</v>
+        <v>680650</v>
       </c>
       <c r="R44" t="n">
-        <v>7087210</v>
+        <v>7087238</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5075,12 +5075,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5091,10 +5091,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126839994</v>
+        <v>126839937</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5102,21 +5102,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>680650</v>
+        <v>680761</v>
       </c>
       <c r="R45" t="n">
-        <v>7087238</v>
+        <v>7087124</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5192,10 +5192,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126838822</v>
+        <v>126836548</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5203,34 +5203,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>680783</v>
+        <v>680662</v>
       </c>
       <c r="R46" t="n">
-        <v>7087170</v>
+        <v>7087231</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5277,12 +5277,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5293,10 +5293,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126837223</v>
+        <v>126836517</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5304,21 +5304,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5328,10 +5328,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>680772</v>
+        <v>680662</v>
       </c>
       <c r="R47" t="n">
-        <v>7087024</v>
+        <v>7087179</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5378,12 +5378,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5394,7 +5394,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126836338</v>
+        <v>126838822</v>
       </c>
       <c r="B48" t="n">
         <v>79014</v>
@@ -5425,14 +5425,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>680648</v>
+        <v>680783</v>
       </c>
       <c r="R48" t="n">
-        <v>7087260</v>
+        <v>7087170</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5479,12 +5479,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5495,7 +5495,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126839998</v>
+        <v>126837223</v>
       </c>
       <c r="B49" t="n">
         <v>79014</v>
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>680673</v>
+        <v>680772</v>
       </c>
       <c r="R49" t="n">
-        <v>7087211</v>
+        <v>7087024</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5580,12 +5580,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5596,32 +5596,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126839976</v>
+        <v>126836338</v>
       </c>
       <c r="B50" t="n">
-        <v>58027</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>680693</v>
+        <v>680648</v>
       </c>
       <c r="R50" t="n">
-        <v>7087162</v>
+        <v>7087260</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5681,12 +5681,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5697,10 +5697,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126836548</v>
+        <v>126839998</v>
       </c>
       <c r="B51" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5708,21 +5708,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>680662</v>
+        <v>680673</v>
       </c>
       <c r="R51" t="n">
-        <v>7087231</v>
+        <v>7087211</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5782,12 +5782,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5798,10 +5798,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126836517</v>
+        <v>126836198</v>
       </c>
       <c r="B52" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5809,21 +5809,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5833,10 +5833,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>680662</v>
+        <v>680721</v>
       </c>
       <c r="R52" t="n">
-        <v>7087179</v>
+        <v>7087133</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5899,32 +5899,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126836198</v>
+        <v>126839976</v>
       </c>
       <c r="B53" t="n">
-        <v>79632</v>
+        <v>58027</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5934,10 +5934,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>680721</v>
+        <v>680693</v>
       </c>
       <c r="R53" t="n">
-        <v>7087133</v>
+        <v>7087162</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5984,12 +5984,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -7029,10 +7029,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126836515</v>
+        <v>126836302</v>
       </c>
       <c r="B64" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7040,21 +7040,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>680644</v>
+        <v>680677</v>
       </c>
       <c r="R64" t="n">
-        <v>7087195</v>
+        <v>7087201</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7130,7 +7130,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126836542</v>
+        <v>126836515</v>
       </c>
       <c r="B65" t="n">
         <v>78681</v>
@@ -7165,10 +7165,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>680710</v>
+        <v>680644</v>
       </c>
       <c r="R65" t="n">
-        <v>7087232</v>
+        <v>7087195</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7231,10 +7231,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126836482</v>
+        <v>126836542</v>
       </c>
       <c r="B66" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7242,21 +7242,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7266,10 +7266,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>680673</v>
+        <v>680710</v>
       </c>
       <c r="R66" t="n">
-        <v>7087202</v>
+        <v>7087232</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7332,45 +7332,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126837038</v>
+        <v>126836482</v>
       </c>
       <c r="B67" t="n">
-        <v>91291</v>
+        <v>79014</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>680783</v>
+        <v>680673</v>
       </c>
       <c r="R67" t="n">
-        <v>7087069</v>
+        <v>7087202</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7417,12 +7417,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7736,45 +7736,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126836302</v>
+        <v>126837038</v>
       </c>
       <c r="B71" t="n">
-        <v>78773</v>
+        <v>91291</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>680677</v>
+        <v>680783</v>
       </c>
       <c r="R71" t="n">
-        <v>7087201</v>
+        <v>7087069</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7821,12 +7821,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -10790,10 +10790,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126836259</v>
+        <v>126836242</v>
       </c>
       <c r="B101" t="n">
-        <v>57657</v>
+        <v>91276</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10801,39 +10801,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>680665</v>
+        <v>680744</v>
       </c>
       <c r="R101" t="n">
-        <v>7087214</v>
+        <v>7087264</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10866,11 +10861,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10901,10 +10891,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126836242</v>
+        <v>126837236</v>
       </c>
       <c r="B102" t="n">
-        <v>91276</v>
+        <v>78681</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10912,21 +10902,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>112</v>
+        <v>353</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10936,10 +10926,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>680744</v>
+        <v>680673</v>
       </c>
       <c r="R102" t="n">
-        <v>7087264</v>
+        <v>7087186</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10986,12 +10976,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11002,7 +10992,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126837236</v>
+        <v>126836522</v>
       </c>
       <c r="B103" t="n">
         <v>78681</v>
@@ -11037,10 +11027,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>680673</v>
+        <v>680726</v>
       </c>
       <c r="R103" t="n">
-        <v>7087186</v>
+        <v>7087132</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11087,12 +11077,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11103,10 +11093,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126836522</v>
+        <v>126836487</v>
       </c>
       <c r="B104" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11114,21 +11104,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11138,10 +11128,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>680726</v>
+        <v>680663</v>
       </c>
       <c r="R104" t="n">
-        <v>7087132</v>
+        <v>7087244</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11204,10 +11194,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126836487</v>
+        <v>126836259</v>
       </c>
       <c r="B105" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11215,34 +11205,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>680663</v>
+        <v>680665</v>
       </c>
       <c r="R105" t="n">
-        <v>7087244</v>
+        <v>7087214</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11275,6 +11270,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11608,32 +11608,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126836303</v>
+        <v>126836507</v>
       </c>
       <c r="B109" t="n">
-        <v>78773</v>
+        <v>92616</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11643,10 +11643,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>680654</v>
+        <v>680724</v>
       </c>
       <c r="R109" t="n">
-        <v>7087239</v>
+        <v>7087106</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11709,32 +11709,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126836507</v>
+        <v>126836462</v>
       </c>
       <c r="B110" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11744,10 +11744,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>680724</v>
+        <v>680777</v>
       </c>
       <c r="R110" t="n">
-        <v>7087106</v>
+        <v>7087215</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11810,45 +11810,50 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126836355</v>
+        <v>126839946</v>
       </c>
       <c r="B111" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>680779</v>
+        <v>680662</v>
       </c>
       <c r="R111" t="n">
-        <v>7087023</v>
+        <v>7087219</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11895,12 +11900,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -11911,10 +11916,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126836462</v>
+        <v>126836303</v>
       </c>
       <c r="B112" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11922,21 +11927,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11946,10 +11951,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>680777</v>
+        <v>680654</v>
       </c>
       <c r="R112" t="n">
-        <v>7087215</v>
+        <v>7087239</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12012,7 +12017,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126836491</v>
+        <v>126836355</v>
       </c>
       <c r="B113" t="n">
         <v>79014</v>
@@ -12047,10 +12052,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>680645</v>
+        <v>680779</v>
       </c>
       <c r="R113" t="n">
-        <v>7087283</v>
+        <v>7087023</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12113,7 +12118,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126836485</v>
+        <v>126836491</v>
       </c>
       <c r="B114" t="n">
         <v>79014</v>
@@ -12148,10 +12153,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>680660</v>
+        <v>680645</v>
       </c>
       <c r="R114" t="n">
-        <v>7087229</v>
+        <v>7087283</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12214,50 +12219,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126839946</v>
+        <v>126836485</v>
       </c>
       <c r="B115" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>680662</v>
+        <v>680660</v>
       </c>
       <c r="R115" t="n">
-        <v>7087219</v>
+        <v>7087229</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12304,12 +12304,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12421,10 +12421,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126836476</v>
+        <v>126836550</v>
       </c>
       <c r="B117" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12432,21 +12432,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12456,10 +12456,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>680712</v>
+        <v>680667</v>
       </c>
       <c r="R117" t="n">
-        <v>7087209</v>
+        <v>7087238</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12522,7 +12522,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126836461</v>
+        <v>126836476</v>
       </c>
       <c r="B118" t="n">
         <v>79014</v>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>680774</v>
+        <v>680712</v>
       </c>
       <c r="R118" t="n">
-        <v>7087204</v>
+        <v>7087209</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12623,7 +12623,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126836356</v>
+        <v>126836461</v>
       </c>
       <c r="B119" t="n">
         <v>79014</v>
@@ -12658,10 +12658,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>680782</v>
+        <v>680774</v>
       </c>
       <c r="R119" t="n">
-        <v>7087012</v>
+        <v>7087204</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12724,10 +12724,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126836550</v>
+        <v>126836356</v>
       </c>
       <c r="B120" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12735,21 +12735,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12759,10 +12759,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>680667</v>
+        <v>680782</v>
       </c>
       <c r="R120" t="n">
-        <v>7087238</v>
+        <v>7087012</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12825,10 +12825,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126839970</v>
+        <v>126836545</v>
       </c>
       <c r="B121" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12836,21 +12836,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>680772</v>
+        <v>680657</v>
       </c>
       <c r="R121" t="n">
-        <v>7087124</v>
+        <v>7087201</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12910,12 +12910,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -12926,10 +12926,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126836559</v>
+        <v>126825809</v>
       </c>
       <c r="B122" t="n">
-        <v>91733</v>
+        <v>78681</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12937,29 +12937,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6040186</v>
+        <v>353</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>680744</v>
+        <v>680666</v>
       </c>
       <c r="R122" t="n">
-        <v>7087264</v>
+        <v>7087235</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12989,30 +12994,39 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -13023,10 +13037,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126836545</v>
+        <v>126836479</v>
       </c>
       <c r="B123" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13034,21 +13048,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13058,10 +13072,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>680657</v>
+        <v>680684</v>
       </c>
       <c r="R123" t="n">
-        <v>7087201</v>
+        <v>7087202</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13124,10 +13138,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126825809</v>
+        <v>126836354</v>
       </c>
       <c r="B124" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13135,34 +13149,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>680666</v>
+        <v>680771</v>
       </c>
       <c r="R124" t="n">
-        <v>7087235</v>
+        <v>7087030</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13192,19 +13206,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>10:27</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>10:27</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13219,12 +13223,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13235,7 +13239,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126836354</v>
+        <v>126836488</v>
       </c>
       <c r="B125" t="n">
         <v>79014</v>
@@ -13270,10 +13274,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>680771</v>
+        <v>680655</v>
       </c>
       <c r="R125" t="n">
-        <v>7087030</v>
+        <v>7087246</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13336,7 +13340,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126836478</v>
+        <v>126836466</v>
       </c>
       <c r="B126" t="n">
         <v>79014</v>
@@ -13371,10 +13375,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>680711</v>
+        <v>680756</v>
       </c>
       <c r="R126" t="n">
-        <v>7087181</v>
+        <v>7087273</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13437,7 +13441,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126836479</v>
+        <v>126836478</v>
       </c>
       <c r="B127" t="n">
         <v>79014</v>
@@ -13472,10 +13476,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>680684</v>
+        <v>680711</v>
       </c>
       <c r="R127" t="n">
-        <v>7087202</v>
+        <v>7087181</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13538,10 +13542,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126836488</v>
+        <v>126839970</v>
       </c>
       <c r="B128" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13549,21 +13553,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13573,10 +13577,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>680655</v>
+        <v>680772</v>
       </c>
       <c r="R128" t="n">
-        <v>7087246</v>
+        <v>7087124</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13623,12 +13627,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -13639,10 +13643,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126836466</v>
+        <v>126836559</v>
       </c>
       <c r="B129" t="n">
-        <v>79014</v>
+        <v>91733</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13650,21 +13654,16 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13674,10 +13673,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>680756</v>
+        <v>680744</v>
       </c>
       <c r="R129" t="n">
-        <v>7087273</v>
+        <v>7087264</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13718,6 +13717,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64499-2023 artfynd.xlsx
+++ b/artfynd/A 64499-2023 artfynd.xlsx
@@ -804,32 +804,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126836523</v>
+        <v>126836506</v>
       </c>
       <c r="B3" t="n">
-        <v>78681</v>
+        <v>92616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680728</v>
+        <v>680723</v>
       </c>
       <c r="R3" t="n">
         <v>7087114</v>
@@ -905,32 +905,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126836552</v>
+        <v>126836504</v>
       </c>
       <c r="B4" t="n">
-        <v>78681</v>
+        <v>92616</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680642</v>
+        <v>680697</v>
       </c>
       <c r="R4" t="n">
-        <v>7087273</v>
+        <v>7087147</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,32 +1006,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126836504</v>
+        <v>126836552</v>
       </c>
       <c r="B5" t="n">
-        <v>92616</v>
+        <v>78681</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680697</v>
+        <v>680642</v>
       </c>
       <c r="R5" t="n">
-        <v>7087147</v>
+        <v>7087273</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126836484</v>
+        <v>126836523</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,21 +1118,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680665</v>
+        <v>680728</v>
       </c>
       <c r="R6" t="n">
-        <v>7087214</v>
+        <v>7087114</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126836489</v>
+        <v>126839973</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1219,21 +1219,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680647</v>
+        <v>680751</v>
       </c>
       <c r="R7" t="n">
-        <v>7087267</v>
+        <v>7087100</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,12 +1293,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1309,10 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126838823</v>
+        <v>126825730</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1320,34 +1320,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680767</v>
+        <v>680666</v>
       </c>
       <c r="R8" t="n">
-        <v>7087204</v>
+        <v>7087235</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,12 +1374,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,12 +1404,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1410,32 +1420,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126836506</v>
+        <v>126836489</v>
       </c>
       <c r="B9" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1445,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680723</v>
+        <v>680647</v>
       </c>
       <c r="R9" t="n">
-        <v>7087114</v>
+        <v>7087267</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126825730</v>
+        <v>126836484</v>
       </c>
       <c r="B10" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,34 +1532,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680666</v>
+        <v>680665</v>
       </c>
       <c r="R10" t="n">
-        <v>7087235</v>
+        <v>7087214</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,22 +1586,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1606,12 +1606,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1622,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126839973</v>
+        <v>126838823</v>
       </c>
       <c r="B11" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,34 +1633,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680751</v>
+        <v>680767</v>
       </c>
       <c r="R11" t="n">
-        <v>7087100</v>
+        <v>7087204</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,12 +1707,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1824,10 +1824,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126839974</v>
+        <v>126840004</v>
       </c>
       <c r="B13" t="n">
-        <v>78772</v>
+        <v>78681</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1835,21 +1835,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680751</v>
+        <v>680639</v>
       </c>
       <c r="R13" t="n">
-        <v>7087100</v>
+        <v>7087277</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,10 +1925,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126836520</v>
+        <v>126837190</v>
       </c>
       <c r="B14" t="n">
-        <v>78681</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,34 +1936,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680716</v>
+        <v>680778</v>
       </c>
       <c r="R14" t="n">
-        <v>7087135</v>
+        <v>7087007</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,6 +2006,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2010,12 +2023,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2026,10 +2039,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126840004</v>
+        <v>126839974</v>
       </c>
       <c r="B15" t="n">
-        <v>78681</v>
+        <v>78772</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,21 +2050,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680639</v>
+        <v>680751</v>
       </c>
       <c r="R15" t="n">
-        <v>7087277</v>
+        <v>7087100</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,10 +2140,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126836546</v>
+        <v>126836555</v>
       </c>
       <c r="B16" t="n">
-        <v>78681</v>
+        <v>78420</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,21 +2151,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,7 +2241,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126837233</v>
+        <v>126836546</v>
       </c>
       <c r="B17" t="n">
         <v>78681</v>
@@ -2263,10 +2276,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680698</v>
+        <v>680660</v>
       </c>
       <c r="R17" t="n">
-        <v>7087108</v>
+        <v>7087210</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2313,12 +2326,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2329,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126836555</v>
+        <v>126836520</v>
       </c>
       <c r="B18" t="n">
-        <v>78420</v>
+        <v>78681</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2340,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2364,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680660</v>
+        <v>680716</v>
       </c>
       <c r="R18" t="n">
-        <v>7087210</v>
+        <v>7087135</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2430,10 +2443,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126837190</v>
+        <v>126837233</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>78681</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2441,42 +2454,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680778</v>
+        <v>680698</v>
       </c>
       <c r="R19" t="n">
-        <v>7087007</v>
+        <v>7087108</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2509,11 +2514,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2544,7 +2544,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126837085</v>
+        <v>126836351</v>
       </c>
       <c r="B20" t="n">
         <v>79014</v>
@@ -2575,14 +2575,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680698</v>
+        <v>680723</v>
       </c>
       <c r="R20" t="n">
-        <v>7087214</v>
+        <v>7087114</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2629,12 +2629,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2645,7 +2645,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126836351</v>
+        <v>126837085</v>
       </c>
       <c r="B21" t="n">
         <v>79014</v>
@@ -2676,14 +2676,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680723</v>
+        <v>680698</v>
       </c>
       <c r="R21" t="n">
-        <v>7087114</v>
+        <v>7087214</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,12 +2730,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2847,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126836547</v>
+        <v>126837232</v>
       </c>
       <c r="B23" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,21 +2858,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680665</v>
+        <v>680637</v>
       </c>
       <c r="R23" t="n">
-        <v>7087202</v>
+        <v>7087243</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2932,12 +2932,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2948,10 +2948,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126837232</v>
+        <v>126836547</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,21 +2959,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>680637</v>
+        <v>680665</v>
       </c>
       <c r="R24" t="n">
-        <v>7087243</v>
+        <v>7087202</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3033,12 +3033,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3049,10 +3049,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126836551</v>
+        <v>126838821</v>
       </c>
       <c r="B25" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3060,34 +3060,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680654</v>
+        <v>680775</v>
       </c>
       <c r="R25" t="n">
-        <v>7087239</v>
+        <v>7087121</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3134,12 +3134,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126840000</v>
+        <v>126836551</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3262,21 +3262,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680643</v>
+        <v>680654</v>
       </c>
       <c r="R27" t="n">
-        <v>7087277</v>
+        <v>7087239</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,12 +3336,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3352,45 +3352,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126839989</v>
+        <v>126837193</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680774</v>
+        <v>680696</v>
       </c>
       <c r="R28" t="n">
-        <v>7087124</v>
+        <v>7087170</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3425,6 +3433,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Blindtarmstömmning</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3437,12 +3450,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3453,7 +3466,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126838821</v>
+        <v>126838825</v>
       </c>
       <c r="B29" t="n">
         <v>79014</v>
@@ -3488,10 +3501,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680775</v>
+        <v>680759</v>
       </c>
       <c r="R29" t="n">
-        <v>7087121</v>
+        <v>7087282</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3554,7 +3567,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126838825</v>
+        <v>126837228</v>
       </c>
       <c r="B30" t="n">
         <v>79014</v>
@@ -3585,14 +3598,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680759</v>
+        <v>680658</v>
       </c>
       <c r="R30" t="n">
-        <v>7087282</v>
+        <v>7087213</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3639,12 +3652,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3655,10 +3668,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126837228</v>
+        <v>126839971</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3666,21 +3679,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3690,10 +3703,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680658</v>
+        <v>680772</v>
       </c>
       <c r="R31" t="n">
-        <v>7087213</v>
+        <v>7087124</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3740,12 +3753,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3756,10 +3769,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126839971</v>
+        <v>126840000</v>
       </c>
       <c r="B32" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3767,21 +3780,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3791,10 +3804,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680772</v>
+        <v>680643</v>
       </c>
       <c r="R32" t="n">
-        <v>7087124</v>
+        <v>7087277</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3857,53 +3870,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126837193</v>
+        <v>126839989</v>
       </c>
       <c r="B33" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680696</v>
+        <v>680774</v>
       </c>
       <c r="R33" t="n">
-        <v>7087170</v>
+        <v>7087124</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3938,11 +3943,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Blindtarmstömmning</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -3955,12 +3955,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3971,10 +3971,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126836543</v>
+        <v>126839997</v>
       </c>
       <c r="B34" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3982,21 +3982,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680708</v>
+        <v>680676</v>
       </c>
       <c r="R34" t="n">
-        <v>7087204</v>
+        <v>7087207</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4056,12 +4056,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4072,53 +4072,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126837192</v>
+        <v>126837084</v>
       </c>
       <c r="B35" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>680665</v>
+        <v>680731</v>
       </c>
       <c r="R35" t="n">
-        <v>7087191</v>
+        <v>7087201</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4153,11 +4145,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4170,12 +4157,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4186,10 +4173,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126838798</v>
+        <v>126836460</v>
       </c>
       <c r="B36" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4197,34 +4184,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>680781</v>
+        <v>680779</v>
       </c>
       <c r="R36" t="n">
-        <v>7087170</v>
+        <v>7087200</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4271,19 +4258,23 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126837084</v>
+        <v>126836463</v>
       </c>
       <c r="B37" t="n">
         <v>79014</v>
@@ -4314,14 +4305,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>680731</v>
+        <v>680773</v>
       </c>
       <c r="R37" t="n">
-        <v>7087201</v>
+        <v>7087233</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4368,12 +4359,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4384,10 +4375,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126839997</v>
+        <v>126836543</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4395,21 +4386,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4419,10 +4410,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>680676</v>
+        <v>680708</v>
       </c>
       <c r="R38" t="n">
-        <v>7087207</v>
+        <v>7087204</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4469,12 +4460,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4485,7 +4476,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126836460</v>
+        <v>126836477</v>
       </c>
       <c r="B39" t="n">
         <v>79014</v>
@@ -4520,10 +4511,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>680779</v>
+        <v>680709</v>
       </c>
       <c r="R39" t="n">
-        <v>7087200</v>
+        <v>7087204</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4586,45 +4577,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126836477</v>
+        <v>126837192</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>680709</v>
+        <v>680665</v>
       </c>
       <c r="R40" t="n">
-        <v>7087204</v>
+        <v>7087191</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4659,6 +4658,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4671,12 +4675,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4687,10 +4691,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126836463</v>
+        <v>126838798</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4698,34 +4702,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>680773</v>
+        <v>680781</v>
       </c>
       <c r="R41" t="n">
-        <v>7087233</v>
+        <v>7087170</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4772,26 +4776,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126836516</v>
+        <v>126839994</v>
       </c>
       <c r="B42" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4799,21 +4799,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>680654</v>
+        <v>680650</v>
       </c>
       <c r="R42" t="n">
-        <v>7087188</v>
+        <v>7087238</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4873,12 +4873,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4990,10 +4990,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126839994</v>
+        <v>126839937</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5001,21 +5001,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>680650</v>
+        <v>680761</v>
       </c>
       <c r="R44" t="n">
-        <v>7087238</v>
+        <v>7087124</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5091,10 +5091,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126839937</v>
+        <v>126836516</v>
       </c>
       <c r="B45" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5102,21 +5102,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>680761</v>
+        <v>680654</v>
       </c>
       <c r="R45" t="n">
-        <v>7087124</v>
+        <v>7087188</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5176,12 +5176,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5192,7 +5192,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126836548</v>
+        <v>126836517</v>
       </c>
       <c r="B46" t="n">
         <v>78681</v>
@@ -5230,7 +5230,7 @@
         <v>680662</v>
       </c>
       <c r="R46" t="n">
-        <v>7087231</v>
+        <v>7087179</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5293,7 +5293,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126836517</v>
+        <v>126836548</v>
       </c>
       <c r="B47" t="n">
         <v>78681</v>
@@ -5331,7 +5331,7 @@
         <v>680662</v>
       </c>
       <c r="R47" t="n">
-        <v>7087179</v>
+        <v>7087231</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5394,45 +5394,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126838822</v>
+        <v>126839976</v>
       </c>
       <c r="B48" t="n">
-        <v>79014</v>
+        <v>58027</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>680783</v>
+        <v>680693</v>
       </c>
       <c r="R48" t="n">
-        <v>7087170</v>
+        <v>7087162</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5479,12 +5479,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5495,7 +5495,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126837223</v>
+        <v>126838822</v>
       </c>
       <c r="B49" t="n">
         <v>79014</v>
@@ -5526,14 +5526,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>680772</v>
+        <v>680783</v>
       </c>
       <c r="R49" t="n">
-        <v>7087024</v>
+        <v>7087170</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5580,12 +5580,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5697,10 +5697,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126839998</v>
+        <v>126836198</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5708,21 +5708,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>680673</v>
+        <v>680721</v>
       </c>
       <c r="R51" t="n">
-        <v>7087211</v>
+        <v>7087133</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5782,12 +5782,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5798,10 +5798,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126836198</v>
+        <v>126839998</v>
       </c>
       <c r="B52" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5809,21 +5809,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5833,10 +5833,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>680721</v>
+        <v>680673</v>
       </c>
       <c r="R52" t="n">
-        <v>7087133</v>
+        <v>7087211</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5883,12 +5883,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5899,32 +5899,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126839976</v>
+        <v>126837223</v>
       </c>
       <c r="B53" t="n">
-        <v>58027</v>
+        <v>79014</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5934,10 +5934,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>680693</v>
+        <v>680772</v>
       </c>
       <c r="R53" t="n">
-        <v>7087162</v>
+        <v>7087024</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5984,12 +5984,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6000,10 +6000,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126837234</v>
+        <v>126836490</v>
       </c>
       <c r="B54" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6011,21 +6011,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6035,10 +6035,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>680694</v>
+        <v>680645</v>
       </c>
       <c r="R54" t="n">
-        <v>7087158</v>
+        <v>7087280</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6085,12 +6085,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6101,10 +6101,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126836541</v>
+        <v>126837225</v>
       </c>
       <c r="B55" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6112,21 +6112,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6136,10 +6136,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>680708</v>
+        <v>680729</v>
       </c>
       <c r="R55" t="n">
-        <v>7087251</v>
+        <v>7087081</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6186,12 +6186,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6202,10 +6202,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126836519</v>
+        <v>126836469</v>
       </c>
       <c r="B56" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6213,21 +6213,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6237,10 +6237,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>680693</v>
+        <v>680728</v>
       </c>
       <c r="R56" t="n">
-        <v>7087159</v>
+        <v>7087278</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6303,10 +6303,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126836486</v>
+        <v>126840919</v>
       </c>
       <c r="B57" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6314,34 +6314,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>680663</v>
+        <v>680640</v>
       </c>
       <c r="R57" t="n">
-        <v>7087231</v>
+        <v>7087261</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6371,29 +6374,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6404,7 +6418,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126836469</v>
+        <v>126839996</v>
       </c>
       <c r="B58" t="n">
         <v>79014</v>
@@ -6439,10 +6453,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>680728</v>
+        <v>680745</v>
       </c>
       <c r="R58" t="n">
-        <v>7087278</v>
+        <v>7087170</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6489,12 +6503,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6505,7 +6519,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126836490</v>
+        <v>126836486</v>
       </c>
       <c r="B59" t="n">
         <v>79014</v>
@@ -6540,10 +6554,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>680645</v>
+        <v>680663</v>
       </c>
       <c r="R59" t="n">
-        <v>7087280</v>
+        <v>7087231</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6606,10 +6620,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126839996</v>
+        <v>126836519</v>
       </c>
       <c r="B60" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6617,21 +6631,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6641,10 +6655,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>680745</v>
+        <v>680693</v>
       </c>
       <c r="R60" t="n">
-        <v>7087170</v>
+        <v>7087159</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6691,12 +6705,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6707,10 +6721,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126837225</v>
+        <v>126837234</v>
       </c>
       <c r="B61" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6718,21 +6732,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6742,10 +6756,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>680729</v>
+        <v>680694</v>
       </c>
       <c r="R61" t="n">
-        <v>7087081</v>
+        <v>7087158</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6808,10 +6822,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126840919</v>
+        <v>126836541</v>
       </c>
       <c r="B62" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6819,37 +6833,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>680640</v>
+        <v>680708</v>
       </c>
       <c r="R62" t="n">
-        <v>7087261</v>
+        <v>7087251</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6879,40 +6890,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>10:17</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>10:17</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7029,10 +7029,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126836302</v>
+        <v>126836515</v>
       </c>
       <c r="B64" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7040,21 +7040,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>680677</v>
+        <v>680644</v>
       </c>
       <c r="R64" t="n">
-        <v>7087201</v>
+        <v>7087195</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7130,10 +7130,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126836515</v>
+        <v>126836302</v>
       </c>
       <c r="B65" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7141,21 +7141,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7165,10 +7165,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>680644</v>
+        <v>680677</v>
       </c>
       <c r="R65" t="n">
-        <v>7087195</v>
+        <v>7087201</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7231,10 +7231,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126836542</v>
+        <v>126839938</v>
       </c>
       <c r="B66" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7242,21 +7242,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7266,10 +7266,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>680710</v>
+        <v>680652</v>
       </c>
       <c r="R66" t="n">
-        <v>7087232</v>
+        <v>7087271</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7316,12 +7316,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7332,10 +7332,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126836482</v>
+        <v>126838804</v>
       </c>
       <c r="B67" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7343,34 +7343,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>680673</v>
+        <v>680765</v>
       </c>
       <c r="R67" t="n">
-        <v>7087202</v>
+        <v>7087124</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7417,12 +7417,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7534,10 +7534,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126839938</v>
+        <v>126836482</v>
       </c>
       <c r="B69" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7545,21 +7545,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>680652</v>
+        <v>680673</v>
       </c>
       <c r="R69" t="n">
-        <v>7087271</v>
+        <v>7087202</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7619,12 +7619,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7635,45 +7635,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126838804</v>
+        <v>126837038</v>
       </c>
       <c r="B70" t="n">
-        <v>78772</v>
+        <v>91291</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>680765</v>
+        <v>680783</v>
       </c>
       <c r="R70" t="n">
-        <v>7087124</v>
+        <v>7087069</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7720,12 +7720,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7736,45 +7736,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126837038</v>
+        <v>126836542</v>
       </c>
       <c r="B71" t="n">
-        <v>91291</v>
+        <v>78681</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>680783</v>
+        <v>680710</v>
       </c>
       <c r="R71" t="n">
-        <v>7087069</v>
+        <v>7087232</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7821,12 +7821,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7837,10 +7837,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126836524</v>
+        <v>126837052</v>
       </c>
       <c r="B72" t="n">
-        <v>78681</v>
+        <v>57817</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7848,34 +7848,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>680720</v>
+        <v>680740</v>
       </c>
       <c r="R72" t="n">
-        <v>7087100</v>
+        <v>7087222</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7922,12 +7922,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7938,10 +7938,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126836544</v>
+        <v>126837069</v>
       </c>
       <c r="B73" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7949,34 +7949,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>680681</v>
+        <v>680673</v>
       </c>
       <c r="R73" t="n">
-        <v>7087195</v>
+        <v>7087276</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8023,12 +8023,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8140,10 +8140,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126836464</v>
+        <v>126836524</v>
       </c>
       <c r="B75" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8151,21 +8151,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>680772</v>
+        <v>680720</v>
       </c>
       <c r="R75" t="n">
-        <v>7087252</v>
+        <v>7087100</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8241,10 +8241,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126836475</v>
+        <v>126836544</v>
       </c>
       <c r="B76" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8252,21 +8252,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8276,10 +8276,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>680708</v>
+        <v>680681</v>
       </c>
       <c r="R76" t="n">
-        <v>7087220</v>
+        <v>7087195</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8342,7 +8342,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126839999</v>
+        <v>126836475</v>
       </c>
       <c r="B77" t="n">
         <v>79014</v>
@@ -8377,10 +8377,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>680651</v>
+        <v>680708</v>
       </c>
       <c r="R77" t="n">
-        <v>7087231</v>
+        <v>7087220</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8427,12 +8427,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8443,7 +8443,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126836473</v>
+        <v>126836336</v>
       </c>
       <c r="B78" t="n">
         <v>79014</v>
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>680710</v>
+        <v>680653</v>
       </c>
       <c r="R78" t="n">
-        <v>7087232</v>
+        <v>7087252</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8544,7 +8544,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126836336</v>
+        <v>126836464</v>
       </c>
       <c r="B79" t="n">
         <v>79014</v>
@@ -8579,7 +8579,7 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>680653</v>
+        <v>680772</v>
       </c>
       <c r="R79" t="n">
         <v>7087252</v>
@@ -8645,10 +8645,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126837052</v>
+        <v>126836473</v>
       </c>
       <c r="B80" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8656,34 +8656,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>680740</v>
+        <v>680710</v>
       </c>
       <c r="R80" t="n">
-        <v>7087222</v>
+        <v>7087232</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8730,12 +8730,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8746,10 +8746,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126837069</v>
+        <v>126839999</v>
       </c>
       <c r="B81" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8757,34 +8757,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>680673</v>
+        <v>680651</v>
       </c>
       <c r="R81" t="n">
-        <v>7087276</v>
+        <v>7087231</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8831,12 +8831,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8847,7 +8847,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126836470</v>
+        <v>126836472</v>
       </c>
       <c r="B82" t="n">
         <v>79014</v>
@@ -8882,10 +8882,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>680718</v>
+        <v>680714</v>
       </c>
       <c r="R82" t="n">
-        <v>7087288</v>
+        <v>7087268</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8948,10 +8948,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126836468</v>
+        <v>126837053</v>
       </c>
       <c r="B83" t="n">
-        <v>79014</v>
+        <v>91346</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8959,34 +8959,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>680752</v>
+        <v>680770</v>
       </c>
       <c r="R83" t="n">
-        <v>7087262</v>
+        <v>7087092</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9033,12 +9033,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9049,7 +9049,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126836472</v>
+        <v>126836470</v>
       </c>
       <c r="B84" t="n">
         <v>79014</v>
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>680714</v>
+        <v>680718</v>
       </c>
       <c r="R84" t="n">
-        <v>7087268</v>
+        <v>7087288</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9150,10 +9150,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126837053</v>
+        <v>126836468</v>
       </c>
       <c r="B85" t="n">
-        <v>91346</v>
+        <v>79014</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9161,34 +9161,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>680770</v>
+        <v>680752</v>
       </c>
       <c r="R85" t="n">
-        <v>7087092</v>
+        <v>7087262</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9235,12 +9235,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9251,10 +9251,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126837231</v>
+        <v>126836309</v>
       </c>
       <c r="B86" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9262,21 +9262,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9286,10 +9286,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>680642</v>
+        <v>680720</v>
       </c>
       <c r="R86" t="n">
-        <v>7087222</v>
+        <v>7087133</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9336,12 +9336,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9352,10 +9352,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126839992</v>
+        <v>126836199</v>
       </c>
       <c r="B87" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9363,21 +9363,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9387,10 +9387,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>680767</v>
+        <v>680719</v>
       </c>
       <c r="R87" t="n">
-        <v>7087114</v>
+        <v>7087133</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9437,12 +9437,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9453,10 +9453,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126837082</v>
+        <v>126840864</v>
       </c>
       <c r="B88" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9464,34 +9464,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>680771</v>
+        <v>680671</v>
       </c>
       <c r="R88" t="n">
-        <v>7087091</v>
+        <v>7087236</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9521,29 +9524,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9554,7 +9568,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126836480</v>
+        <v>126836481</v>
       </c>
       <c r="B89" t="n">
         <v>79014</v>
@@ -9589,10 +9603,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>680660</v>
+        <v>680670</v>
       </c>
       <c r="R89" t="n">
-        <v>7087210</v>
+        <v>7087199</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9655,7 +9669,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126836481</v>
+        <v>126837231</v>
       </c>
       <c r="B90" t="n">
         <v>79014</v>
@@ -9690,10 +9704,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>680670</v>
+        <v>680642</v>
       </c>
       <c r="R90" t="n">
-        <v>7087199</v>
+        <v>7087222</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9740,12 +9754,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9756,7 +9770,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126836357</v>
+        <v>126836480</v>
       </c>
       <c r="B91" t="n">
         <v>79014</v>
@@ -9791,10 +9805,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>680784</v>
+        <v>680660</v>
       </c>
       <c r="R91" t="n">
-        <v>7087010</v>
+        <v>7087210</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9857,32 +9871,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126836503</v>
+        <v>126836357</v>
       </c>
       <c r="B92" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9892,10 +9906,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>680682</v>
+        <v>680784</v>
       </c>
       <c r="R92" t="n">
-        <v>7087164</v>
+        <v>7087010</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9958,10 +9972,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126836199</v>
+        <v>126837082</v>
       </c>
       <c r="B93" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9969,34 +9983,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>680719</v>
+        <v>680771</v>
       </c>
       <c r="R93" t="n">
-        <v>7087133</v>
+        <v>7087091</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10043,12 +10057,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10059,10 +10073,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126840864</v>
+        <v>126839992</v>
       </c>
       <c r="B94" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10070,37 +10084,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>680671</v>
+        <v>680767</v>
       </c>
       <c r="R94" t="n">
-        <v>7087236</v>
+        <v>7087114</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10130,40 +10141,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10174,32 +10174,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126836309</v>
+        <v>126836503</v>
       </c>
       <c r="B95" t="n">
-        <v>78772</v>
+        <v>92616</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>680720</v>
+        <v>680682</v>
       </c>
       <c r="R95" t="n">
-        <v>7087133</v>
+        <v>7087164</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10275,7 +10275,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126838824</v>
+        <v>126836471</v>
       </c>
       <c r="B96" t="n">
         <v>79014</v>
@@ -10306,14 +10306,14 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>680778</v>
+        <v>680715</v>
       </c>
       <c r="R96" t="n">
-        <v>7087226</v>
+        <v>7087274</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10360,12 +10360,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10376,7 +10376,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126836471</v>
+        <v>126838824</v>
       </c>
       <c r="B97" t="n">
         <v>79014</v>
@@ -10407,14 +10407,14 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>680715</v>
+        <v>680778</v>
       </c>
       <c r="R97" t="n">
-        <v>7087274</v>
+        <v>7087226</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10461,12 +10461,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10588,32 +10588,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126836226</v>
+        <v>126836505</v>
       </c>
       <c r="B99" t="n">
-        <v>91326</v>
+        <v>92616</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10623,10 +10623,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>680802</v>
+        <v>680711</v>
       </c>
       <c r="R99" t="n">
-        <v>7086993</v>
+        <v>7087139</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10689,32 +10689,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126836505</v>
+        <v>126836226</v>
       </c>
       <c r="B100" t="n">
-        <v>92616</v>
+        <v>91326</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10724,10 +10724,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>680711</v>
+        <v>680802</v>
       </c>
       <c r="R100" t="n">
-        <v>7087139</v>
+        <v>7086993</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10790,10 +10790,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126836242</v>
+        <v>126836522</v>
       </c>
       <c r="B101" t="n">
-        <v>91276</v>
+        <v>78681</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10801,21 +10801,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>112</v>
+        <v>353</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10825,10 +10825,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>680744</v>
+        <v>680726</v>
       </c>
       <c r="R101" t="n">
-        <v>7087264</v>
+        <v>7087132</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10992,10 +10992,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126836522</v>
+        <v>126836242</v>
       </c>
       <c r="B103" t="n">
-        <v>78681</v>
+        <v>91276</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11003,21 +11003,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>353</v>
+        <v>112</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11027,10 +11027,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>680726</v>
+        <v>680744</v>
       </c>
       <c r="R103" t="n">
-        <v>7087132</v>
+        <v>7087264</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11093,7 +11093,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126836487</v>
+        <v>126836352</v>
       </c>
       <c r="B104" t="n">
         <v>79014</v>
@@ -11128,10 +11128,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>680663</v>
+        <v>680753</v>
       </c>
       <c r="R104" t="n">
-        <v>7087244</v>
+        <v>7087043</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11194,10 +11194,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126836259</v>
+        <v>126836487</v>
       </c>
       <c r="B105" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11205,39 +11205,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>680665</v>
+        <v>680663</v>
       </c>
       <c r="R105" t="n">
-        <v>7087214</v>
+        <v>7087244</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11270,11 +11265,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11305,10 +11295,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126836352</v>
+        <v>126836259</v>
       </c>
       <c r="B106" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11316,34 +11306,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>680753</v>
+        <v>680665</v>
       </c>
       <c r="R106" t="n">
-        <v>7087043</v>
+        <v>7087214</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11376,6 +11371,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11608,32 +11608,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126836507</v>
+        <v>126836491</v>
       </c>
       <c r="B109" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11643,10 +11643,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>680724</v>
+        <v>680645</v>
       </c>
       <c r="R109" t="n">
-        <v>7087106</v>
+        <v>7087283</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11810,50 +11810,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126839946</v>
+        <v>126836485</v>
       </c>
       <c r="B111" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>680662</v>
+        <v>680660</v>
       </c>
       <c r="R111" t="n">
-        <v>7087219</v>
+        <v>7087229</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11900,12 +11895,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -11916,10 +11911,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126836303</v>
+        <v>126836355</v>
       </c>
       <c r="B112" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11927,21 +11922,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11951,10 +11946,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>680654</v>
+        <v>680779</v>
       </c>
       <c r="R112" t="n">
-        <v>7087239</v>
+        <v>7087023</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12017,32 +12012,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126836355</v>
+        <v>126836507</v>
       </c>
       <c r="B113" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12052,10 +12047,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>680779</v>
+        <v>680724</v>
       </c>
       <c r="R113" t="n">
-        <v>7087023</v>
+        <v>7087106</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12118,45 +12113,50 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126836491</v>
+        <v>126839946</v>
       </c>
       <c r="B114" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>680645</v>
+        <v>680662</v>
       </c>
       <c r="R114" t="n">
-        <v>7087283</v>
+        <v>7087219</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12203,12 +12203,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12219,32 +12219,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126836485</v>
+        <v>126836230</v>
       </c>
       <c r="B115" t="n">
-        <v>79014</v>
+        <v>57479</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12254,10 +12254,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>680660</v>
+        <v>680774</v>
       </c>
       <c r="R115" t="n">
-        <v>7087229</v>
+        <v>7087234</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12320,32 +12320,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126836230</v>
+        <v>126836303</v>
       </c>
       <c r="B116" t="n">
-        <v>57479</v>
+        <v>78773</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>102976</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12355,10 +12355,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>680774</v>
+        <v>680654</v>
       </c>
       <c r="R116" t="n">
-        <v>7087234</v>
+        <v>7087239</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12522,7 +12522,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126836476</v>
+        <v>126836461</v>
       </c>
       <c r="B118" t="n">
         <v>79014</v>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>680712</v>
+        <v>680774</v>
       </c>
       <c r="R118" t="n">
-        <v>7087209</v>
+        <v>7087204</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12623,7 +12623,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126836461</v>
+        <v>126836476</v>
       </c>
       <c r="B119" t="n">
         <v>79014</v>
@@ -12658,10 +12658,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>680774</v>
+        <v>680712</v>
       </c>
       <c r="R119" t="n">
-        <v>7087204</v>
+        <v>7087209</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12825,7 +12825,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126836545</v>
+        <v>126825809</v>
       </c>
       <c r="B121" t="n">
         <v>78681</v>
@@ -12856,14 +12856,14 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>680657</v>
+        <v>680666</v>
       </c>
       <c r="R121" t="n">
-        <v>7087201</v>
+        <v>7087235</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12893,9 +12893,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12910,12 +12920,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -12926,7 +12936,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126825809</v>
+        <v>126836545</v>
       </c>
       <c r="B122" t="n">
         <v>78681</v>
@@ -12957,14 +12967,14 @@
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>680666</v>
+        <v>680657</v>
       </c>
       <c r="R122" t="n">
-        <v>7087235</v>
+        <v>7087201</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12994,19 +13004,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>10:27</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>10:27</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13021,12 +13021,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -13037,10 +13037,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126836479</v>
+        <v>126839970</v>
       </c>
       <c r="B123" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13048,21 +13048,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13072,10 +13072,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>680684</v>
+        <v>680772</v>
       </c>
       <c r="R123" t="n">
-        <v>7087202</v>
+        <v>7087124</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13122,12 +13122,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -13138,10 +13138,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126836354</v>
+        <v>126836559</v>
       </c>
       <c r="B124" t="n">
-        <v>79014</v>
+        <v>91733</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13149,21 +13149,16 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13173,10 +13168,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>680771</v>
+        <v>680744</v>
       </c>
       <c r="R124" t="n">
-        <v>7087030</v>
+        <v>7087264</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13217,6 +13212,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13239,7 +13235,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126836488</v>
+        <v>126836354</v>
       </c>
       <c r="B125" t="n">
         <v>79014</v>
@@ -13274,10 +13270,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>680655</v>
+        <v>680771</v>
       </c>
       <c r="R125" t="n">
-        <v>7087246</v>
+        <v>7087030</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13441,7 +13437,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126836478</v>
+        <v>126836479</v>
       </c>
       <c r="B127" t="n">
         <v>79014</v>
@@ -13476,10 +13472,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>680711</v>
+        <v>680684</v>
       </c>
       <c r="R127" t="n">
-        <v>7087181</v>
+        <v>7087202</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13542,10 +13538,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126839970</v>
+        <v>126836488</v>
       </c>
       <c r="B128" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13553,21 +13549,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13577,10 +13573,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>680772</v>
+        <v>680655</v>
       </c>
       <c r="R128" t="n">
-        <v>7087124</v>
+        <v>7087246</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13627,12 +13623,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -13643,10 +13639,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126836559</v>
+        <v>126836478</v>
       </c>
       <c r="B129" t="n">
-        <v>91733</v>
+        <v>79014</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13654,16 +13650,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13673,10 +13674,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>680744</v>
+        <v>680711</v>
       </c>
       <c r="R129" t="n">
-        <v>7087264</v>
+        <v>7087181</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13717,7 +13718,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13740,7 +13740,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126838826</v>
+        <v>126836467</v>
       </c>
       <c r="B130" t="n">
         <v>79014</v>
@@ -13771,14 +13771,14 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>680675</v>
+        <v>680758</v>
       </c>
       <c r="R130" t="n">
-        <v>7087310</v>
+        <v>7087267</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13825,12 +13825,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -13841,7 +13841,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126836467</v>
+        <v>126838827</v>
       </c>
       <c r="B131" t="n">
         <v>79014</v>
@@ -13872,14 +13872,14 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>680758</v>
+        <v>680665</v>
       </c>
       <c r="R131" t="n">
-        <v>7087267</v>
+        <v>7087288</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13926,12 +13926,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -13942,7 +13942,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126838827</v>
+        <v>126838826</v>
       </c>
       <c r="B132" t="n">
         <v>79014</v>
@@ -13977,10 +13977,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>680665</v>
+        <v>680675</v>
       </c>
       <c r="R132" t="n">
-        <v>7087288</v>
+        <v>7087310</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>

--- a/artfynd/A 64499-2023 artfynd.xlsx
+++ b/artfynd/A 64499-2023 artfynd.xlsx
@@ -4788,10 +4788,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126839994</v>
+        <v>126839937</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4799,21 +4799,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>680650</v>
+        <v>680761</v>
       </c>
       <c r="R42" t="n">
-        <v>7087238</v>
+        <v>7087124</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4889,7 +4889,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126836483</v>
+        <v>126839994</v>
       </c>
       <c r="B43" t="n">
         <v>79014</v>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>680673</v>
+        <v>680650</v>
       </c>
       <c r="R43" t="n">
-        <v>7087210</v>
+        <v>7087238</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4974,12 +4974,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -4990,10 +4990,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126839937</v>
+        <v>126836483</v>
       </c>
       <c r="B44" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5001,21 +5001,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>680761</v>
+        <v>680673</v>
       </c>
       <c r="R44" t="n">
-        <v>7087124</v>
+        <v>7087210</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5075,12 +5075,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5394,45 +5394,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126839976</v>
+        <v>126838822</v>
       </c>
       <c r="B48" t="n">
-        <v>58027</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>680693</v>
+        <v>680783</v>
       </c>
       <c r="R48" t="n">
-        <v>7087162</v>
+        <v>7087170</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5479,12 +5479,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5495,7 +5495,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126838822</v>
+        <v>126836338</v>
       </c>
       <c r="B49" t="n">
         <v>79014</v>
@@ -5526,14 +5526,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>680783</v>
+        <v>680648</v>
       </c>
       <c r="R49" t="n">
-        <v>7087170</v>
+        <v>7087260</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5580,12 +5580,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5596,10 +5596,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126836338</v>
+        <v>126836198</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5607,21 +5607,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>680648</v>
+        <v>680721</v>
       </c>
       <c r="R50" t="n">
-        <v>7087260</v>
+        <v>7087133</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5697,10 +5697,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126836198</v>
+        <v>126839998</v>
       </c>
       <c r="B51" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5708,21 +5708,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>680721</v>
+        <v>680673</v>
       </c>
       <c r="R51" t="n">
-        <v>7087133</v>
+        <v>7087211</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5782,12 +5782,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5798,7 +5798,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126839998</v>
+        <v>126837223</v>
       </c>
       <c r="B52" t="n">
         <v>79014</v>
@@ -5833,10 +5833,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>680673</v>
+        <v>680772</v>
       </c>
       <c r="R52" t="n">
-        <v>7087211</v>
+        <v>7087024</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5883,12 +5883,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5899,32 +5899,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126837223</v>
+        <v>126839976</v>
       </c>
       <c r="B53" t="n">
-        <v>79014</v>
+        <v>58027</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5934,10 +5934,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>680772</v>
+        <v>680693</v>
       </c>
       <c r="R53" t="n">
-        <v>7087024</v>
+        <v>7087162</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5984,12 +5984,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -7029,10 +7029,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126836515</v>
+        <v>126836474</v>
       </c>
       <c r="B64" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7040,21 +7040,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>680644</v>
+        <v>680712</v>
       </c>
       <c r="R64" t="n">
-        <v>7087195</v>
+        <v>7087225</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7130,10 +7130,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126836302</v>
+        <v>126836482</v>
       </c>
       <c r="B65" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7141,21 +7141,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7165,10 +7165,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>680677</v>
+        <v>680673</v>
       </c>
       <c r="R65" t="n">
-        <v>7087201</v>
+        <v>7087202</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7231,45 +7231,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126839938</v>
+        <v>126837038</v>
       </c>
       <c r="B66" t="n">
-        <v>79632</v>
+        <v>91291</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>680652</v>
+        <v>680783</v>
       </c>
       <c r="R66" t="n">
-        <v>7087271</v>
+        <v>7087069</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7316,12 +7316,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7332,10 +7332,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126838804</v>
+        <v>126836542</v>
       </c>
       <c r="B67" t="n">
-        <v>78772</v>
+        <v>78681</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7343,34 +7343,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>680765</v>
+        <v>680710</v>
       </c>
       <c r="R67" t="n">
-        <v>7087124</v>
+        <v>7087232</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7417,12 +7417,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7433,10 +7433,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126836474</v>
+        <v>126836515</v>
       </c>
       <c r="B68" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7444,21 +7444,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7468,10 +7468,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>680712</v>
+        <v>680644</v>
       </c>
       <c r="R68" t="n">
-        <v>7087225</v>
+        <v>7087195</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7534,10 +7534,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126836482</v>
+        <v>126836302</v>
       </c>
       <c r="B69" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7545,21 +7545,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>680673</v>
+        <v>680677</v>
       </c>
       <c r="R69" t="n">
-        <v>7087202</v>
+        <v>7087201</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7635,45 +7635,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126837038</v>
+        <v>126839938</v>
       </c>
       <c r="B70" t="n">
-        <v>91291</v>
+        <v>79632</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>680783</v>
+        <v>680652</v>
       </c>
       <c r="R70" t="n">
-        <v>7087069</v>
+        <v>7087271</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7720,12 +7720,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7736,10 +7736,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126836542</v>
+        <v>126838804</v>
       </c>
       <c r="B71" t="n">
-        <v>78681</v>
+        <v>78772</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7747,34 +7747,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>680710</v>
+        <v>680765</v>
       </c>
       <c r="R71" t="n">
-        <v>7087232</v>
+        <v>7087124</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7821,12 +7821,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8847,10 +8847,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126836472</v>
+        <v>126837053</v>
       </c>
       <c r="B82" t="n">
-        <v>79014</v>
+        <v>91346</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8858,34 +8858,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>680714</v>
+        <v>680770</v>
       </c>
       <c r="R82" t="n">
-        <v>7087268</v>
+        <v>7087092</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8932,12 +8932,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -8948,10 +8948,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126837053</v>
+        <v>126836472</v>
       </c>
       <c r="B83" t="n">
-        <v>91346</v>
+        <v>79014</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8959,34 +8959,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>680770</v>
+        <v>680714</v>
       </c>
       <c r="R83" t="n">
-        <v>7087092</v>
+        <v>7087268</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9033,12 +9033,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -12825,10 +12825,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126825809</v>
+        <v>126836354</v>
       </c>
       <c r="B121" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12836,34 +12836,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>680666</v>
+        <v>680771</v>
       </c>
       <c r="R121" t="n">
-        <v>7087235</v>
+        <v>7087030</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12893,19 +12893,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>10:27</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>10:27</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12920,12 +12910,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -12936,10 +12926,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126836545</v>
+        <v>126836466</v>
       </c>
       <c r="B122" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12947,21 +12937,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12971,10 +12961,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>680657</v>
+        <v>680756</v>
       </c>
       <c r="R122" t="n">
-        <v>7087201</v>
+        <v>7087273</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13037,10 +13027,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126839970</v>
+        <v>126836479</v>
       </c>
       <c r="B123" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13048,21 +13038,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13072,10 +13062,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>680772</v>
+        <v>680684</v>
       </c>
       <c r="R123" t="n">
-        <v>7087124</v>
+        <v>7087202</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13122,12 +13112,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -13138,10 +13128,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126836559</v>
+        <v>126836488</v>
       </c>
       <c r="B124" t="n">
-        <v>91733</v>
+        <v>79014</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13149,16 +13139,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13168,10 +13163,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>680744</v>
+        <v>680655</v>
       </c>
       <c r="R124" t="n">
-        <v>7087264</v>
+        <v>7087246</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13212,7 +13207,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13235,7 +13229,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126836354</v>
+        <v>126836478</v>
       </c>
       <c r="B125" t="n">
         <v>79014</v>
@@ -13270,10 +13264,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>680771</v>
+        <v>680711</v>
       </c>
       <c r="R125" t="n">
-        <v>7087030</v>
+        <v>7087181</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13336,10 +13330,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126836466</v>
+        <v>126825809</v>
       </c>
       <c r="B126" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13347,34 +13341,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>680756</v>
+        <v>680666</v>
       </c>
       <c r="R126" t="n">
-        <v>7087273</v>
+        <v>7087235</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13404,9 +13398,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13421,12 +13425,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -13437,10 +13441,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126836479</v>
+        <v>126836545</v>
       </c>
       <c r="B127" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13448,21 +13452,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13472,10 +13476,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>680684</v>
+        <v>680657</v>
       </c>
       <c r="R127" t="n">
-        <v>7087202</v>
+        <v>7087201</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13538,10 +13542,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126836488</v>
+        <v>126836559</v>
       </c>
       <c r="B128" t="n">
-        <v>79014</v>
+        <v>91733</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13549,21 +13553,16 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13573,10 +13572,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>680655</v>
+        <v>680744</v>
       </c>
       <c r="R128" t="n">
-        <v>7087246</v>
+        <v>7087264</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13617,6 +13616,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13639,10 +13639,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126836478</v>
+        <v>126839970</v>
       </c>
       <c r="B129" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13650,21 +13650,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13674,10 +13674,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>680711</v>
+        <v>680772</v>
       </c>
       <c r="R129" t="n">
-        <v>7087181</v>
+        <v>7087124</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13724,12 +13724,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">

--- a/artfynd/A 64499-2023 artfynd.xlsx
+++ b/artfynd/A 64499-2023 artfynd.xlsx
@@ -804,45 +804,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126836506</v>
+        <v>126825730</v>
       </c>
       <c r="B3" t="n">
-        <v>92616</v>
+        <v>79632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680723</v>
+        <v>680666</v>
       </c>
       <c r="R3" t="n">
-        <v>7087114</v>
+        <v>7087235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,12 +869,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,12 +899,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -905,32 +915,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126836504</v>
+        <v>126836489</v>
       </c>
       <c r="B4" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680697</v>
+        <v>680647</v>
       </c>
       <c r="R4" t="n">
-        <v>7087147</v>
+        <v>7087267</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126836552</v>
+        <v>126836484</v>
       </c>
       <c r="B5" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680642</v>
+        <v>680665</v>
       </c>
       <c r="R5" t="n">
-        <v>7087273</v>
+        <v>7087214</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,32 +1117,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126836523</v>
+        <v>126836506</v>
       </c>
       <c r="B6" t="n">
-        <v>78681</v>
+        <v>92616</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,7 +1152,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680728</v>
+        <v>680723</v>
       </c>
       <c r="R6" t="n">
         <v>7087114</v>
@@ -1208,32 +1218,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126839973</v>
+        <v>126836504</v>
       </c>
       <c r="B7" t="n">
-        <v>78773</v>
+        <v>92616</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680751</v>
+        <v>680697</v>
       </c>
       <c r="R7" t="n">
-        <v>7087100</v>
+        <v>7087147</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,12 +1303,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1309,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126825730</v>
+        <v>126836552</v>
       </c>
       <c r="B8" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1320,34 +1330,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680666</v>
+        <v>680642</v>
       </c>
       <c r="R8" t="n">
-        <v>7087235</v>
+        <v>7087273</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,22 +1384,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,12 +1404,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1420,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126836489</v>
+        <v>126836523</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1431,21 +1431,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680647</v>
+        <v>680728</v>
       </c>
       <c r="R9" t="n">
-        <v>7087267</v>
+        <v>7087114</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126836484</v>
+        <v>126838823</v>
       </c>
       <c r="B10" t="n">
         <v>79014</v>
@@ -1552,14 +1552,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680665</v>
+        <v>680767</v>
       </c>
       <c r="R10" t="n">
-        <v>7087214</v>
+        <v>7087204</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,12 +1606,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1622,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126838823</v>
+        <v>126839973</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,34 +1633,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680767</v>
+        <v>680751</v>
       </c>
       <c r="R11" t="n">
-        <v>7087204</v>
+        <v>7087100</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,12 +1707,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1723,10 +1723,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126837083</v>
+        <v>126836546</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1734,34 +1734,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680743</v>
+        <v>680660</v>
       </c>
       <c r="R12" t="n">
-        <v>7087104</v>
+        <v>7087210</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1808,12 +1808,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1824,7 +1824,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126840004</v>
+        <v>126836520</v>
       </c>
       <c r="B13" t="n">
         <v>78681</v>
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680639</v>
+        <v>680716</v>
       </c>
       <c r="R13" t="n">
-        <v>7087277</v>
+        <v>7087135</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,12 +1909,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1925,10 +1925,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126837190</v>
+        <v>126840004</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>78681</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,42 +1936,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680778</v>
+        <v>680639</v>
       </c>
       <c r="R14" t="n">
-        <v>7087007</v>
+        <v>7087277</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,11 +1998,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2023,12 +2010,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2039,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126839974</v>
+        <v>126837190</v>
       </c>
       <c r="B15" t="n">
-        <v>78772</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2050,34 +2037,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680751</v>
+        <v>680778</v>
       </c>
       <c r="R15" t="n">
-        <v>7087100</v>
+        <v>7087007</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,6 +2107,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2124,12 +2124,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2140,10 +2140,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126836555</v>
+        <v>126839974</v>
       </c>
       <c r="B16" t="n">
-        <v>78420</v>
+        <v>78772</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2151,21 +2151,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680660</v>
+        <v>680751</v>
       </c>
       <c r="R16" t="n">
-        <v>7087210</v>
+        <v>7087100</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,12 +2225,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2241,10 +2241,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126836546</v>
+        <v>126837083</v>
       </c>
       <c r="B17" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,34 +2252,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680660</v>
+        <v>680743</v>
       </c>
       <c r="R17" t="n">
-        <v>7087210</v>
+        <v>7087104</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2326,12 +2326,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126836520</v>
+        <v>126836555</v>
       </c>
       <c r="B18" t="n">
-        <v>78681</v>
+        <v>78420</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680716</v>
+        <v>680660</v>
       </c>
       <c r="R18" t="n">
-        <v>7087135</v>
+        <v>7087210</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3049,7 +3049,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126838821</v>
+        <v>126838825</v>
       </c>
       <c r="B25" t="n">
         <v>79014</v>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680775</v>
+        <v>680759</v>
       </c>
       <c r="R25" t="n">
-        <v>7087121</v>
+        <v>7087282</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126840003</v>
+        <v>126838821</v>
       </c>
       <c r="B26" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3161,34 +3161,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680729</v>
+        <v>680775</v>
       </c>
       <c r="R26" t="n">
-        <v>7087103</v>
+        <v>7087121</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,12 +3235,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126836551</v>
+        <v>126837228</v>
       </c>
       <c r="B27" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3262,21 +3262,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680654</v>
+        <v>680658</v>
       </c>
       <c r="R27" t="n">
-        <v>7087239</v>
+        <v>7087213</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,12 +3336,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3352,53 +3352,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126837193</v>
+        <v>126839971</v>
       </c>
       <c r="B28" t="n">
-        <v>56849</v>
+        <v>78772</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680696</v>
+        <v>680772</v>
       </c>
       <c r="R28" t="n">
-        <v>7087170</v>
+        <v>7087124</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3433,11 +3425,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Blindtarmstömmning</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3450,12 +3437,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3466,7 +3453,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126838825</v>
+        <v>126840000</v>
       </c>
       <c r="B29" t="n">
         <v>79014</v>
@@ -3497,14 +3484,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680759</v>
+        <v>680643</v>
       </c>
       <c r="R29" t="n">
-        <v>7087282</v>
+        <v>7087277</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,12 +3538,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3567,7 +3554,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126837228</v>
+        <v>126839989</v>
       </c>
       <c r="B30" t="n">
         <v>79014</v>
@@ -3602,10 +3589,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680658</v>
+        <v>680774</v>
       </c>
       <c r="R30" t="n">
-        <v>7087213</v>
+        <v>7087124</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3652,12 +3639,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3668,10 +3655,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126839971</v>
+        <v>126840003</v>
       </c>
       <c r="B31" t="n">
-        <v>78772</v>
+        <v>78681</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3679,21 +3666,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3703,10 +3690,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680772</v>
+        <v>680729</v>
       </c>
       <c r="R31" t="n">
-        <v>7087124</v>
+        <v>7087103</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3769,10 +3756,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126840000</v>
+        <v>126836551</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3780,21 +3767,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3804,10 +3791,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680643</v>
+        <v>680654</v>
       </c>
       <c r="R32" t="n">
-        <v>7087277</v>
+        <v>7087239</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3854,12 +3841,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3870,45 +3857,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126839989</v>
+        <v>126837193</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680774</v>
+        <v>680696</v>
       </c>
       <c r="R33" t="n">
-        <v>7087124</v>
+        <v>7087170</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3943,6 +3938,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Blindtarmstömmning</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -3955,12 +3955,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -7837,10 +7837,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126837052</v>
+        <v>126836475</v>
       </c>
       <c r="B72" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7848,34 +7848,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>680740</v>
+        <v>680708</v>
       </c>
       <c r="R72" t="n">
-        <v>7087222</v>
+        <v>7087220</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7922,12 +7922,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7938,10 +7938,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126837069</v>
+        <v>126836336</v>
       </c>
       <c r="B73" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7949,34 +7949,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>680673</v>
+        <v>680653</v>
       </c>
       <c r="R73" t="n">
-        <v>7087276</v>
+        <v>7087252</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8023,12 +8023,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8039,10 +8039,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126840002</v>
+        <v>126836464</v>
       </c>
       <c r="B74" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8050,21 +8050,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8074,10 +8074,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>680724</v>
+        <v>680772</v>
       </c>
       <c r="R74" t="n">
-        <v>7087119</v>
+        <v>7087252</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8124,12 +8124,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8140,10 +8140,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126836524</v>
+        <v>126836473</v>
       </c>
       <c r="B75" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8151,21 +8151,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>680720</v>
+        <v>680710</v>
       </c>
       <c r="R75" t="n">
-        <v>7087100</v>
+        <v>7087232</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8241,10 +8241,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126836544</v>
+        <v>126839999</v>
       </c>
       <c r="B76" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8252,21 +8252,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8276,10 +8276,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>680681</v>
+        <v>680651</v>
       </c>
       <c r="R76" t="n">
-        <v>7087195</v>
+        <v>7087231</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8326,12 +8326,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8342,10 +8342,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126836475</v>
+        <v>126837052</v>
       </c>
       <c r="B77" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8353,34 +8353,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>680708</v>
+        <v>680740</v>
       </c>
       <c r="R77" t="n">
-        <v>7087220</v>
+        <v>7087222</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8427,12 +8427,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8443,10 +8443,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126836336</v>
+        <v>126837069</v>
       </c>
       <c r="B78" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8454,34 +8454,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>680653</v>
+        <v>680673</v>
       </c>
       <c r="R78" t="n">
-        <v>7087252</v>
+        <v>7087276</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8528,12 +8528,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8544,10 +8544,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126836464</v>
+        <v>126840002</v>
       </c>
       <c r="B79" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8555,21 +8555,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8579,10 +8579,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>680772</v>
+        <v>680724</v>
       </c>
       <c r="R79" t="n">
-        <v>7087252</v>
+        <v>7087119</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8629,12 +8629,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8645,10 +8645,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126836473</v>
+        <v>126836524</v>
       </c>
       <c r="B80" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8656,21 +8656,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8680,10 +8680,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>680710</v>
+        <v>680720</v>
       </c>
       <c r="R80" t="n">
-        <v>7087232</v>
+        <v>7087100</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8746,10 +8746,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126839999</v>
+        <v>126836544</v>
       </c>
       <c r="B81" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8757,21 +8757,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8781,10 +8781,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>680651</v>
+        <v>680681</v>
       </c>
       <c r="R81" t="n">
-        <v>7087231</v>
+        <v>7087195</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8831,12 +8831,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -10275,10 +10275,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126836471</v>
+        <v>126836226</v>
       </c>
       <c r="B96" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10286,21 +10286,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10310,10 +10310,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>680715</v>
+        <v>680802</v>
       </c>
       <c r="R96" t="n">
-        <v>7087274</v>
+        <v>7086993</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10376,7 +10376,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126838824</v>
+        <v>126836471</v>
       </c>
       <c r="B97" t="n">
         <v>79014</v>
@@ -10407,14 +10407,14 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>680778</v>
+        <v>680715</v>
       </c>
       <c r="R97" t="n">
-        <v>7087226</v>
+        <v>7087274</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10461,12 +10461,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10477,10 +10477,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126826458</v>
+        <v>126838824</v>
       </c>
       <c r="B98" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10488,34 +10488,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>680755</v>
+        <v>680778</v>
       </c>
       <c r="R98" t="n">
-        <v>7087104</v>
+        <v>7087226</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10545,19 +10545,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10572,12 +10562,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10588,45 +10578,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126836505</v>
+        <v>126826458</v>
       </c>
       <c r="B99" t="n">
-        <v>92616</v>
+        <v>78772</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>680711</v>
+        <v>680755</v>
       </c>
       <c r="R99" t="n">
-        <v>7087139</v>
+        <v>7087104</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10656,9 +10646,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10673,12 +10673,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10689,32 +10689,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126836226</v>
+        <v>126836505</v>
       </c>
       <c r="B100" t="n">
-        <v>91326</v>
+        <v>92616</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10724,10 +10724,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>680802</v>
+        <v>680711</v>
       </c>
       <c r="R100" t="n">
-        <v>7086993</v>
+        <v>7087139</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12012,10 +12012,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126836507</v>
+        <v>126839946</v>
       </c>
       <c r="B113" t="n">
-        <v>92616</v>
+        <v>56849</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12023,34 +12023,39 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>680724</v>
+        <v>680662</v>
       </c>
       <c r="R113" t="n">
-        <v>7087106</v>
+        <v>7087219</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12097,12 +12102,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12113,50 +12118,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126839946</v>
+        <v>126836303</v>
       </c>
       <c r="B114" t="n">
-        <v>56849</v>
+        <v>78773</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>680662</v>
+        <v>680654</v>
       </c>
       <c r="R114" t="n">
-        <v>7087219</v>
+        <v>7087239</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12203,12 +12203,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12219,32 +12219,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126836230</v>
+        <v>126836507</v>
       </c>
       <c r="B115" t="n">
-        <v>57479</v>
+        <v>92616</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>102976</v>
+        <v>4364</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12254,10 +12254,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>680774</v>
+        <v>680724</v>
       </c>
       <c r="R115" t="n">
-        <v>7087234</v>
+        <v>7087106</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12320,32 +12320,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126836303</v>
+        <v>126836230</v>
       </c>
       <c r="B116" t="n">
-        <v>78773</v>
+        <v>57479</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>102976</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12355,10 +12355,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>680654</v>
+        <v>680774</v>
       </c>
       <c r="R116" t="n">
-        <v>7087239</v>
+        <v>7087234</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12421,10 +12421,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126836550</v>
+        <v>126836461</v>
       </c>
       <c r="B117" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12432,21 +12432,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12456,10 +12456,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>680667</v>
+        <v>680774</v>
       </c>
       <c r="R117" t="n">
-        <v>7087238</v>
+        <v>7087204</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12522,7 +12522,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126836461</v>
+        <v>126836476</v>
       </c>
       <c r="B118" t="n">
         <v>79014</v>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>680774</v>
+        <v>680712</v>
       </c>
       <c r="R118" t="n">
-        <v>7087204</v>
+        <v>7087209</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12623,7 +12623,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126836476</v>
+        <v>126836356</v>
       </c>
       <c r="B119" t="n">
         <v>79014</v>
@@ -12658,10 +12658,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>680712</v>
+        <v>680782</v>
       </c>
       <c r="R119" t="n">
-        <v>7087209</v>
+        <v>7087012</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12724,10 +12724,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126836356</v>
+        <v>126836550</v>
       </c>
       <c r="B120" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12735,21 +12735,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12759,10 +12759,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>680782</v>
+        <v>680667</v>
       </c>
       <c r="R120" t="n">
-        <v>7087012</v>
+        <v>7087238</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>

--- a/artfynd/A 64499-2023 artfynd.xlsx
+++ b/artfynd/A 64499-2023 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126825730</v>
+        <v>126836489</v>
       </c>
       <c r="B3" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,34 +815,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680666</v>
+        <v>680647</v>
       </c>
       <c r="R3" t="n">
-        <v>7087235</v>
+        <v>7087267</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,22 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,12 +889,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -915,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126836489</v>
+        <v>126836484</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -950,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680647</v>
+        <v>680665</v>
       </c>
       <c r="R4" t="n">
-        <v>7087267</v>
+        <v>7087214</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126836484</v>
+        <v>126838823</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,14 +1037,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680665</v>
+        <v>680767</v>
       </c>
       <c r="R5" t="n">
-        <v>7087214</v>
+        <v>7087204</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,12 +1091,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1117,45 +1107,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126836506</v>
+        <v>126825730</v>
       </c>
       <c r="B6" t="n">
-        <v>92616</v>
+        <v>79636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680723</v>
+        <v>680666</v>
       </c>
       <c r="R6" t="n">
-        <v>7087114</v>
+        <v>7087235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,12 +1172,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1202,12 +1202,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1218,32 +1218,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126836504</v>
+        <v>126839973</v>
       </c>
       <c r="B7" t="n">
-        <v>92616</v>
+        <v>78777</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680697</v>
+        <v>680751</v>
       </c>
       <c r="R7" t="n">
-        <v>7087147</v>
+        <v>7087100</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,12 +1303,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1322,7 +1322,7 @@
         <v>126836552</v>
       </c>
       <c r="B8" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>126836523</v>
       </c>
       <c r="B9" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1521,45 +1521,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126838823</v>
+        <v>126836506</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>92620</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680767</v>
+        <v>680723</v>
       </c>
       <c r="R10" t="n">
-        <v>7087204</v>
+        <v>7087114</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,12 +1606,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1622,32 +1622,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126839973</v>
+        <v>126836504</v>
       </c>
       <c r="B11" t="n">
-        <v>78773</v>
+        <v>92620</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680751</v>
+        <v>680697</v>
       </c>
       <c r="R11" t="n">
-        <v>7087100</v>
+        <v>7087147</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,12 +1707,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1726,7 +1726,7 @@
         <v>126836546</v>
       </c>
       <c r="B12" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>126836520</v>
       </c>
       <c r="B13" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1925,10 +1925,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126840004</v>
+        <v>126837233</v>
       </c>
       <c r="B14" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680639</v>
+        <v>680698</v>
       </c>
       <c r="R14" t="n">
-        <v>7087277</v>
+        <v>7087108</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,12 +2010,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126837190</v>
+        <v>126840004</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>78685</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,42 +2037,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680778</v>
+        <v>680639</v>
       </c>
       <c r="R15" t="n">
-        <v>7087007</v>
+        <v>7087277</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,11 +2099,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2124,12 +2111,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2140,10 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126839974</v>
+        <v>126837083</v>
       </c>
       <c r="B16" t="n">
-        <v>78772</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2151,34 +2138,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680751</v>
+        <v>680743</v>
       </c>
       <c r="R16" t="n">
-        <v>7087100</v>
+        <v>7087104</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,12 +2212,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2241,10 +2228,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126837083</v>
+        <v>126839974</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>78776</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,34 +2239,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680743</v>
+        <v>680751</v>
       </c>
       <c r="R17" t="n">
-        <v>7087104</v>
+        <v>7087100</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2326,12 +2313,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2345,7 +2332,7 @@
         <v>126836555</v>
       </c>
       <c r="B18" t="n">
-        <v>78420</v>
+        <v>78424</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2443,10 +2430,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126837233</v>
+        <v>126837190</v>
       </c>
       <c r="B19" t="n">
-        <v>78681</v>
+        <v>57661</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,34 +2441,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680698</v>
+        <v>680778</v>
       </c>
       <c r="R19" t="n">
-        <v>7087108</v>
+        <v>7087007</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2514,6 +2509,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2547,7 +2547,7 @@
         <v>126836351</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>126837085</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>126837227</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2847,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126837232</v>
+        <v>126836547</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>78685</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,21 +2858,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680637</v>
+        <v>680665</v>
       </c>
       <c r="R23" t="n">
-        <v>7087243</v>
+        <v>7087202</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2932,12 +2932,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2948,10 +2948,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126836547</v>
+        <v>126837232</v>
       </c>
       <c r="B24" t="n">
-        <v>78681</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,21 +2959,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>680665</v>
+        <v>680637</v>
       </c>
       <c r="R24" t="n">
-        <v>7087202</v>
+        <v>7087243</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3033,12 +3033,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3052,7 +3052,7 @@
         <v>126838825</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>126838821</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>126837228</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3352,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126839971</v>
+        <v>126840000</v>
       </c>
       <c r="B28" t="n">
-        <v>78772</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3363,21 +3363,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680772</v>
+        <v>680643</v>
       </c>
       <c r="R28" t="n">
-        <v>7087124</v>
+        <v>7087277</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126840000</v>
+        <v>126839989</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680643</v>
+        <v>680774</v>
       </c>
       <c r="R29" t="n">
-        <v>7087277</v>
+        <v>7087124</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3554,10 +3554,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126839989</v>
+        <v>126839971</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>78776</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3565,21 +3565,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680774</v>
+        <v>680772</v>
       </c>
       <c r="R30" t="n">
         <v>7087124</v>
@@ -3655,45 +3655,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126840003</v>
+        <v>126837193</v>
       </c>
       <c r="B31" t="n">
-        <v>78681</v>
+        <v>56853</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680729</v>
+        <v>680696</v>
       </c>
       <c r="R31" t="n">
-        <v>7087103</v>
+        <v>7087170</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3728,6 +3736,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Blindtarmstömmning</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3740,12 +3753,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3756,10 +3769,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126836551</v>
+        <v>126840003</v>
       </c>
       <c r="B32" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3791,10 +3804,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680654</v>
+        <v>680729</v>
       </c>
       <c r="R32" t="n">
-        <v>7087239</v>
+        <v>7087103</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3841,12 +3854,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3857,53 +3870,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126837193</v>
+        <v>126836551</v>
       </c>
       <c r="B33" t="n">
-        <v>56849</v>
+        <v>78685</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680696</v>
+        <v>680654</v>
       </c>
       <c r="R33" t="n">
-        <v>7087170</v>
+        <v>7087239</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3938,11 +3943,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Blindtarmstömmning</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -3955,12 +3955,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3974,7 +3974,7 @@
         <v>126839997</v>
       </c>
       <c r="B34" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4072,45 +4072,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126837084</v>
+        <v>126837192</v>
       </c>
       <c r="B35" t="n">
-        <v>79014</v>
+        <v>56853</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>680731</v>
+        <v>680665</v>
       </c>
       <c r="R35" t="n">
-        <v>7087201</v>
+        <v>7087191</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,6 +4153,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4157,12 +4170,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4173,10 +4186,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126836460</v>
+        <v>126838798</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>57821</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4184,34 +4197,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>680779</v>
+        <v>680781</v>
       </c>
       <c r="R36" t="n">
-        <v>7087200</v>
+        <v>7087170</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4258,26 +4271,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126836463</v>
+        <v>126836543</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>78685</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4285,21 +4294,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4309,10 +4318,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>680773</v>
+        <v>680708</v>
       </c>
       <c r="R37" t="n">
-        <v>7087233</v>
+        <v>7087204</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4375,10 +4384,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126836543</v>
+        <v>126837084</v>
       </c>
       <c r="B38" t="n">
-        <v>78681</v>
+        <v>79018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4386,34 +4395,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>680708</v>
+        <v>680731</v>
       </c>
       <c r="R38" t="n">
-        <v>7087204</v>
+        <v>7087201</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4460,12 +4469,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4476,10 +4485,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126836477</v>
+        <v>126836460</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4511,10 +4520,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>680709</v>
+        <v>680779</v>
       </c>
       <c r="R39" t="n">
-        <v>7087204</v>
+        <v>7087200</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4577,53 +4586,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126837192</v>
+        <v>126836463</v>
       </c>
       <c r="B40" t="n">
-        <v>56849</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>680665</v>
+        <v>680773</v>
       </c>
       <c r="R40" t="n">
-        <v>7087191</v>
+        <v>7087233</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4658,11 +4659,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4675,12 +4671,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4691,10 +4687,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126838798</v>
+        <v>126836477</v>
       </c>
       <c r="B41" t="n">
-        <v>57817</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4702,34 +4698,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>680781</v>
+        <v>680709</v>
       </c>
       <c r="R41" t="n">
-        <v>7087170</v>
+        <v>7087204</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4776,22 +4772,26 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126839937</v>
+        <v>126836516</v>
       </c>
       <c r="B42" t="n">
-        <v>79632</v>
+        <v>78685</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4799,21 +4799,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>680761</v>
+        <v>680654</v>
       </c>
       <c r="R42" t="n">
-        <v>7087124</v>
+        <v>7087188</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4873,12 +4873,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4892,7 +4892,7 @@
         <v>126839994</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>126836483</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5091,10 +5091,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126836516</v>
+        <v>126839937</v>
       </c>
       <c r="B45" t="n">
-        <v>78681</v>
+        <v>79636</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5102,21 +5102,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>680654</v>
+        <v>680761</v>
       </c>
       <c r="R45" t="n">
-        <v>7087188</v>
+        <v>7087124</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5176,12 +5176,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5195,7 +5195,7 @@
         <v>126836517</v>
       </c>
       <c r="B46" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>126836548</v>
       </c>
       <c r="B47" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>126838822</v>
       </c>
       <c r="B48" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>126836338</v>
       </c>
       <c r="B49" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5596,10 +5596,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126836198</v>
+        <v>126839998</v>
       </c>
       <c r="B50" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5607,21 +5607,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>680721</v>
+        <v>680673</v>
       </c>
       <c r="R50" t="n">
-        <v>7087133</v>
+        <v>7087211</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5681,12 +5681,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5697,10 +5697,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126839998</v>
+        <v>126837223</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>680673</v>
+        <v>680772</v>
       </c>
       <c r="R51" t="n">
-        <v>7087211</v>
+        <v>7087024</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5782,12 +5782,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5798,10 +5798,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126837223</v>
+        <v>126836198</v>
       </c>
       <c r="B52" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5809,21 +5809,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5833,10 +5833,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>680772</v>
+        <v>680721</v>
       </c>
       <c r="R52" t="n">
-        <v>7087024</v>
+        <v>7087133</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5883,12 +5883,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5902,7 +5902,7 @@
         <v>126839976</v>
       </c>
       <c r="B53" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6000,10 +6000,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126836490</v>
+        <v>126836519</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>78685</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6011,21 +6011,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6035,10 +6035,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>680645</v>
+        <v>680693</v>
       </c>
       <c r="R54" t="n">
-        <v>7087280</v>
+        <v>7087159</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6101,10 +6101,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126837225</v>
+        <v>126837234</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>78685</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6112,21 +6112,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6136,10 +6136,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>680729</v>
+        <v>680694</v>
       </c>
       <c r="R55" t="n">
-        <v>7087081</v>
+        <v>7087158</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6202,10 +6202,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126836469</v>
+        <v>126836541</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>78685</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6213,21 +6213,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6237,10 +6237,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>680728</v>
+        <v>680708</v>
       </c>
       <c r="R56" t="n">
-        <v>7087278</v>
+        <v>7087251</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6303,10 +6303,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126840919</v>
+        <v>126839996</v>
       </c>
       <c r="B57" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6314,37 +6314,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>680640</v>
+        <v>680745</v>
       </c>
       <c r="R57" t="n">
-        <v>7087261</v>
+        <v>7087170</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6374,40 +6371,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>10:17</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>10:17</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6418,10 +6404,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126839996</v>
+        <v>126836486</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6453,10 +6439,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>680745</v>
+        <v>680663</v>
       </c>
       <c r="R58" t="n">
-        <v>7087170</v>
+        <v>7087231</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6503,12 +6489,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6519,10 +6505,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126836486</v>
+        <v>126836490</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6554,10 +6540,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>680663</v>
+        <v>680645</v>
       </c>
       <c r="R59" t="n">
-        <v>7087231</v>
+        <v>7087280</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6620,10 +6606,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126836519</v>
+        <v>126837225</v>
       </c>
       <c r="B60" t="n">
-        <v>78681</v>
+        <v>79018</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6631,21 +6617,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6655,10 +6641,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>680693</v>
+        <v>680729</v>
       </c>
       <c r="R60" t="n">
-        <v>7087159</v>
+        <v>7087081</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6705,12 +6691,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6721,10 +6707,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126837234</v>
+        <v>126836469</v>
       </c>
       <c r="B61" t="n">
-        <v>78681</v>
+        <v>79018</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6732,21 +6718,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6756,10 +6742,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>680694</v>
+        <v>680728</v>
       </c>
       <c r="R61" t="n">
-        <v>7087158</v>
+        <v>7087278</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6806,12 +6792,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6822,45 +6808,50 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126836541</v>
+        <v>126839949</v>
       </c>
       <c r="B62" t="n">
-        <v>78681</v>
+        <v>56853</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>680708</v>
+        <v>680726</v>
       </c>
       <c r="R62" t="n">
-        <v>7087251</v>
+        <v>7087219</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6907,12 +6898,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6923,50 +6914,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126839949</v>
+        <v>126840919</v>
       </c>
       <c r="B63" t="n">
-        <v>56849</v>
+        <v>79636</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>680726</v>
+        <v>680640</v>
       </c>
       <c r="R63" t="n">
-        <v>7087219</v>
+        <v>7087261</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6996,29 +6985,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7029,10 +7029,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126836474</v>
+        <v>126836302</v>
       </c>
       <c r="B64" t="n">
-        <v>79014</v>
+        <v>78777</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7040,21 +7040,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>680712</v>
+        <v>680677</v>
       </c>
       <c r="R64" t="n">
-        <v>7087225</v>
+        <v>7087201</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7130,10 +7130,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126836482</v>
+        <v>126839938</v>
       </c>
       <c r="B65" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7141,21 +7141,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7165,10 +7165,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>680673</v>
+        <v>680652</v>
       </c>
       <c r="R65" t="n">
-        <v>7087202</v>
+        <v>7087271</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7215,12 +7215,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7231,45 +7231,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126837038</v>
+        <v>126838804</v>
       </c>
       <c r="B66" t="n">
-        <v>91291</v>
+        <v>78776</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>680783</v>
+        <v>680765</v>
       </c>
       <c r="R66" t="n">
-        <v>7087069</v>
+        <v>7087124</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7316,12 +7316,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7335,7 +7335,7 @@
         <v>126836542</v>
       </c>
       <c r="B67" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>126836515</v>
       </c>
       <c r="B68" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7534,10 +7534,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126836302</v>
+        <v>126836474</v>
       </c>
       <c r="B69" t="n">
-        <v>78773</v>
+        <v>79018</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7545,21 +7545,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>680677</v>
+        <v>680712</v>
       </c>
       <c r="R69" t="n">
-        <v>7087201</v>
+        <v>7087225</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7635,10 +7635,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126839938</v>
+        <v>126836482</v>
       </c>
       <c r="B70" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7646,21 +7646,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7670,10 +7670,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>680652</v>
+        <v>680673</v>
       </c>
       <c r="R70" t="n">
-        <v>7087271</v>
+        <v>7087202</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7720,12 +7720,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7736,45 +7736,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126838804</v>
+        <v>126837038</v>
       </c>
       <c r="B71" t="n">
-        <v>78772</v>
+        <v>91295</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>680765</v>
+        <v>680783</v>
       </c>
       <c r="R71" t="n">
-        <v>7087124</v>
+        <v>7087069</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7821,12 +7821,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7837,10 +7837,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126836475</v>
+        <v>126837052</v>
       </c>
       <c r="B72" t="n">
-        <v>79014</v>
+        <v>57821</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7848,34 +7848,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>680708</v>
+        <v>680740</v>
       </c>
       <c r="R72" t="n">
-        <v>7087220</v>
+        <v>7087222</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7922,12 +7922,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7938,10 +7938,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126836336</v>
+        <v>126837069</v>
       </c>
       <c r="B73" t="n">
-        <v>79014</v>
+        <v>78777</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7949,34 +7949,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>680653</v>
+        <v>680673</v>
       </c>
       <c r="R73" t="n">
-        <v>7087252</v>
+        <v>7087276</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8023,12 +8023,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8039,10 +8039,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126836464</v>
+        <v>126840002</v>
       </c>
       <c r="B74" t="n">
-        <v>79014</v>
+        <v>78685</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8050,21 +8050,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8074,10 +8074,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>680772</v>
+        <v>680724</v>
       </c>
       <c r="R74" t="n">
-        <v>7087252</v>
+        <v>7087119</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8124,12 +8124,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8140,10 +8140,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126836473</v>
+        <v>126836524</v>
       </c>
       <c r="B75" t="n">
-        <v>79014</v>
+        <v>78685</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8151,21 +8151,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>680710</v>
+        <v>680720</v>
       </c>
       <c r="R75" t="n">
-        <v>7087232</v>
+        <v>7087100</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8241,10 +8241,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126839999</v>
+        <v>126836544</v>
       </c>
       <c r="B76" t="n">
-        <v>79014</v>
+        <v>78685</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8252,21 +8252,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8276,10 +8276,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>680651</v>
+        <v>680681</v>
       </c>
       <c r="R76" t="n">
-        <v>7087231</v>
+        <v>7087195</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8326,12 +8326,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8342,10 +8342,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126837052</v>
+        <v>126836473</v>
       </c>
       <c r="B77" t="n">
-        <v>57817</v>
+        <v>79018</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8353,34 +8353,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>680740</v>
+        <v>680710</v>
       </c>
       <c r="R77" t="n">
-        <v>7087222</v>
+        <v>7087232</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8427,12 +8427,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8443,10 +8443,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126837069</v>
+        <v>126839999</v>
       </c>
       <c r="B78" t="n">
-        <v>78773</v>
+        <v>79018</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8454,34 +8454,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>680673</v>
+        <v>680651</v>
       </c>
       <c r="R78" t="n">
-        <v>7087276</v>
+        <v>7087231</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8528,12 +8528,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8544,10 +8544,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126840002</v>
+        <v>126836475</v>
       </c>
       <c r="B79" t="n">
-        <v>78681</v>
+        <v>79018</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8555,21 +8555,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8579,10 +8579,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>680724</v>
+        <v>680708</v>
       </c>
       <c r="R79" t="n">
-        <v>7087119</v>
+        <v>7087220</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8629,12 +8629,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8645,10 +8645,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126836524</v>
+        <v>126836336</v>
       </c>
       <c r="B80" t="n">
-        <v>78681</v>
+        <v>79018</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8656,21 +8656,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8680,10 +8680,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>680720</v>
+        <v>680653</v>
       </c>
       <c r="R80" t="n">
-        <v>7087100</v>
+        <v>7087252</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8746,10 +8746,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126836544</v>
+        <v>126836464</v>
       </c>
       <c r="B81" t="n">
-        <v>78681</v>
+        <v>79018</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8757,21 +8757,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8781,10 +8781,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>680681</v>
+        <v>680772</v>
       </c>
       <c r="R81" t="n">
-        <v>7087195</v>
+        <v>7087252</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8850,7 +8850,7 @@
         <v>126837053</v>
       </c>
       <c r="B82" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>126836472</v>
       </c>
       <c r="B83" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>126836470</v>
       </c>
       <c r="B84" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>126836468</v>
       </c>
       <c r="B85" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9251,32 +9251,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126836309</v>
+        <v>126836503</v>
       </c>
       <c r="B86" t="n">
-        <v>78772</v>
+        <v>92620</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9286,10 +9286,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>680720</v>
+        <v>680682</v>
       </c>
       <c r="R86" t="n">
-        <v>7087133</v>
+        <v>7087164</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9352,10 +9352,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126836199</v>
+        <v>126836481</v>
       </c>
       <c r="B87" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9363,21 +9363,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9387,10 +9387,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>680719</v>
+        <v>680670</v>
       </c>
       <c r="R87" t="n">
-        <v>7087133</v>
+        <v>7087199</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9453,10 +9453,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126840864</v>
+        <v>126837231</v>
       </c>
       <c r="B88" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9464,37 +9464,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>680671</v>
+        <v>680642</v>
       </c>
       <c r="R88" t="n">
-        <v>7087236</v>
+        <v>7087222</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9524,40 +9521,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9568,10 +9554,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126836481</v>
+        <v>126836480</v>
       </c>
       <c r="B89" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9603,10 +9589,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>680670</v>
+        <v>680660</v>
       </c>
       <c r="R89" t="n">
-        <v>7087199</v>
+        <v>7087210</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9669,10 +9655,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126837231</v>
+        <v>126836357</v>
       </c>
       <c r="B90" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9704,10 +9690,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>680642</v>
+        <v>680784</v>
       </c>
       <c r="R90" t="n">
-        <v>7087222</v>
+        <v>7087010</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9754,12 +9740,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9770,10 +9756,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126836480</v>
+        <v>126837082</v>
       </c>
       <c r="B91" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9801,14 +9787,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>680660</v>
+        <v>680771</v>
       </c>
       <c r="R91" t="n">
-        <v>7087210</v>
+        <v>7087091</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9855,12 +9841,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -9871,10 +9857,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126836357</v>
+        <v>126839992</v>
       </c>
       <c r="B92" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9906,10 +9892,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>680784</v>
+        <v>680767</v>
       </c>
       <c r="R92" t="n">
-        <v>7087010</v>
+        <v>7087114</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9956,12 +9942,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -9972,10 +9958,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126837082</v>
+        <v>126836309</v>
       </c>
       <c r="B93" t="n">
-        <v>79014</v>
+        <v>78776</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9983,34 +9969,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>680771</v>
+        <v>680720</v>
       </c>
       <c r="R93" t="n">
-        <v>7087091</v>
+        <v>7087133</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10057,12 +10043,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10073,10 +10059,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126839992</v>
+        <v>126836199</v>
       </c>
       <c r="B94" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10084,21 +10070,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10108,10 +10094,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>680767</v>
+        <v>680719</v>
       </c>
       <c r="R94" t="n">
-        <v>7087114</v>
+        <v>7087133</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10158,12 +10144,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10174,45 +10160,48 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126836503</v>
+        <v>126840864</v>
       </c>
       <c r="B95" t="n">
-        <v>92616</v>
+        <v>79636</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>680682</v>
+        <v>680671</v>
       </c>
       <c r="R95" t="n">
-        <v>7087164</v>
+        <v>7087236</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10242,29 +10231,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10278,7 +10278,7 @@
         <v>126836226</v>
       </c>
       <c r="B96" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10376,32 +10376,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126836471</v>
+        <v>126836505</v>
       </c>
       <c r="B97" t="n">
-        <v>79014</v>
+        <v>92620</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10411,10 +10411,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>680715</v>
+        <v>680711</v>
       </c>
       <c r="R97" t="n">
-        <v>7087274</v>
+        <v>7087139</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10477,10 +10477,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126838824</v>
+        <v>126836471</v>
       </c>
       <c r="B98" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10508,14 +10508,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>680778</v>
+        <v>680715</v>
       </c>
       <c r="R98" t="n">
-        <v>7087226</v>
+        <v>7087274</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10562,12 +10562,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10578,10 +10578,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126826458</v>
+        <v>126838824</v>
       </c>
       <c r="B99" t="n">
-        <v>78772</v>
+        <v>79018</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10589,34 +10589,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>680755</v>
+        <v>680778</v>
       </c>
       <c r="R99" t="n">
-        <v>7087104</v>
+        <v>7087226</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10646,19 +10646,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10673,12 +10663,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10689,45 +10679,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126836505</v>
+        <v>126826458</v>
       </c>
       <c r="B100" t="n">
-        <v>92616</v>
+        <v>78776</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>680711</v>
+        <v>680755</v>
       </c>
       <c r="R100" t="n">
-        <v>7087139</v>
+        <v>7087104</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10757,9 +10747,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10774,12 +10774,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10790,10 +10790,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126836522</v>
+        <v>126836259</v>
       </c>
       <c r="B101" t="n">
-        <v>78681</v>
+        <v>57661</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10801,34 +10801,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>680726</v>
+        <v>680665</v>
       </c>
       <c r="R101" t="n">
-        <v>7087132</v>
+        <v>7087214</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10861,6 +10866,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10891,10 +10901,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126837236</v>
+        <v>126836522</v>
       </c>
       <c r="B102" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10926,10 +10936,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>680673</v>
+        <v>680726</v>
       </c>
       <c r="R102" t="n">
-        <v>7087186</v>
+        <v>7087132</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10976,12 +10986,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -10992,10 +11002,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126836242</v>
+        <v>126837236</v>
       </c>
       <c r="B103" t="n">
-        <v>91276</v>
+        <v>78685</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11003,21 +11013,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>112</v>
+        <v>353</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11027,10 +11037,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>680744</v>
+        <v>680673</v>
       </c>
       <c r="R103" t="n">
-        <v>7087264</v>
+        <v>7087186</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11077,12 +11087,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11093,10 +11103,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126836352</v>
+        <v>126836242</v>
       </c>
       <c r="B104" t="n">
-        <v>79014</v>
+        <v>91280</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11104,21 +11114,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11128,10 +11138,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>680753</v>
+        <v>680744</v>
       </c>
       <c r="R104" t="n">
-        <v>7087043</v>
+        <v>7087264</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11194,10 +11204,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126836487</v>
+        <v>126836352</v>
       </c>
       <c r="B105" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11229,10 +11239,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>680663</v>
+        <v>680753</v>
       </c>
       <c r="R105" t="n">
-        <v>7087244</v>
+        <v>7087043</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11295,10 +11305,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126836259</v>
+        <v>126836487</v>
       </c>
       <c r="B106" t="n">
-        <v>57657</v>
+        <v>79018</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11306,39 +11316,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>680665</v>
+        <v>680663</v>
       </c>
       <c r="R106" t="n">
-        <v>7087214</v>
+        <v>7087244</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11371,11 +11376,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11409,7 +11409,7 @@
         <v>126836458</v>
       </c>
       <c r="B107" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>126836353</v>
       </c>
       <c r="B108" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11608,10 +11608,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126836491</v>
+        <v>126836303</v>
       </c>
       <c r="B109" t="n">
-        <v>79014</v>
+        <v>78777</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11619,21 +11619,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11643,10 +11643,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>680645</v>
+        <v>680654</v>
       </c>
       <c r="R109" t="n">
-        <v>7087283</v>
+        <v>7087239</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11709,32 +11709,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126836462</v>
+        <v>126836507</v>
       </c>
       <c r="B110" t="n">
-        <v>79014</v>
+        <v>92620</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11744,10 +11744,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>680777</v>
+        <v>680724</v>
       </c>
       <c r="R110" t="n">
-        <v>7087215</v>
+        <v>7087106</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11810,10 +11810,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126836485</v>
+        <v>126836462</v>
       </c>
       <c r="B111" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11845,10 +11845,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>680660</v>
+        <v>680777</v>
       </c>
       <c r="R111" t="n">
-        <v>7087229</v>
+        <v>7087215</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11911,45 +11911,50 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126836355</v>
+        <v>126839946</v>
       </c>
       <c r="B112" t="n">
-        <v>79014</v>
+        <v>56853</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>680779</v>
+        <v>680662</v>
       </c>
       <c r="R112" t="n">
-        <v>7087023</v>
+        <v>7087219</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11996,12 +12001,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12012,50 +12017,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126839946</v>
+        <v>126836491</v>
       </c>
       <c r="B113" t="n">
-        <v>56849</v>
+        <v>79018</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>680662</v>
+        <v>680645</v>
       </c>
       <c r="R113" t="n">
-        <v>7087219</v>
+        <v>7087283</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12102,12 +12102,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12118,10 +12118,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126836303</v>
+        <v>126836355</v>
       </c>
       <c r="B114" t="n">
-        <v>78773</v>
+        <v>79018</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12129,21 +12129,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12153,10 +12153,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>680654</v>
+        <v>680779</v>
       </c>
       <c r="R114" t="n">
-        <v>7087239</v>
+        <v>7087023</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12219,32 +12219,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126836507</v>
+        <v>126836485</v>
       </c>
       <c r="B115" t="n">
-        <v>92616</v>
+        <v>79018</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12254,10 +12254,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>680724</v>
+        <v>680660</v>
       </c>
       <c r="R115" t="n">
-        <v>7087106</v>
+        <v>7087229</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12323,7 +12323,7 @@
         <v>126836230</v>
       </c>
       <c r="B116" t="n">
-        <v>57479</v>
+        <v>57483</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12421,10 +12421,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126836461</v>
+        <v>126836550</v>
       </c>
       <c r="B117" t="n">
-        <v>79014</v>
+        <v>78685</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12432,21 +12432,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12456,10 +12456,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>680774</v>
+        <v>680667</v>
       </c>
       <c r="R117" t="n">
-        <v>7087204</v>
+        <v>7087238</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12522,10 +12522,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126836476</v>
+        <v>126836461</v>
       </c>
       <c r="B118" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>680712</v>
+        <v>680774</v>
       </c>
       <c r="R118" t="n">
-        <v>7087209</v>
+        <v>7087204</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12623,10 +12623,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126836356</v>
+        <v>126836476</v>
       </c>
       <c r="B119" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12658,10 +12658,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>680782</v>
+        <v>680712</v>
       </c>
       <c r="R119" t="n">
-        <v>7087012</v>
+        <v>7087209</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12724,10 +12724,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126836550</v>
+        <v>126836356</v>
       </c>
       <c r="B120" t="n">
-        <v>78681</v>
+        <v>79018</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12735,21 +12735,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12759,10 +12759,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>680667</v>
+        <v>680782</v>
       </c>
       <c r="R120" t="n">
-        <v>7087238</v>
+        <v>7087012</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12825,10 +12825,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126836354</v>
+        <v>126839970</v>
       </c>
       <c r="B121" t="n">
-        <v>79014</v>
+        <v>78777</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12836,21 +12836,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>680771</v>
+        <v>680772</v>
       </c>
       <c r="R121" t="n">
-        <v>7087030</v>
+        <v>7087124</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12910,12 +12910,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -12926,10 +12926,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126836466</v>
+        <v>126836559</v>
       </c>
       <c r="B122" t="n">
-        <v>79014</v>
+        <v>91737</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12937,21 +12937,16 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12961,10 +12956,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>680756</v>
+        <v>680744</v>
       </c>
       <c r="R122" t="n">
-        <v>7087273</v>
+        <v>7087264</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13005,6 +13000,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13027,10 +13023,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126836479</v>
+        <v>126825809</v>
       </c>
       <c r="B123" t="n">
-        <v>79014</v>
+        <v>78685</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13038,34 +13034,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>680684</v>
+        <v>680666</v>
       </c>
       <c r="R123" t="n">
-        <v>7087202</v>
+        <v>7087235</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13095,9 +13091,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13112,12 +13118,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -13128,10 +13134,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126836488</v>
+        <v>126836545</v>
       </c>
       <c r="B124" t="n">
-        <v>79014</v>
+        <v>78685</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13139,21 +13145,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13163,10 +13169,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>680655</v>
+        <v>680657</v>
       </c>
       <c r="R124" t="n">
-        <v>7087246</v>
+        <v>7087201</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13229,10 +13235,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126836478</v>
+        <v>126836354</v>
       </c>
       <c r="B125" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13264,10 +13270,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>680711</v>
+        <v>680771</v>
       </c>
       <c r="R125" t="n">
-        <v>7087181</v>
+        <v>7087030</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13330,10 +13336,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126825809</v>
+        <v>126836466</v>
       </c>
       <c r="B126" t="n">
-        <v>78681</v>
+        <v>79018</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13341,34 +13347,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>680666</v>
+        <v>680756</v>
       </c>
       <c r="R126" t="n">
-        <v>7087235</v>
+        <v>7087273</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13398,19 +13404,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>10:27</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>10:27</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13425,12 +13421,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -13441,10 +13437,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126836545</v>
+        <v>126836479</v>
       </c>
       <c r="B127" t="n">
-        <v>78681</v>
+        <v>79018</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13452,21 +13448,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13476,10 +13472,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>680657</v>
+        <v>680684</v>
       </c>
       <c r="R127" t="n">
-        <v>7087201</v>
+        <v>7087202</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13542,10 +13538,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126836559</v>
+        <v>126836488</v>
       </c>
       <c r="B128" t="n">
-        <v>91733</v>
+        <v>79018</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13553,16 +13549,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13572,10 +13573,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>680744</v>
+        <v>680655</v>
       </c>
       <c r="R128" t="n">
-        <v>7087264</v>
+        <v>7087246</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13616,7 +13617,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13639,10 +13639,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126839970</v>
+        <v>126836478</v>
       </c>
       <c r="B129" t="n">
-        <v>78773</v>
+        <v>79018</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13650,21 +13650,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13674,10 +13674,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>680772</v>
+        <v>680711</v>
       </c>
       <c r="R129" t="n">
-        <v>7087124</v>
+        <v>7087181</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13724,12 +13724,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -13743,7 +13743,7 @@
         <v>126836467</v>
       </c>
       <c r="B130" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         <v>126838827</v>
       </c>
       <c r="B131" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>126838826</v>
       </c>
       <c r="B132" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>126825866</v>
       </c>
       <c r="B133" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>

--- a/artfynd/A 64499-2023 artfynd.xlsx
+++ b/artfynd/A 64499-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126836489</v>
+        <v>126836484</v>
       </c>
       <c r="B3" t="n">
         <v>79018</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680647</v>
+        <v>680665</v>
       </c>
       <c r="R3" t="n">
-        <v>7087267</v>
+        <v>7087214</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126836484</v>
+        <v>126836552</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680665</v>
+        <v>680642</v>
       </c>
       <c r="R4" t="n">
-        <v>7087214</v>
+        <v>7087273</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126838823</v>
+        <v>126836523</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,34 +1017,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680767</v>
+        <v>680728</v>
       </c>
       <c r="R5" t="n">
-        <v>7087204</v>
+        <v>7087114</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,12 +1091,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1107,45 +1107,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126825730</v>
+        <v>126836506</v>
       </c>
       <c r="B6" t="n">
-        <v>79636</v>
+        <v>92620</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680666</v>
+        <v>680723</v>
       </c>
       <c r="R6" t="n">
-        <v>7087235</v>
+        <v>7087114</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,22 +1172,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1202,12 +1192,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1218,32 +1208,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126839973</v>
+        <v>126836504</v>
       </c>
       <c r="B7" t="n">
-        <v>78777</v>
+        <v>92620</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680751</v>
+        <v>680697</v>
       </c>
       <c r="R7" t="n">
-        <v>7087100</v>
+        <v>7087147</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,12 +1293,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1319,10 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126836552</v>
+        <v>126825730</v>
       </c>
       <c r="B8" t="n">
-        <v>78685</v>
+        <v>79636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1330,34 +1320,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680642</v>
+        <v>680666</v>
       </c>
       <c r="R8" t="n">
-        <v>7087273</v>
+        <v>7087235</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,12 +1374,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,12 +1404,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1420,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126836523</v>
+        <v>126836489</v>
       </c>
       <c r="B9" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1431,21 +1431,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680728</v>
+        <v>680647</v>
       </c>
       <c r="R9" t="n">
-        <v>7087114</v>
+        <v>7087267</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,45 +1521,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126836506</v>
+        <v>126838823</v>
       </c>
       <c r="B10" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680723</v>
+        <v>680767</v>
       </c>
       <c r="R10" t="n">
-        <v>7087114</v>
+        <v>7087204</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,12 +1606,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1622,32 +1622,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126836504</v>
+        <v>126839973</v>
       </c>
       <c r="B11" t="n">
-        <v>92620</v>
+        <v>78777</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680697</v>
+        <v>680751</v>
       </c>
       <c r="R11" t="n">
-        <v>7087147</v>
+        <v>7087100</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,12 +1707,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1723,10 +1723,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126836546</v>
+        <v>126837190</v>
       </c>
       <c r="B12" t="n">
-        <v>78685</v>
+        <v>57661</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1734,34 +1734,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680660</v>
+        <v>680778</v>
       </c>
       <c r="R12" t="n">
-        <v>7087210</v>
+        <v>7087007</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,6 +1804,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1808,12 +1821,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1824,7 +1837,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126836520</v>
+        <v>126836546</v>
       </c>
       <c r="B13" t="n">
         <v>78685</v>
@@ -1859,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680716</v>
+        <v>680660</v>
       </c>
       <c r="R13" t="n">
-        <v>7087135</v>
+        <v>7087210</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,7 +1938,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126837233</v>
+        <v>126836520</v>
       </c>
       <c r="B14" t="n">
         <v>78685</v>
@@ -1960,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680698</v>
+        <v>680716</v>
       </c>
       <c r="R14" t="n">
-        <v>7087108</v>
+        <v>7087135</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,12 +2023,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2026,7 +2039,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126840004</v>
+        <v>126837233</v>
       </c>
       <c r="B15" t="n">
         <v>78685</v>
@@ -2061,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680639</v>
+        <v>680698</v>
       </c>
       <c r="R15" t="n">
-        <v>7087277</v>
+        <v>7087108</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2111,12 +2124,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2127,10 +2140,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126837083</v>
+        <v>126840004</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,34 +2151,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680743</v>
+        <v>680639</v>
       </c>
       <c r="R16" t="n">
-        <v>7087104</v>
+        <v>7087277</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2212,12 +2225,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2329,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126836555</v>
+        <v>126837083</v>
       </c>
       <c r="B18" t="n">
-        <v>78424</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2340,34 +2353,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680660</v>
+        <v>680743</v>
       </c>
       <c r="R18" t="n">
-        <v>7087210</v>
+        <v>7087104</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,12 +2427,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2430,10 +2443,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126837190</v>
+        <v>126836555</v>
       </c>
       <c r="B19" t="n">
-        <v>57661</v>
+        <v>78424</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2441,42 +2454,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680778</v>
+        <v>680660</v>
       </c>
       <c r="R19" t="n">
-        <v>7087007</v>
+        <v>7087210</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,11 +2516,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2528,12 +2528,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2544,7 +2544,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126836351</v>
+        <v>126837227</v>
       </c>
       <c r="B20" t="n">
         <v>79018</v>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680723</v>
+        <v>680693</v>
       </c>
       <c r="R20" t="n">
-        <v>7087114</v>
+        <v>7087147</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2629,12 +2629,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2645,7 +2645,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126837085</v>
+        <v>126836351</v>
       </c>
       <c r="B21" t="n">
         <v>79018</v>
@@ -2676,14 +2676,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680698</v>
+        <v>680723</v>
       </c>
       <c r="R21" t="n">
-        <v>7087214</v>
+        <v>7087114</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,12 +2730,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2746,7 +2746,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126837227</v>
+        <v>126837085</v>
       </c>
       <c r="B22" t="n">
         <v>79018</v>
@@ -2777,14 +2777,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>680693</v>
+        <v>680698</v>
       </c>
       <c r="R22" t="n">
-        <v>7087147</v>
+        <v>7087214</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2831,12 +2831,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3049,10 +3049,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126838825</v>
+        <v>126840003</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3060,34 +3060,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680759</v>
+        <v>680729</v>
       </c>
       <c r="R25" t="n">
-        <v>7087282</v>
+        <v>7087103</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3134,12 +3134,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3150,10 +3150,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126838821</v>
+        <v>126836551</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3161,34 +3161,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680775</v>
+        <v>680654</v>
       </c>
       <c r="R26" t="n">
-        <v>7087121</v>
+        <v>7087239</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,12 +3235,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3251,7 +3251,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126837228</v>
+        <v>126838825</v>
       </c>
       <c r="B27" t="n">
         <v>79018</v>
@@ -3282,14 +3282,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680658</v>
+        <v>680759</v>
       </c>
       <c r="R27" t="n">
-        <v>7087213</v>
+        <v>7087282</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,12 +3336,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3352,7 +3352,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126840000</v>
+        <v>126838821</v>
       </c>
       <c r="B28" t="n">
         <v>79018</v>
@@ -3383,14 +3383,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680643</v>
+        <v>680775</v>
       </c>
       <c r="R28" t="n">
-        <v>7087277</v>
+        <v>7087121</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3437,12 +3437,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3453,7 +3453,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126839989</v>
+        <v>126837228</v>
       </c>
       <c r="B29" t="n">
         <v>79018</v>
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680774</v>
+        <v>680658</v>
       </c>
       <c r="R29" t="n">
-        <v>7087124</v>
+        <v>7087213</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3538,12 +3538,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3655,53 +3655,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126837193</v>
+        <v>126840000</v>
       </c>
       <c r="B31" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680696</v>
+        <v>680643</v>
       </c>
       <c r="R31" t="n">
-        <v>7087170</v>
+        <v>7087277</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3736,11 +3728,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Blindtarmstömmning</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3753,12 +3740,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3769,10 +3756,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126840003</v>
+        <v>126839989</v>
       </c>
       <c r="B32" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3780,21 +3767,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3804,10 +3791,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680729</v>
+        <v>680774</v>
       </c>
       <c r="R32" t="n">
-        <v>7087103</v>
+        <v>7087124</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3870,45 +3857,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126836551</v>
+        <v>126837193</v>
       </c>
       <c r="B33" t="n">
-        <v>78685</v>
+        <v>56853</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680654</v>
+        <v>680696</v>
       </c>
       <c r="R33" t="n">
-        <v>7087239</v>
+        <v>7087170</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3943,6 +3938,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Blindtarmstömmning</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -3955,12 +3955,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3971,10 +3971,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126839997</v>
+        <v>126836543</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3982,21 +3982,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680676</v>
+        <v>680708</v>
       </c>
       <c r="R34" t="n">
-        <v>7087207</v>
+        <v>7087204</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4056,12 +4056,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4283,10 +4283,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126836543</v>
+        <v>126839997</v>
       </c>
       <c r="B37" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4294,21 +4294,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>680708</v>
+        <v>680676</v>
       </c>
       <c r="R37" t="n">
-        <v>7087204</v>
+        <v>7087207</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4368,12 +4368,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4788,10 +4788,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126836516</v>
+        <v>126839937</v>
       </c>
       <c r="B42" t="n">
-        <v>78685</v>
+        <v>79636</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4799,21 +4799,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>680654</v>
+        <v>680761</v>
       </c>
       <c r="R42" t="n">
-        <v>7087188</v>
+        <v>7087124</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4873,12 +4873,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4990,10 +4990,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126836483</v>
+        <v>126836516</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5001,21 +5001,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>680673</v>
+        <v>680654</v>
       </c>
       <c r="R44" t="n">
-        <v>7087210</v>
+        <v>7087188</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5091,10 +5091,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126839937</v>
+        <v>126836483</v>
       </c>
       <c r="B45" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5102,21 +5102,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>680761</v>
+        <v>680673</v>
       </c>
       <c r="R45" t="n">
-        <v>7087124</v>
+        <v>7087210</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5176,12 +5176,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5192,10 +5192,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126836517</v>
+        <v>126838822</v>
       </c>
       <c r="B46" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5203,34 +5203,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>680662</v>
+        <v>680783</v>
       </c>
       <c r="R46" t="n">
-        <v>7087179</v>
+        <v>7087170</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5277,12 +5277,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5293,10 +5293,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126836548</v>
+        <v>126836338</v>
       </c>
       <c r="B47" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5304,21 +5304,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5328,10 +5328,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>680662</v>
+        <v>680648</v>
       </c>
       <c r="R47" t="n">
-        <v>7087231</v>
+        <v>7087260</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5394,10 +5394,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126838822</v>
+        <v>126836198</v>
       </c>
       <c r="B48" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5405,34 +5405,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>680783</v>
+        <v>680721</v>
       </c>
       <c r="R48" t="n">
-        <v>7087170</v>
+        <v>7087133</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5479,12 +5479,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5495,7 +5495,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126836338</v>
+        <v>126839998</v>
       </c>
       <c r="B49" t="n">
         <v>79018</v>
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>680648</v>
+        <v>680673</v>
       </c>
       <c r="R49" t="n">
-        <v>7087260</v>
+        <v>7087211</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5580,12 +5580,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5596,7 +5596,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126839998</v>
+        <v>126837223</v>
       </c>
       <c r="B50" t="n">
         <v>79018</v>
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>680673</v>
+        <v>680772</v>
       </c>
       <c r="R50" t="n">
-        <v>7087211</v>
+        <v>7087024</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5681,12 +5681,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5697,32 +5697,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126837223</v>
+        <v>126839976</v>
       </c>
       <c r="B51" t="n">
-        <v>79018</v>
+        <v>58031</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>680772</v>
+        <v>680693</v>
       </c>
       <c r="R51" t="n">
-        <v>7087024</v>
+        <v>7087162</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5782,12 +5782,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5798,10 +5798,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126836198</v>
+        <v>126836548</v>
       </c>
       <c r="B52" t="n">
-        <v>79636</v>
+        <v>78685</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5809,21 +5809,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5833,10 +5833,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>680721</v>
+        <v>680662</v>
       </c>
       <c r="R52" t="n">
-        <v>7087133</v>
+        <v>7087231</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5899,32 +5899,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126839976</v>
+        <v>126836517</v>
       </c>
       <c r="B53" t="n">
-        <v>58031</v>
+        <v>78685</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103015</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5934,10 +5934,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>680693</v>
+        <v>680662</v>
       </c>
       <c r="R53" t="n">
-        <v>7087162</v>
+        <v>7087179</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5984,12 +5984,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6000,45 +6000,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126836519</v>
+        <v>126839949</v>
       </c>
       <c r="B54" t="n">
-        <v>78685</v>
+        <v>56853</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>680693</v>
+        <v>680726</v>
       </c>
       <c r="R54" t="n">
-        <v>7087159</v>
+        <v>7087219</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6085,12 +6090,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6101,7 +6106,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126837234</v>
+        <v>126836519</v>
       </c>
       <c r="B55" t="n">
         <v>78685</v>
@@ -6136,10 +6141,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>680694</v>
+        <v>680693</v>
       </c>
       <c r="R55" t="n">
-        <v>7087158</v>
+        <v>7087159</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6186,12 +6191,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6303,10 +6308,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126839996</v>
+        <v>126837234</v>
       </c>
       <c r="B57" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6314,21 +6319,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6338,10 +6343,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>680745</v>
+        <v>680694</v>
       </c>
       <c r="R57" t="n">
-        <v>7087170</v>
+        <v>7087158</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6388,12 +6393,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6404,7 +6409,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126836486</v>
+        <v>126836469</v>
       </c>
       <c r="B58" t="n">
         <v>79018</v>
@@ -6439,10 +6444,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>680663</v>
+        <v>680728</v>
       </c>
       <c r="R58" t="n">
-        <v>7087231</v>
+        <v>7087278</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6505,10 +6510,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126836490</v>
+        <v>126840919</v>
       </c>
       <c r="B59" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6516,34 +6521,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>680645</v>
+        <v>680640</v>
       </c>
       <c r="R59" t="n">
-        <v>7087280</v>
+        <v>7087261</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6573,29 +6581,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6606,7 +6625,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126837225</v>
+        <v>126839996</v>
       </c>
       <c r="B60" t="n">
         <v>79018</v>
@@ -6641,10 +6660,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>680729</v>
+        <v>680745</v>
       </c>
       <c r="R60" t="n">
-        <v>7087081</v>
+        <v>7087170</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6691,12 +6710,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6707,7 +6726,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126836469</v>
+        <v>126836490</v>
       </c>
       <c r="B61" t="n">
         <v>79018</v>
@@ -6742,10 +6761,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>680728</v>
+        <v>680645</v>
       </c>
       <c r="R61" t="n">
-        <v>7087278</v>
+        <v>7087280</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6808,50 +6827,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126839949</v>
+        <v>126837225</v>
       </c>
       <c r="B62" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>680726</v>
+        <v>680729</v>
       </c>
       <c r="R62" t="n">
-        <v>7087219</v>
+        <v>7087081</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6898,12 +6912,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6914,10 +6928,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126840919</v>
+        <v>126836486</v>
       </c>
       <c r="B63" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6925,37 +6939,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>680640</v>
+        <v>680663</v>
       </c>
       <c r="R63" t="n">
-        <v>7087261</v>
+        <v>7087231</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6985,40 +6996,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>10:17</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>10:17</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7029,10 +7029,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126836302</v>
+        <v>126836542</v>
       </c>
       <c r="B64" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7040,21 +7040,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>680677</v>
+        <v>680710</v>
       </c>
       <c r="R64" t="n">
-        <v>7087201</v>
+        <v>7087232</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7130,10 +7130,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126839938</v>
+        <v>126836515</v>
       </c>
       <c r="B65" t="n">
-        <v>79636</v>
+        <v>78685</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7141,21 +7141,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7165,10 +7165,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>680652</v>
+        <v>680644</v>
       </c>
       <c r="R65" t="n">
-        <v>7087271</v>
+        <v>7087195</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7215,12 +7215,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7231,45 +7231,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126838804</v>
+        <v>126837038</v>
       </c>
       <c r="B66" t="n">
-        <v>78776</v>
+        <v>91295</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>680765</v>
+        <v>680783</v>
       </c>
       <c r="R66" t="n">
-        <v>7087124</v>
+        <v>7087069</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7316,12 +7316,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7332,10 +7332,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126836542</v>
+        <v>126839938</v>
       </c>
       <c r="B67" t="n">
-        <v>78685</v>
+        <v>79636</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7343,21 +7343,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>680710</v>
+        <v>680652</v>
       </c>
       <c r="R67" t="n">
-        <v>7087232</v>
+        <v>7087271</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7417,12 +7417,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7433,10 +7433,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126836515</v>
+        <v>126838804</v>
       </c>
       <c r="B68" t="n">
-        <v>78685</v>
+        <v>78776</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7444,34 +7444,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>680644</v>
+        <v>680765</v>
       </c>
       <c r="R68" t="n">
-        <v>7087195</v>
+        <v>7087124</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7518,12 +7518,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7736,45 +7736,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126837038</v>
+        <v>126836302</v>
       </c>
       <c r="B71" t="n">
-        <v>91295</v>
+        <v>78777</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>680783</v>
+        <v>680677</v>
       </c>
       <c r="R71" t="n">
-        <v>7087069</v>
+        <v>7087201</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7821,12 +7821,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7837,10 +7837,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126837052</v>
+        <v>126840002</v>
       </c>
       <c r="B72" t="n">
-        <v>57821</v>
+        <v>78685</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7848,34 +7848,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>680740</v>
+        <v>680724</v>
       </c>
       <c r="R72" t="n">
-        <v>7087222</v>
+        <v>7087119</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7922,12 +7922,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7938,10 +7938,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126837069</v>
+        <v>126836544</v>
       </c>
       <c r="B73" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7949,34 +7949,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>680673</v>
+        <v>680681</v>
       </c>
       <c r="R73" t="n">
-        <v>7087276</v>
+        <v>7087195</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8023,12 +8023,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8039,7 +8039,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126840002</v>
+        <v>126836524</v>
       </c>
       <c r="B74" t="n">
         <v>78685</v>
@@ -8074,10 +8074,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>680724</v>
+        <v>680720</v>
       </c>
       <c r="R74" t="n">
-        <v>7087119</v>
+        <v>7087100</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8124,12 +8124,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8140,10 +8140,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126836524</v>
+        <v>126836475</v>
       </c>
       <c r="B75" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8151,21 +8151,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>680720</v>
+        <v>680708</v>
       </c>
       <c r="R75" t="n">
-        <v>7087100</v>
+        <v>7087220</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8241,10 +8241,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126836544</v>
+        <v>126836336</v>
       </c>
       <c r="B76" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8252,21 +8252,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8276,10 +8276,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>680681</v>
+        <v>680653</v>
       </c>
       <c r="R76" t="n">
-        <v>7087195</v>
+        <v>7087252</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8342,7 +8342,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126836473</v>
+        <v>126836464</v>
       </c>
       <c r="B77" t="n">
         <v>79018</v>
@@ -8377,10 +8377,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>680710</v>
+        <v>680772</v>
       </c>
       <c r="R77" t="n">
-        <v>7087232</v>
+        <v>7087252</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8443,7 +8443,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126839999</v>
+        <v>126836473</v>
       </c>
       <c r="B78" t="n">
         <v>79018</v>
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>680651</v>
+        <v>680710</v>
       </c>
       <c r="R78" t="n">
-        <v>7087231</v>
+        <v>7087232</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8528,12 +8528,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8544,7 +8544,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126836475</v>
+        <v>126839999</v>
       </c>
       <c r="B79" t="n">
         <v>79018</v>
@@ -8579,10 +8579,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>680708</v>
+        <v>680651</v>
       </c>
       <c r="R79" t="n">
-        <v>7087220</v>
+        <v>7087231</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8629,12 +8629,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8645,10 +8645,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126836336</v>
+        <v>126837052</v>
       </c>
       <c r="B80" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8656,34 +8656,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>680653</v>
+        <v>680740</v>
       </c>
       <c r="R80" t="n">
-        <v>7087252</v>
+        <v>7087222</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8730,12 +8730,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8746,10 +8746,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126836464</v>
+        <v>126837069</v>
       </c>
       <c r="B81" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8757,34 +8757,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>680772</v>
+        <v>680673</v>
       </c>
       <c r="R81" t="n">
-        <v>7087252</v>
+        <v>7087276</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8831,12 +8831,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8847,10 +8847,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126837053</v>
+        <v>126836472</v>
       </c>
       <c r="B82" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8858,34 +8858,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>680770</v>
+        <v>680714</v>
       </c>
       <c r="R82" t="n">
-        <v>7087092</v>
+        <v>7087268</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8932,12 +8932,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -8948,7 +8948,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126836472</v>
+        <v>126836470</v>
       </c>
       <c r="B83" t="n">
         <v>79018</v>
@@ -8983,10 +8983,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>680714</v>
+        <v>680718</v>
       </c>
       <c r="R83" t="n">
-        <v>7087268</v>
+        <v>7087288</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9049,7 +9049,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126836470</v>
+        <v>126836468</v>
       </c>
       <c r="B84" t="n">
         <v>79018</v>
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>680718</v>
+        <v>680752</v>
       </c>
       <c r="R84" t="n">
-        <v>7087288</v>
+        <v>7087262</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9150,10 +9150,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126836468</v>
+        <v>126837053</v>
       </c>
       <c r="B85" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9161,34 +9161,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>680752</v>
+        <v>680770</v>
       </c>
       <c r="R85" t="n">
-        <v>7087262</v>
+        <v>7087092</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9235,12 +9235,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9352,10 +9352,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126836481</v>
+        <v>126836309</v>
       </c>
       <c r="B87" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9363,21 +9363,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9387,10 +9387,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>680670</v>
+        <v>680720</v>
       </c>
       <c r="R87" t="n">
-        <v>7087199</v>
+        <v>7087133</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9453,10 +9453,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126837231</v>
+        <v>126836199</v>
       </c>
       <c r="B88" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9464,21 +9464,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9488,10 +9488,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>680642</v>
+        <v>680719</v>
       </c>
       <c r="R88" t="n">
-        <v>7087222</v>
+        <v>7087133</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9538,12 +9538,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9554,10 +9554,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126836480</v>
+        <v>126840864</v>
       </c>
       <c r="B89" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9565,34 +9565,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>680660</v>
+        <v>680671</v>
       </c>
       <c r="R89" t="n">
-        <v>7087210</v>
+        <v>7087236</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9622,29 +9625,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9655,7 +9669,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126836357</v>
+        <v>126836481</v>
       </c>
       <c r="B90" t="n">
         <v>79018</v>
@@ -9690,10 +9704,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>680784</v>
+        <v>680670</v>
       </c>
       <c r="R90" t="n">
-        <v>7087010</v>
+        <v>7087199</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9756,7 +9770,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126837082</v>
+        <v>126837231</v>
       </c>
       <c r="B91" t="n">
         <v>79018</v>
@@ -9787,14 +9801,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>680771</v>
+        <v>680642</v>
       </c>
       <c r="R91" t="n">
-        <v>7087091</v>
+        <v>7087222</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9841,12 +9855,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -9857,7 +9871,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126839992</v>
+        <v>126836480</v>
       </c>
       <c r="B92" t="n">
         <v>79018</v>
@@ -9892,10 +9906,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>680767</v>
+        <v>680660</v>
       </c>
       <c r="R92" t="n">
-        <v>7087114</v>
+        <v>7087210</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9942,12 +9956,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -9958,10 +9972,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126836309</v>
+        <v>126836357</v>
       </c>
       <c r="B93" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9969,21 +9983,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9993,10 +10007,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>680720</v>
+        <v>680784</v>
       </c>
       <c r="R93" t="n">
-        <v>7087133</v>
+        <v>7087010</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10059,10 +10073,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126836199</v>
+        <v>126837082</v>
       </c>
       <c r="B94" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10070,34 +10084,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>680719</v>
+        <v>680771</v>
       </c>
       <c r="R94" t="n">
-        <v>7087133</v>
+        <v>7087091</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10144,12 +10158,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10160,10 +10174,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126840864</v>
+        <v>126839992</v>
       </c>
       <c r="B95" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10171,37 +10185,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>680671</v>
+        <v>680767</v>
       </c>
       <c r="R95" t="n">
-        <v>7087236</v>
+        <v>7087114</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10231,40 +10242,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10275,32 +10275,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126836226</v>
+        <v>126836505</v>
       </c>
       <c r="B96" t="n">
-        <v>91330</v>
+        <v>92620</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10310,10 +10310,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>680802</v>
+        <v>680711</v>
       </c>
       <c r="R96" t="n">
-        <v>7086993</v>
+        <v>7087139</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10376,32 +10376,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126836505</v>
+        <v>126836226</v>
       </c>
       <c r="B97" t="n">
-        <v>92620</v>
+        <v>91330</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10411,10 +10411,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>680711</v>
+        <v>680802</v>
       </c>
       <c r="R97" t="n">
-        <v>7087139</v>
+        <v>7086993</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10790,10 +10790,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126836259</v>
+        <v>126836487</v>
       </c>
       <c r="B101" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10801,39 +10801,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>680665</v>
+        <v>680663</v>
       </c>
       <c r="R101" t="n">
-        <v>7087214</v>
+        <v>7087244</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10866,11 +10861,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10901,7 +10891,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126836522</v>
+        <v>126837236</v>
       </c>
       <c r="B102" t="n">
         <v>78685</v>
@@ -10936,10 +10926,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>680726</v>
+        <v>680673</v>
       </c>
       <c r="R102" t="n">
-        <v>7087132</v>
+        <v>7087186</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10986,12 +10976,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11002,10 +10992,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126837236</v>
+        <v>126836242</v>
       </c>
       <c r="B103" t="n">
-        <v>78685</v>
+        <v>91280</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11013,21 +11003,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>353</v>
+        <v>112</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11037,10 +11027,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>680673</v>
+        <v>680744</v>
       </c>
       <c r="R103" t="n">
-        <v>7087186</v>
+        <v>7087264</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11087,12 +11077,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11103,10 +11093,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126836242</v>
+        <v>126836522</v>
       </c>
       <c r="B104" t="n">
-        <v>91280</v>
+        <v>78685</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11114,21 +11104,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>112</v>
+        <v>353</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11138,10 +11128,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>680744</v>
+        <v>680726</v>
       </c>
       <c r="R104" t="n">
-        <v>7087264</v>
+        <v>7087132</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11305,10 +11295,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126836487</v>
+        <v>126836259</v>
       </c>
       <c r="B106" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11316,34 +11306,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>680663</v>
+        <v>680665</v>
       </c>
       <c r="R106" t="n">
-        <v>7087244</v>
+        <v>7087214</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11376,6 +11371,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11608,32 +11608,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126836303</v>
+        <v>126836230</v>
       </c>
       <c r="B109" t="n">
-        <v>78777</v>
+        <v>57483</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>102976</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11643,10 +11643,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>680654</v>
+        <v>680774</v>
       </c>
       <c r="R109" t="n">
-        <v>7087239</v>
+        <v>7087234</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11810,7 +11810,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126836462</v>
+        <v>126836491</v>
       </c>
       <c r="B111" t="n">
         <v>79018</v>
@@ -11845,10 +11845,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>680777</v>
+        <v>680645</v>
       </c>
       <c r="R111" t="n">
-        <v>7087215</v>
+        <v>7087283</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11911,50 +11911,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126839946</v>
+        <v>126836462</v>
       </c>
       <c r="B112" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>680662</v>
+        <v>680777</v>
       </c>
       <c r="R112" t="n">
-        <v>7087219</v>
+        <v>7087215</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12001,12 +11996,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12017,7 +12012,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126836491</v>
+        <v>126836485</v>
       </c>
       <c r="B113" t="n">
         <v>79018</v>
@@ -12052,10 +12047,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>680645</v>
+        <v>680660</v>
       </c>
       <c r="R113" t="n">
-        <v>7087283</v>
+        <v>7087229</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12219,45 +12214,50 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126836485</v>
+        <v>126839946</v>
       </c>
       <c r="B115" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>680660</v>
+        <v>680662</v>
       </c>
       <c r="R115" t="n">
-        <v>7087229</v>
+        <v>7087219</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12304,12 +12304,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12320,32 +12320,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126836230</v>
+        <v>126836303</v>
       </c>
       <c r="B116" t="n">
-        <v>57483</v>
+        <v>78777</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>102976</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12355,10 +12355,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>680774</v>
+        <v>680654</v>
       </c>
       <c r="R116" t="n">
-        <v>7087234</v>
+        <v>7087239</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12825,10 +12825,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126839970</v>
+        <v>126836559</v>
       </c>
       <c r="B121" t="n">
-        <v>78777</v>
+        <v>91737</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12836,21 +12836,16 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12860,10 +12855,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>680772</v>
+        <v>680744</v>
       </c>
       <c r="R121" t="n">
-        <v>7087124</v>
+        <v>7087264</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12904,18 +12899,19 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -12926,10 +12922,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126836559</v>
+        <v>126839970</v>
       </c>
       <c r="B122" t="n">
-        <v>91737</v>
+        <v>78777</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12937,16 +12933,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6040186</v>
+        <v>228912</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12956,10 +12957,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>680744</v>
+        <v>680772</v>
       </c>
       <c r="R122" t="n">
-        <v>7087264</v>
+        <v>7087124</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13000,19 +13001,18 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -13023,7 +13023,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126825809</v>
+        <v>126836545</v>
       </c>
       <c r="B123" t="n">
         <v>78685</v>
@@ -13054,14 +13054,14 @@
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>680666</v>
+        <v>680657</v>
       </c>
       <c r="R123" t="n">
-        <v>7087235</v>
+        <v>7087201</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13091,19 +13091,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>10:27</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>10:27</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13118,12 +13108,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -13134,7 +13124,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126836545</v>
+        <v>126825809</v>
       </c>
       <c r="B124" t="n">
         <v>78685</v>
@@ -13165,14 +13155,14 @@
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>680657</v>
+        <v>680666</v>
       </c>
       <c r="R124" t="n">
-        <v>7087201</v>
+        <v>7087235</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13202,9 +13192,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13219,12 +13219,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">

--- a/artfynd/A 64499-2023 artfynd.xlsx
+++ b/artfynd/A 64499-2023 artfynd.xlsx
@@ -4072,53 +4072,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126837192</v>
+        <v>126836460</v>
       </c>
       <c r="B35" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>680665</v>
+        <v>680779</v>
       </c>
       <c r="R35" t="n">
-        <v>7087191</v>
+        <v>7087200</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4153,11 +4145,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4170,12 +4157,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4186,10 +4173,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126838798</v>
+        <v>126836463</v>
       </c>
       <c r="B36" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4197,34 +4184,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>680781</v>
+        <v>680773</v>
       </c>
       <c r="R36" t="n">
-        <v>7087170</v>
+        <v>7087233</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4271,19 +4258,23 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126839997</v>
+        <v>126836477</v>
       </c>
       <c r="B37" t="n">
         <v>79018</v>
@@ -4318,10 +4309,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>680676</v>
+        <v>680709</v>
       </c>
       <c r="R37" t="n">
-        <v>7087207</v>
+        <v>7087204</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4368,12 +4359,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4384,10 +4375,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126837084</v>
+        <v>126838798</v>
       </c>
       <c r="B38" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4395,34 +4386,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>680731</v>
+        <v>680781</v>
       </c>
       <c r="R38" t="n">
-        <v>7087201</v>
+        <v>7087170</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4469,23 +4460,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126836460</v>
+        <v>126839997</v>
       </c>
       <c r="B39" t="n">
         <v>79018</v>
@@ -4520,10 +4507,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>680779</v>
+        <v>680676</v>
       </c>
       <c r="R39" t="n">
-        <v>7087200</v>
+        <v>7087207</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4570,12 +4557,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4586,7 +4573,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126836463</v>
+        <v>126837084</v>
       </c>
       <c r="B40" t="n">
         <v>79018</v>
@@ -4617,14 +4604,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>680773</v>
+        <v>680731</v>
       </c>
       <c r="R40" t="n">
-        <v>7087233</v>
+        <v>7087201</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4671,12 +4658,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4687,45 +4674,53 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126836477</v>
+        <v>126837192</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>680709</v>
+        <v>680665</v>
       </c>
       <c r="R41" t="n">
-        <v>7087204</v>
+        <v>7087191</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4760,6 +4755,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4772,12 +4772,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -7231,45 +7231,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126837038</v>
+        <v>126839938</v>
       </c>
       <c r="B66" t="n">
-        <v>91295</v>
+        <v>79636</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>680783</v>
+        <v>680652</v>
       </c>
       <c r="R66" t="n">
-        <v>7087069</v>
+        <v>7087271</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7316,12 +7316,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7332,10 +7332,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126839938</v>
+        <v>126836474</v>
       </c>
       <c r="B67" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7343,21 +7343,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>680652</v>
+        <v>680712</v>
       </c>
       <c r="R67" t="n">
-        <v>7087271</v>
+        <v>7087225</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7417,12 +7417,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7534,7 +7534,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126836474</v>
+        <v>126836482</v>
       </c>
       <c r="B69" t="n">
         <v>79018</v>
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>680712</v>
+        <v>680673</v>
       </c>
       <c r="R69" t="n">
-        <v>7087225</v>
+        <v>7087202</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7635,45 +7635,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126836482</v>
+        <v>126837038</v>
       </c>
       <c r="B70" t="n">
-        <v>79018</v>
+        <v>91295</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>680673</v>
+        <v>680783</v>
       </c>
       <c r="R70" t="n">
-        <v>7087202</v>
+        <v>7087069</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7720,12 +7720,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -11608,32 +11608,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126836230</v>
+        <v>126836491</v>
       </c>
       <c r="B109" t="n">
-        <v>57483</v>
+        <v>79018</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11643,10 +11643,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>680774</v>
+        <v>680645</v>
       </c>
       <c r="R109" t="n">
-        <v>7087234</v>
+        <v>7087283</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11709,32 +11709,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126836507</v>
+        <v>126836462</v>
       </c>
       <c r="B110" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11744,10 +11744,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>680724</v>
+        <v>680777</v>
       </c>
       <c r="R110" t="n">
-        <v>7087106</v>
+        <v>7087215</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11810,7 +11810,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126836491</v>
+        <v>126836485</v>
       </c>
       <c r="B111" t="n">
         <v>79018</v>
@@ -11845,10 +11845,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>680645</v>
+        <v>680660</v>
       </c>
       <c r="R111" t="n">
-        <v>7087283</v>
+        <v>7087229</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11911,32 +11911,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126836462</v>
+        <v>126836230</v>
       </c>
       <c r="B112" t="n">
-        <v>79018</v>
+        <v>57483</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11946,10 +11946,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>680777</v>
+        <v>680774</v>
       </c>
       <c r="R112" t="n">
-        <v>7087215</v>
+        <v>7087234</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12012,32 +12012,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126836485</v>
+        <v>126836507</v>
       </c>
       <c r="B113" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>680660</v>
+        <v>680724</v>
       </c>
       <c r="R113" t="n">
-        <v>7087229</v>
+        <v>7087106</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12825,10 +12825,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126836559</v>
+        <v>126836354</v>
       </c>
       <c r="B121" t="n">
-        <v>91737</v>
+        <v>79018</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12836,16 +12836,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12855,10 +12860,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>680744</v>
+        <v>680771</v>
       </c>
       <c r="R121" t="n">
-        <v>7087264</v>
+        <v>7087030</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12899,7 +12904,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12922,10 +12926,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126839970</v>
+        <v>126836466</v>
       </c>
       <c r="B122" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12933,21 +12937,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12957,10 +12961,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>680772</v>
+        <v>680756</v>
       </c>
       <c r="R122" t="n">
-        <v>7087124</v>
+        <v>7087273</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13007,12 +13011,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -13023,10 +13027,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126836545</v>
+        <v>126836479</v>
       </c>
       <c r="B123" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13034,21 +13038,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13058,10 +13062,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>680657</v>
+        <v>680684</v>
       </c>
       <c r="R123" t="n">
-        <v>7087201</v>
+        <v>7087202</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13124,10 +13128,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126825809</v>
+        <v>126836488</v>
       </c>
       <c r="B124" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13135,34 +13139,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>680666</v>
+        <v>680655</v>
       </c>
       <c r="R124" t="n">
-        <v>7087235</v>
+        <v>7087246</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13192,19 +13196,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>10:27</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>10:27</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13219,12 +13213,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13235,7 +13229,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126836354</v>
+        <v>126836478</v>
       </c>
       <c r="B125" t="n">
         <v>79018</v>
@@ -13270,10 +13264,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>680771</v>
+        <v>680711</v>
       </c>
       <c r="R125" t="n">
-        <v>7087030</v>
+        <v>7087181</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13336,10 +13330,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126836466</v>
+        <v>126836545</v>
       </c>
       <c r="B126" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13347,21 +13341,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13371,10 +13365,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>680756</v>
+        <v>680657</v>
       </c>
       <c r="R126" t="n">
-        <v>7087273</v>
+        <v>7087201</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13437,10 +13431,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126836479</v>
+        <v>126825809</v>
       </c>
       <c r="B127" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13448,34 +13442,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>680684</v>
+        <v>680666</v>
       </c>
       <c r="R127" t="n">
-        <v>7087202</v>
+        <v>7087235</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13505,9 +13499,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13522,12 +13526,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13538,10 +13542,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126836488</v>
+        <v>126839970</v>
       </c>
       <c r="B128" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13549,21 +13553,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13573,10 +13577,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>680655</v>
+        <v>680772</v>
       </c>
       <c r="R128" t="n">
-        <v>7087246</v>
+        <v>7087124</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13623,12 +13627,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -13639,10 +13643,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126836478</v>
+        <v>126836559</v>
       </c>
       <c r="B129" t="n">
-        <v>79018</v>
+        <v>91737</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13650,21 +13654,16 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13674,10 +13673,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>680711</v>
+        <v>680744</v>
       </c>
       <c r="R129" t="n">
-        <v>7087181</v>
+        <v>7087264</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13718,6 +13717,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64499-2023 artfynd.xlsx
+++ b/artfynd/A 64499-2023 artfynd.xlsx
@@ -3453,10 +3453,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126837228</v>
+        <v>126839971</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3464,21 +3464,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680658</v>
+        <v>680772</v>
       </c>
       <c r="R29" t="n">
-        <v>7087213</v>
+        <v>7087124</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3538,12 +3538,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3554,10 +3554,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126839971</v>
+        <v>126840000</v>
       </c>
       <c r="B30" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3565,21 +3565,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680772</v>
+        <v>680643</v>
       </c>
       <c r="R30" t="n">
-        <v>7087124</v>
+        <v>7087277</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3655,7 +3655,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126840000</v>
+        <v>126839989</v>
       </c>
       <c r="B31" t="n">
         <v>79018</v>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680643</v>
+        <v>680774</v>
       </c>
       <c r="R31" t="n">
-        <v>7087277</v>
+        <v>7087124</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3756,45 +3756,53 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126839989</v>
+        <v>126837193</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680774</v>
+        <v>680696</v>
       </c>
       <c r="R32" t="n">
-        <v>7087124</v>
+        <v>7087170</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3829,6 +3837,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Blindtarmstömmning</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3841,12 +3854,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3857,53 +3870,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126837193</v>
+        <v>126837228</v>
       </c>
       <c r="B33" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680696</v>
+        <v>680658</v>
       </c>
       <c r="R33" t="n">
-        <v>7087170</v>
+        <v>7087213</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3936,11 +3941,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Blindtarmstömmning</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4788,10 +4788,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126839937</v>
+        <v>126836516</v>
       </c>
       <c r="B42" t="n">
-        <v>79636</v>
+        <v>78685</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4799,21 +4799,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>680761</v>
+        <v>680654</v>
       </c>
       <c r="R42" t="n">
-        <v>7087124</v>
+        <v>7087188</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4873,12 +4873,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4889,10 +4889,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126839994</v>
+        <v>126839937</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4900,21 +4900,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>680650</v>
+        <v>680761</v>
       </c>
       <c r="R43" t="n">
-        <v>7087238</v>
+        <v>7087124</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4990,10 +4990,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126836516</v>
+        <v>126839994</v>
       </c>
       <c r="B44" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5001,21 +5001,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>680654</v>
+        <v>680650</v>
       </c>
       <c r="R44" t="n">
-        <v>7087188</v>
+        <v>7087238</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5075,12 +5075,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5192,10 +5192,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126838822</v>
+        <v>126836517</v>
       </c>
       <c r="B46" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5203,34 +5203,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>680783</v>
+        <v>680662</v>
       </c>
       <c r="R46" t="n">
-        <v>7087170</v>
+        <v>7087179</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5277,12 +5277,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5293,7 +5293,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126836338</v>
+        <v>126838822</v>
       </c>
       <c r="B47" t="n">
         <v>79018</v>
@@ -5324,14 +5324,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>680648</v>
+        <v>680783</v>
       </c>
       <c r="R47" t="n">
-        <v>7087260</v>
+        <v>7087170</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5378,12 +5378,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5394,10 +5394,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126836198</v>
+        <v>126836338</v>
       </c>
       <c r="B48" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5405,21 +5405,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>680721</v>
+        <v>680648</v>
       </c>
       <c r="R48" t="n">
-        <v>7087133</v>
+        <v>7087260</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5495,10 +5495,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126839998</v>
+        <v>126836198</v>
       </c>
       <c r="B49" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5506,21 +5506,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>680673</v>
+        <v>680721</v>
       </c>
       <c r="R49" t="n">
-        <v>7087211</v>
+        <v>7087133</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5580,12 +5580,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5596,7 +5596,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126837223</v>
+        <v>126839998</v>
       </c>
       <c r="B50" t="n">
         <v>79018</v>
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>680772</v>
+        <v>680673</v>
       </c>
       <c r="R50" t="n">
-        <v>7087024</v>
+        <v>7087211</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5681,12 +5681,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5697,32 +5697,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126839976</v>
+        <v>126837223</v>
       </c>
       <c r="B51" t="n">
-        <v>58031</v>
+        <v>79018</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>680693</v>
+        <v>680772</v>
       </c>
       <c r="R51" t="n">
-        <v>7087162</v>
+        <v>7087024</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5782,12 +5782,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5798,32 +5798,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126836548</v>
+        <v>126839976</v>
       </c>
       <c r="B52" t="n">
-        <v>78685</v>
+        <v>58031</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>103015</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5833,10 +5833,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>680662</v>
+        <v>680693</v>
       </c>
       <c r="R52" t="n">
-        <v>7087231</v>
+        <v>7087162</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5883,12 +5883,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5899,7 +5899,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126836517</v>
+        <v>126836548</v>
       </c>
       <c r="B53" t="n">
         <v>78685</v>
@@ -5937,7 +5937,7 @@
         <v>680662</v>
       </c>
       <c r="R53" t="n">
-        <v>7087179</v>
+        <v>7087231</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6000,50 +6000,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126839949</v>
+        <v>126836519</v>
       </c>
       <c r="B54" t="n">
-        <v>56853</v>
+        <v>78685</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>680726</v>
+        <v>680693</v>
       </c>
       <c r="R54" t="n">
-        <v>7087219</v>
+        <v>7087159</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6090,12 +6085,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6106,7 +6101,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126836519</v>
+        <v>126836541</v>
       </c>
       <c r="B55" t="n">
         <v>78685</v>
@@ -6141,10 +6136,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>680693</v>
+        <v>680708</v>
       </c>
       <c r="R55" t="n">
-        <v>7087159</v>
+        <v>7087251</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6207,7 +6202,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126836541</v>
+        <v>126837234</v>
       </c>
       <c r="B56" t="n">
         <v>78685</v>
@@ -6242,10 +6237,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>680708</v>
+        <v>680694</v>
       </c>
       <c r="R56" t="n">
-        <v>7087251</v>
+        <v>7087158</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6292,12 +6287,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6308,10 +6303,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126837234</v>
+        <v>126836490</v>
       </c>
       <c r="B57" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6319,21 +6314,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6343,10 +6338,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>680694</v>
+        <v>680645</v>
       </c>
       <c r="R57" t="n">
-        <v>7087158</v>
+        <v>7087280</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6393,12 +6388,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6409,7 +6404,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126836469</v>
+        <v>126837225</v>
       </c>
       <c r="B58" t="n">
         <v>79018</v>
@@ -6444,10 +6439,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>680728</v>
+        <v>680729</v>
       </c>
       <c r="R58" t="n">
-        <v>7087278</v>
+        <v>7087081</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6494,12 +6489,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6510,10 +6505,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126840919</v>
+        <v>126836469</v>
       </c>
       <c r="B59" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6521,37 +6516,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>680640</v>
+        <v>680728</v>
       </c>
       <c r="R59" t="n">
-        <v>7087261</v>
+        <v>7087278</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6581,40 +6573,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>10:17</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>10:17</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6726,10 +6707,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126836490</v>
+        <v>126840919</v>
       </c>
       <c r="B61" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6737,34 +6718,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>680645</v>
+        <v>680640</v>
       </c>
       <c r="R61" t="n">
-        <v>7087280</v>
+        <v>7087261</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6794,29 +6778,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6827,7 +6822,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126837225</v>
+        <v>126836486</v>
       </c>
       <c r="B62" t="n">
         <v>79018</v>
@@ -6862,10 +6857,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>680729</v>
+        <v>680663</v>
       </c>
       <c r="R62" t="n">
-        <v>7087081</v>
+        <v>7087231</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6912,12 +6907,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6928,45 +6923,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126836486</v>
+        <v>126839949</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>680663</v>
+        <v>680726</v>
       </c>
       <c r="R63" t="n">
-        <v>7087231</v>
+        <v>7087219</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7013,12 +7013,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7231,45 +7231,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126839938</v>
+        <v>126837038</v>
       </c>
       <c r="B66" t="n">
-        <v>79636</v>
+        <v>91295</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>680652</v>
+        <v>680783</v>
       </c>
       <c r="R66" t="n">
-        <v>7087271</v>
+        <v>7087069</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7316,12 +7316,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7332,10 +7332,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126836474</v>
+        <v>126839938</v>
       </c>
       <c r="B67" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7343,21 +7343,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>680712</v>
+        <v>680652</v>
       </c>
       <c r="R67" t="n">
-        <v>7087225</v>
+        <v>7087271</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7417,12 +7417,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7534,7 +7534,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126836482</v>
+        <v>126836474</v>
       </c>
       <c r="B69" t="n">
         <v>79018</v>
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>680673</v>
+        <v>680712</v>
       </c>
       <c r="R69" t="n">
-        <v>7087202</v>
+        <v>7087225</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7635,45 +7635,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126837038</v>
+        <v>126836482</v>
       </c>
       <c r="B70" t="n">
-        <v>91295</v>
+        <v>79018</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>680783</v>
+        <v>680673</v>
       </c>
       <c r="R70" t="n">
-        <v>7087069</v>
+        <v>7087202</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7720,12 +7720,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7837,10 +7837,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126840002</v>
+        <v>126837052</v>
       </c>
       <c r="B72" t="n">
-        <v>78685</v>
+        <v>57821</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7848,34 +7848,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>680724</v>
+        <v>680740</v>
       </c>
       <c r="R72" t="n">
-        <v>7087119</v>
+        <v>7087222</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7922,12 +7922,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7938,7 +7938,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126836544</v>
+        <v>126840002</v>
       </c>
       <c r="B73" t="n">
         <v>78685</v>
@@ -7973,10 +7973,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>680681</v>
+        <v>680724</v>
       </c>
       <c r="R73" t="n">
-        <v>7087195</v>
+        <v>7087119</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8023,12 +8023,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8039,7 +8039,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126836524</v>
+        <v>126836544</v>
       </c>
       <c r="B74" t="n">
         <v>78685</v>
@@ -8074,10 +8074,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>680720</v>
+        <v>680681</v>
       </c>
       <c r="R74" t="n">
-        <v>7087100</v>
+        <v>7087195</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8140,10 +8140,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126836475</v>
+        <v>126836524</v>
       </c>
       <c r="B75" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8151,21 +8151,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>680708</v>
+        <v>680720</v>
       </c>
       <c r="R75" t="n">
-        <v>7087220</v>
+        <v>7087100</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8241,7 +8241,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126836336</v>
+        <v>126836475</v>
       </c>
       <c r="B76" t="n">
         <v>79018</v>
@@ -8276,10 +8276,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>680653</v>
+        <v>680708</v>
       </c>
       <c r="R76" t="n">
-        <v>7087252</v>
+        <v>7087220</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8342,7 +8342,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126836464</v>
+        <v>126836336</v>
       </c>
       <c r="B77" t="n">
         <v>79018</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>680772</v>
+        <v>680653</v>
       </c>
       <c r="R77" t="n">
         <v>7087252</v>
@@ -8443,7 +8443,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126836473</v>
+        <v>126836464</v>
       </c>
       <c r="B78" t="n">
         <v>79018</v>
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>680710</v>
+        <v>680772</v>
       </c>
       <c r="R78" t="n">
-        <v>7087232</v>
+        <v>7087252</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8544,7 +8544,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126839999</v>
+        <v>126836473</v>
       </c>
       <c r="B79" t="n">
         <v>79018</v>
@@ -8579,10 +8579,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>680651</v>
+        <v>680710</v>
       </c>
       <c r="R79" t="n">
-        <v>7087231</v>
+        <v>7087232</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8629,12 +8629,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8645,10 +8645,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126837052</v>
+        <v>126839999</v>
       </c>
       <c r="B80" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8656,34 +8656,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>680740</v>
+        <v>680651</v>
       </c>
       <c r="R80" t="n">
-        <v>7087222</v>
+        <v>7087231</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8730,12 +8730,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -12825,10 +12825,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126836354</v>
+        <v>126836559</v>
       </c>
       <c r="B121" t="n">
-        <v>79018</v>
+        <v>91737</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12836,21 +12836,16 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12860,10 +12855,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>680771</v>
+        <v>680744</v>
       </c>
       <c r="R121" t="n">
-        <v>7087030</v>
+        <v>7087264</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12904,6 +12899,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12926,10 +12922,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126836466</v>
+        <v>126839970</v>
       </c>
       <c r="B122" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12937,21 +12933,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12961,10 +12957,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>680756</v>
+        <v>680772</v>
       </c>
       <c r="R122" t="n">
-        <v>7087273</v>
+        <v>7087124</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13011,12 +13007,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -13027,10 +13023,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126836479</v>
+        <v>126836545</v>
       </c>
       <c r="B123" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13038,21 +13034,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13062,10 +13058,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>680684</v>
+        <v>680657</v>
       </c>
       <c r="R123" t="n">
-        <v>7087202</v>
+        <v>7087201</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13128,10 +13124,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126836488</v>
+        <v>126825809</v>
       </c>
       <c r="B124" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13139,34 +13135,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>680655</v>
+        <v>680666</v>
       </c>
       <c r="R124" t="n">
-        <v>7087246</v>
+        <v>7087235</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13196,9 +13192,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13213,12 +13219,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13229,7 +13235,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126836478</v>
+        <v>126836354</v>
       </c>
       <c r="B125" t="n">
         <v>79018</v>
@@ -13264,10 +13270,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>680711</v>
+        <v>680771</v>
       </c>
       <c r="R125" t="n">
-        <v>7087181</v>
+        <v>7087030</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13330,10 +13336,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126836545</v>
+        <v>126836466</v>
       </c>
       <c r="B126" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13341,21 +13347,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13365,10 +13371,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>680657</v>
+        <v>680756</v>
       </c>
       <c r="R126" t="n">
-        <v>7087201</v>
+        <v>7087273</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13431,10 +13437,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126825809</v>
+        <v>126836479</v>
       </c>
       <c r="B127" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13442,34 +13448,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>680666</v>
+        <v>680684</v>
       </c>
       <c r="R127" t="n">
-        <v>7087235</v>
+        <v>7087202</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13499,19 +13505,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>10:27</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>10:27</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13526,12 +13522,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13542,10 +13538,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126839970</v>
+        <v>126836488</v>
       </c>
       <c r="B128" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13553,21 +13549,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13577,10 +13573,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>680772</v>
+        <v>680655</v>
       </c>
       <c r="R128" t="n">
-        <v>7087124</v>
+        <v>7087246</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13627,12 +13623,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -13643,10 +13639,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126836559</v>
+        <v>126836478</v>
       </c>
       <c r="B129" t="n">
-        <v>91737</v>
+        <v>79018</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13654,16 +13650,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13673,10 +13674,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>680744</v>
+        <v>680711</v>
       </c>
       <c r="R129" t="n">
-        <v>7087264</v>
+        <v>7087181</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13717,7 +13718,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64499-2023 artfynd.xlsx
+++ b/artfynd/A 64499-2023 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126836484</v>
+        <v>126839973</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,21 +815,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680665</v>
+        <v>680751</v>
       </c>
       <c r="R3" t="n">
-        <v>7087214</v>
+        <v>7087100</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,12 +889,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1309,10 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126825730</v>
+        <v>126836489</v>
       </c>
       <c r="B8" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1320,34 +1320,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680666</v>
+        <v>680647</v>
       </c>
       <c r="R8" t="n">
-        <v>7087235</v>
+        <v>7087267</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,22 +1374,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,12 +1394,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1420,7 +1410,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126836489</v>
+        <v>126836484</v>
       </c>
       <c r="B9" t="n">
         <v>79018</v>
@@ -1455,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680647</v>
+        <v>680665</v>
       </c>
       <c r="R9" t="n">
-        <v>7087267</v>
+        <v>7087214</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1622,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126839973</v>
+        <v>126825730</v>
       </c>
       <c r="B11" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,34 +1623,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680751</v>
+        <v>680666</v>
       </c>
       <c r="R11" t="n">
-        <v>7087100</v>
+        <v>7087235</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1687,12 +1677,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1707,12 +1707,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1723,10 +1723,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126837190</v>
+        <v>126836546</v>
       </c>
       <c r="B12" t="n">
-        <v>57661</v>
+        <v>78685</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1734,42 +1734,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680778</v>
+        <v>680660</v>
       </c>
       <c r="R12" t="n">
-        <v>7087007</v>
+        <v>7087210</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,11 +1796,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1821,12 +1808,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1837,7 +1824,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126836546</v>
+        <v>126836520</v>
       </c>
       <c r="B13" t="n">
         <v>78685</v>
@@ -1872,10 +1859,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680660</v>
+        <v>680716</v>
       </c>
       <c r="R13" t="n">
-        <v>7087210</v>
+        <v>7087135</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,7 +1925,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126836520</v>
+        <v>126837233</v>
       </c>
       <c r="B14" t="n">
         <v>78685</v>
@@ -1973,10 +1960,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680716</v>
+        <v>680698</v>
       </c>
       <c r="R14" t="n">
-        <v>7087135</v>
+        <v>7087108</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2023,12 +2010,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2039,7 +2026,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126837233</v>
+        <v>126840004</v>
       </c>
       <c r="B15" t="n">
         <v>78685</v>
@@ -2074,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680698</v>
+        <v>680639</v>
       </c>
       <c r="R15" t="n">
-        <v>7087108</v>
+        <v>7087277</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,12 +2111,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2140,10 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126840004</v>
+        <v>126837083</v>
       </c>
       <c r="B16" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2151,34 +2138,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680639</v>
+        <v>680743</v>
       </c>
       <c r="R16" t="n">
-        <v>7087277</v>
+        <v>7087104</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,12 +2212,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2241,10 +2228,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126839974</v>
+        <v>126836555</v>
       </c>
       <c r="B17" t="n">
-        <v>78776</v>
+        <v>78424</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,21 +2239,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2276,10 +2263,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680751</v>
+        <v>680660</v>
       </c>
       <c r="R17" t="n">
-        <v>7087100</v>
+        <v>7087210</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2326,12 +2313,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2342,10 +2329,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126837083</v>
+        <v>126839974</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,34 +2340,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680743</v>
+        <v>680751</v>
       </c>
       <c r="R18" t="n">
-        <v>7087104</v>
+        <v>7087100</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,12 +2414,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2443,10 +2430,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126836555</v>
+        <v>126837190</v>
       </c>
       <c r="B19" t="n">
-        <v>78424</v>
+        <v>57661</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,34 +2441,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680660</v>
+        <v>680778</v>
       </c>
       <c r="R19" t="n">
-        <v>7087210</v>
+        <v>7087007</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,6 +2511,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2528,12 +2528,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2544,7 +2544,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126837227</v>
+        <v>126836351</v>
       </c>
       <c r="B20" t="n">
         <v>79018</v>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680693</v>
+        <v>680723</v>
       </c>
       <c r="R20" t="n">
-        <v>7087147</v>
+        <v>7087114</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2629,12 +2629,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2645,7 +2645,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126836351</v>
+        <v>126837085</v>
       </c>
       <c r="B21" t="n">
         <v>79018</v>
@@ -2676,14 +2676,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680723</v>
+        <v>680698</v>
       </c>
       <c r="R21" t="n">
-        <v>7087114</v>
+        <v>7087214</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,12 +2730,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2746,7 +2746,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126837085</v>
+        <v>126837227</v>
       </c>
       <c r="B22" t="n">
         <v>79018</v>
@@ -2777,14 +2777,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>680698</v>
+        <v>680693</v>
       </c>
       <c r="R22" t="n">
-        <v>7087214</v>
+        <v>7087147</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2831,12 +2831,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3352,7 +3352,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126838821</v>
+        <v>126837228</v>
       </c>
       <c r="B28" t="n">
         <v>79018</v>
@@ -3383,14 +3383,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680775</v>
+        <v>680658</v>
       </c>
       <c r="R28" t="n">
-        <v>7087121</v>
+        <v>7087213</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3437,12 +3437,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3453,10 +3453,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126839971</v>
+        <v>126839989</v>
       </c>
       <c r="B29" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3464,21 +3464,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680772</v>
+        <v>680774</v>
       </c>
       <c r="R29" t="n">
         <v>7087124</v>
@@ -3655,10 +3655,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126839989</v>
+        <v>126839971</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3666,21 +3666,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680774</v>
+        <v>680772</v>
       </c>
       <c r="R31" t="n">
         <v>7087124</v>
@@ -3756,53 +3756,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126837193</v>
+        <v>126838821</v>
       </c>
       <c r="B32" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680696</v>
+        <v>680775</v>
       </c>
       <c r="R32" t="n">
-        <v>7087170</v>
+        <v>7087121</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,11 +3829,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Blindtarmstömmning</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3854,12 +3841,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3870,45 +3857,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126837228</v>
+        <v>126837193</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680658</v>
+        <v>680696</v>
       </c>
       <c r="R33" t="n">
-        <v>7087213</v>
+        <v>7087170</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3941,6 +3936,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Blindtarmstömmning</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3971,10 +3971,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126836543</v>
+        <v>126837084</v>
       </c>
       <c r="B34" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3982,34 +3982,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680708</v>
+        <v>680731</v>
       </c>
       <c r="R34" t="n">
-        <v>7087204</v>
+        <v>7087201</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4056,12 +4056,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4072,7 +4072,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126836460</v>
+        <v>126836463</v>
       </c>
       <c r="B35" t="n">
         <v>79018</v>
@@ -4107,10 +4107,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>680779</v>
+        <v>680773</v>
       </c>
       <c r="R35" t="n">
-        <v>7087200</v>
+        <v>7087233</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4173,7 +4173,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126836463</v>
+        <v>126839997</v>
       </c>
       <c r="B36" t="n">
         <v>79018</v>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>680773</v>
+        <v>680676</v>
       </c>
       <c r="R36" t="n">
-        <v>7087233</v>
+        <v>7087207</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4258,12 +4258,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4274,45 +4274,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126836477</v>
+        <v>126837192</v>
       </c>
       <c r="B37" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>680709</v>
+        <v>680665</v>
       </c>
       <c r="R37" t="n">
-        <v>7087204</v>
+        <v>7087191</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,6 +4355,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4359,12 +4372,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4472,10 +4485,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126839997</v>
+        <v>126836543</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4483,21 +4496,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4507,10 +4520,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>680676</v>
+        <v>680708</v>
       </c>
       <c r="R39" t="n">
-        <v>7087207</v>
+        <v>7087204</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4557,12 +4570,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4573,7 +4586,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126837084</v>
+        <v>126836460</v>
       </c>
       <c r="B40" t="n">
         <v>79018</v>
@@ -4604,14 +4617,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>680731</v>
+        <v>680779</v>
       </c>
       <c r="R40" t="n">
-        <v>7087201</v>
+        <v>7087200</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4658,12 +4671,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4674,53 +4687,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126837192</v>
+        <v>126836477</v>
       </c>
       <c r="B41" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>680665</v>
+        <v>680709</v>
       </c>
       <c r="R41" t="n">
-        <v>7087191</v>
+        <v>7087204</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4755,11 +4760,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4772,12 +4772,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4889,10 +4889,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126839937</v>
+        <v>126836483</v>
       </c>
       <c r="B43" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4900,21 +4900,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>680761</v>
+        <v>680673</v>
       </c>
       <c r="R43" t="n">
-        <v>7087124</v>
+        <v>7087210</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4974,12 +4974,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -4990,10 +4990,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126839994</v>
+        <v>126839937</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5001,21 +5001,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>680650</v>
+        <v>680761</v>
       </c>
       <c r="R44" t="n">
-        <v>7087238</v>
+        <v>7087124</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5091,7 +5091,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126836483</v>
+        <v>126839994</v>
       </c>
       <c r="B45" t="n">
         <v>79018</v>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>680673</v>
+        <v>680650</v>
       </c>
       <c r="R45" t="n">
-        <v>7087210</v>
+        <v>7087238</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5176,12 +5176,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5293,10 +5293,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126838822</v>
+        <v>126836548</v>
       </c>
       <c r="B47" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5304,34 +5304,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>680783</v>
+        <v>680662</v>
       </c>
       <c r="R47" t="n">
-        <v>7087170</v>
+        <v>7087231</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5378,12 +5378,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5495,10 +5495,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126836198</v>
+        <v>126839998</v>
       </c>
       <c r="B49" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5506,21 +5506,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>680721</v>
+        <v>680673</v>
       </c>
       <c r="R49" t="n">
-        <v>7087133</v>
+        <v>7087211</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5580,12 +5580,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5596,7 +5596,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126839998</v>
+        <v>126837223</v>
       </c>
       <c r="B50" t="n">
         <v>79018</v>
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>680673</v>
+        <v>680772</v>
       </c>
       <c r="R50" t="n">
-        <v>7087211</v>
+        <v>7087024</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5681,12 +5681,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5697,10 +5697,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126837223</v>
+        <v>126836198</v>
       </c>
       <c r="B51" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5708,21 +5708,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>680772</v>
+        <v>680721</v>
       </c>
       <c r="R51" t="n">
-        <v>7087024</v>
+        <v>7087133</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5782,12 +5782,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5798,45 +5798,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126839976</v>
+        <v>126838822</v>
       </c>
       <c r="B52" t="n">
-        <v>58031</v>
+        <v>79018</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>680693</v>
+        <v>680783</v>
       </c>
       <c r="R52" t="n">
-        <v>7087162</v>
+        <v>7087170</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5883,12 +5883,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5899,32 +5899,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126836548</v>
+        <v>126839976</v>
       </c>
       <c r="B53" t="n">
-        <v>78685</v>
+        <v>58031</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5934,10 +5934,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>680662</v>
+        <v>680693</v>
       </c>
       <c r="R53" t="n">
-        <v>7087231</v>
+        <v>7087162</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5984,12 +5984,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6101,7 +6101,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126836541</v>
+        <v>126837234</v>
       </c>
       <c r="B55" t="n">
         <v>78685</v>
@@ -6136,10 +6136,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>680708</v>
+        <v>680694</v>
       </c>
       <c r="R55" t="n">
-        <v>7087251</v>
+        <v>7087158</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6186,12 +6186,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6202,7 +6202,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126837234</v>
+        <v>126836541</v>
       </c>
       <c r="B56" t="n">
         <v>78685</v>
@@ -6237,10 +6237,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>680694</v>
+        <v>680708</v>
       </c>
       <c r="R56" t="n">
-        <v>7087158</v>
+        <v>7087251</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6287,12 +6287,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6707,10 +6707,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126840919</v>
+        <v>126836486</v>
       </c>
       <c r="B61" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6718,37 +6718,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>680640</v>
+        <v>680663</v>
       </c>
       <c r="R61" t="n">
-        <v>7087261</v>
+        <v>7087231</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6778,40 +6775,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>10:17</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>10:17</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6822,10 +6808,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126836486</v>
+        <v>126840919</v>
       </c>
       <c r="B62" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6833,34 +6819,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>680663</v>
+        <v>680640</v>
       </c>
       <c r="R62" t="n">
-        <v>7087231</v>
+        <v>7087261</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6890,29 +6879,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7231,45 +7231,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126837038</v>
+        <v>126839938</v>
       </c>
       <c r="B66" t="n">
-        <v>91295</v>
+        <v>79636</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>680783</v>
+        <v>680652</v>
       </c>
       <c r="R66" t="n">
-        <v>7087069</v>
+        <v>7087271</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7316,12 +7316,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7332,10 +7332,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126839938</v>
+        <v>126838804</v>
       </c>
       <c r="B67" t="n">
-        <v>79636</v>
+        <v>78776</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7343,34 +7343,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>680652</v>
+        <v>680765</v>
       </c>
       <c r="R67" t="n">
-        <v>7087271</v>
+        <v>7087124</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7417,12 +7417,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7433,45 +7433,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126838804</v>
+        <v>126837038</v>
       </c>
       <c r="B68" t="n">
-        <v>78776</v>
+        <v>91295</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>680765</v>
+        <v>680783</v>
       </c>
       <c r="R68" t="n">
-        <v>7087124</v>
+        <v>7087069</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7518,12 +7518,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7837,10 +7837,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126837052</v>
+        <v>126837069</v>
       </c>
       <c r="B72" t="n">
-        <v>57821</v>
+        <v>78777</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7848,21 +7848,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7872,10 +7872,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>680740</v>
+        <v>680673</v>
       </c>
       <c r="R72" t="n">
-        <v>7087222</v>
+        <v>7087276</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8039,7 +8039,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126836544</v>
+        <v>126836524</v>
       </c>
       <c r="B74" t="n">
         <v>78685</v>
@@ -8074,10 +8074,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>680681</v>
+        <v>680720</v>
       </c>
       <c r="R74" t="n">
-        <v>7087195</v>
+        <v>7087100</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8140,7 +8140,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126836524</v>
+        <v>126836544</v>
       </c>
       <c r="B75" t="n">
         <v>78685</v>
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>680720</v>
+        <v>680681</v>
       </c>
       <c r="R75" t="n">
-        <v>7087100</v>
+        <v>7087195</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8241,7 +8241,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126836475</v>
+        <v>126839999</v>
       </c>
       <c r="B76" t="n">
         <v>79018</v>
@@ -8276,10 +8276,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>680708</v>
+        <v>680651</v>
       </c>
       <c r="R76" t="n">
-        <v>7087220</v>
+        <v>7087231</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8326,12 +8326,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8342,7 +8342,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126836336</v>
+        <v>126836475</v>
       </c>
       <c r="B77" t="n">
         <v>79018</v>
@@ -8377,10 +8377,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>680653</v>
+        <v>680708</v>
       </c>
       <c r="R77" t="n">
-        <v>7087252</v>
+        <v>7087220</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8443,7 +8443,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126836464</v>
+        <v>126836336</v>
       </c>
       <c r="B78" t="n">
         <v>79018</v>
@@ -8478,7 +8478,7 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>680772</v>
+        <v>680653</v>
       </c>
       <c r="R78" t="n">
         <v>7087252</v>
@@ -8544,7 +8544,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126836473</v>
+        <v>126836464</v>
       </c>
       <c r="B79" t="n">
         <v>79018</v>
@@ -8579,10 +8579,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>680710</v>
+        <v>680772</v>
       </c>
       <c r="R79" t="n">
-        <v>7087232</v>
+        <v>7087252</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8645,7 +8645,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126839999</v>
+        <v>126836473</v>
       </c>
       <c r="B80" t="n">
         <v>79018</v>
@@ -8680,10 +8680,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>680651</v>
+        <v>680710</v>
       </c>
       <c r="R80" t="n">
-        <v>7087231</v>
+        <v>7087232</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8730,12 +8730,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8746,10 +8746,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126837069</v>
+        <v>126837052</v>
       </c>
       <c r="B81" t="n">
-        <v>78777</v>
+        <v>57821</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8757,21 +8757,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8781,10 +8781,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>680673</v>
+        <v>680740</v>
       </c>
       <c r="R81" t="n">
-        <v>7087276</v>
+        <v>7087222</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8847,10 +8847,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126836472</v>
+        <v>126837053</v>
       </c>
       <c r="B82" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8858,34 +8858,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>680714</v>
+        <v>680770</v>
       </c>
       <c r="R82" t="n">
-        <v>7087268</v>
+        <v>7087092</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8932,12 +8932,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9150,10 +9150,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126837053</v>
+        <v>126836472</v>
       </c>
       <c r="B85" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9161,34 +9161,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>680770</v>
+        <v>680714</v>
       </c>
       <c r="R85" t="n">
-        <v>7087092</v>
+        <v>7087268</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9235,12 +9235,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9352,10 +9352,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126836309</v>
+        <v>126836481</v>
       </c>
       <c r="B87" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9363,21 +9363,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9387,10 +9387,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>680720</v>
+        <v>680670</v>
       </c>
       <c r="R87" t="n">
-        <v>7087133</v>
+        <v>7087199</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9453,10 +9453,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126836199</v>
+        <v>126837231</v>
       </c>
       <c r="B88" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9464,21 +9464,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9488,10 +9488,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>680719</v>
+        <v>680642</v>
       </c>
       <c r="R88" t="n">
-        <v>7087133</v>
+        <v>7087222</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9538,12 +9538,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9554,10 +9554,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126840864</v>
+        <v>126836480</v>
       </c>
       <c r="B89" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9565,37 +9565,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>680671</v>
+        <v>680660</v>
       </c>
       <c r="R89" t="n">
-        <v>7087236</v>
+        <v>7087210</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9625,40 +9622,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9669,7 +9655,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126836481</v>
+        <v>126836357</v>
       </c>
       <c r="B90" t="n">
         <v>79018</v>
@@ -9704,10 +9690,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>680670</v>
+        <v>680784</v>
       </c>
       <c r="R90" t="n">
-        <v>7087199</v>
+        <v>7087010</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9770,7 +9756,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126837231</v>
+        <v>126837082</v>
       </c>
       <c r="B91" t="n">
         <v>79018</v>
@@ -9801,14 +9787,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>680642</v>
+        <v>680771</v>
       </c>
       <c r="R91" t="n">
-        <v>7087222</v>
+        <v>7087091</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9855,12 +9841,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -9871,7 +9857,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126836480</v>
+        <v>126839992</v>
       </c>
       <c r="B92" t="n">
         <v>79018</v>
@@ -9906,10 +9892,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>680660</v>
+        <v>680767</v>
       </c>
       <c r="R92" t="n">
-        <v>7087210</v>
+        <v>7087114</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9956,12 +9942,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -9972,10 +9958,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126836357</v>
+        <v>126836199</v>
       </c>
       <c r="B93" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9983,21 +9969,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10007,10 +9993,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>680784</v>
+        <v>680719</v>
       </c>
       <c r="R93" t="n">
-        <v>7087010</v>
+        <v>7087133</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10073,10 +10059,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126837082</v>
+        <v>126840864</v>
       </c>
       <c r="B94" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10084,34 +10070,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>680771</v>
+        <v>680671</v>
       </c>
       <c r="R94" t="n">
-        <v>7087091</v>
+        <v>7087236</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10141,29 +10130,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10174,10 +10174,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126839992</v>
+        <v>126836309</v>
       </c>
       <c r="B95" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10185,21 +10185,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>680767</v>
+        <v>680720</v>
       </c>
       <c r="R95" t="n">
-        <v>7087114</v>
+        <v>7087133</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10259,12 +10259,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10376,10 +10376,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126836226</v>
+        <v>126836471</v>
       </c>
       <c r="B97" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10387,21 +10387,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10411,10 +10411,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>680802</v>
+        <v>680715</v>
       </c>
       <c r="R97" t="n">
-        <v>7086993</v>
+        <v>7087274</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10477,7 +10477,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126836471</v>
+        <v>126838824</v>
       </c>
       <c r="B98" t="n">
         <v>79018</v>
@@ -10508,14 +10508,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>680715</v>
+        <v>680778</v>
       </c>
       <c r="R98" t="n">
-        <v>7087274</v>
+        <v>7087226</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10562,12 +10562,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10578,10 +10578,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126838824</v>
+        <v>126826458</v>
       </c>
       <c r="B99" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10589,34 +10589,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>680778</v>
+        <v>680755</v>
       </c>
       <c r="R99" t="n">
-        <v>7087226</v>
+        <v>7087104</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10646,9 +10646,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10663,12 +10673,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10679,10 +10689,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126826458</v>
+        <v>126836226</v>
       </c>
       <c r="B100" t="n">
-        <v>78776</v>
+        <v>91330</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10690,34 +10700,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>680755</v>
+        <v>680802</v>
       </c>
       <c r="R100" t="n">
-        <v>7087104</v>
+        <v>7086993</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10747,19 +10757,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10774,12 +10774,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10790,7 +10790,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126836487</v>
+        <v>126836352</v>
       </c>
       <c r="B101" t="n">
         <v>79018</v>
@@ -10825,10 +10825,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>680663</v>
+        <v>680753</v>
       </c>
       <c r="R101" t="n">
-        <v>7087244</v>
+        <v>7087043</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10891,7 +10891,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126837236</v>
+        <v>126836522</v>
       </c>
       <c r="B102" t="n">
         <v>78685</v>
@@ -10926,10 +10926,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>680673</v>
+        <v>680726</v>
       </c>
       <c r="R102" t="n">
-        <v>7087186</v>
+        <v>7087132</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10976,12 +10976,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -10992,10 +10992,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126836242</v>
+        <v>126837236</v>
       </c>
       <c r="B103" t="n">
-        <v>91280</v>
+        <v>78685</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11003,21 +11003,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>112</v>
+        <v>353</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11027,10 +11027,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>680744</v>
+        <v>680673</v>
       </c>
       <c r="R103" t="n">
-        <v>7087264</v>
+        <v>7087186</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11077,12 +11077,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11093,10 +11093,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126836522</v>
+        <v>126836242</v>
       </c>
       <c r="B104" t="n">
-        <v>78685</v>
+        <v>91280</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11104,21 +11104,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>353</v>
+        <v>112</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11128,10 +11128,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>680726</v>
+        <v>680744</v>
       </c>
       <c r="R104" t="n">
-        <v>7087132</v>
+        <v>7087264</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11194,7 +11194,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126836352</v>
+        <v>126836487</v>
       </c>
       <c r="B105" t="n">
         <v>79018</v>
@@ -11229,10 +11229,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>680753</v>
+        <v>680663</v>
       </c>
       <c r="R105" t="n">
-        <v>7087043</v>
+        <v>7087244</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11911,45 +11911,50 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126836230</v>
+        <v>126839946</v>
       </c>
       <c r="B112" t="n">
-        <v>57483</v>
+        <v>56853</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>102976</v>
+        <v>100138</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>680774</v>
+        <v>680662</v>
       </c>
       <c r="R112" t="n">
-        <v>7087234</v>
+        <v>7087219</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11996,12 +12001,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12012,32 +12017,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126836507</v>
+        <v>126836230</v>
       </c>
       <c r="B113" t="n">
-        <v>92620</v>
+        <v>57483</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4364</v>
+        <v>102976</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12047,10 +12052,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>680724</v>
+        <v>680774</v>
       </c>
       <c r="R113" t="n">
-        <v>7087106</v>
+        <v>7087234</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12113,32 +12118,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126836355</v>
+        <v>126836507</v>
       </c>
       <c r="B114" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12148,10 +12153,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>680779</v>
+        <v>680724</v>
       </c>
       <c r="R114" t="n">
-        <v>7087023</v>
+        <v>7087106</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12214,50 +12219,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126839946</v>
+        <v>126836355</v>
       </c>
       <c r="B115" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>680662</v>
+        <v>680779</v>
       </c>
       <c r="R115" t="n">
-        <v>7087219</v>
+        <v>7087023</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12304,12 +12304,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12825,10 +12825,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126836559</v>
+        <v>126836354</v>
       </c>
       <c r="B121" t="n">
-        <v>91737</v>
+        <v>79018</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12836,16 +12836,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12855,10 +12860,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>680744</v>
+        <v>680771</v>
       </c>
       <c r="R121" t="n">
-        <v>7087264</v>
+        <v>7087030</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12899,7 +12904,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12922,10 +12926,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126839970</v>
+        <v>126836559</v>
       </c>
       <c r="B122" t="n">
-        <v>78777</v>
+        <v>91737</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12933,21 +12937,16 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12957,10 +12956,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>680772</v>
+        <v>680744</v>
       </c>
       <c r="R122" t="n">
-        <v>7087124</v>
+        <v>7087264</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13001,18 +13000,19 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -13023,7 +13023,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126836545</v>
+        <v>126825809</v>
       </c>
       <c r="B123" t="n">
         <v>78685</v>
@@ -13054,14 +13054,14 @@
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>680657</v>
+        <v>680666</v>
       </c>
       <c r="R123" t="n">
-        <v>7087201</v>
+        <v>7087235</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13091,9 +13091,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13108,12 +13118,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -13124,7 +13134,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126825809</v>
+        <v>126836545</v>
       </c>
       <c r="B124" t="n">
         <v>78685</v>
@@ -13155,14 +13165,14 @@
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>680666</v>
+        <v>680657</v>
       </c>
       <c r="R124" t="n">
-        <v>7087235</v>
+        <v>7087201</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13192,19 +13202,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>10:27</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>10:27</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13219,12 +13219,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13235,7 +13235,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126836354</v>
+        <v>126836466</v>
       </c>
       <c r="B125" t="n">
         <v>79018</v>
@@ -13270,10 +13270,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>680771</v>
+        <v>680756</v>
       </c>
       <c r="R125" t="n">
-        <v>7087030</v>
+        <v>7087273</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13336,7 +13336,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126836466</v>
+        <v>126836479</v>
       </c>
       <c r="B126" t="n">
         <v>79018</v>
@@ -13371,10 +13371,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>680756</v>
+        <v>680684</v>
       </c>
       <c r="R126" t="n">
-        <v>7087273</v>
+        <v>7087202</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13437,7 +13437,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126836479</v>
+        <v>126836488</v>
       </c>
       <c r="B127" t="n">
         <v>79018</v>
@@ -13472,10 +13472,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>680684</v>
+        <v>680655</v>
       </c>
       <c r="R127" t="n">
-        <v>7087202</v>
+        <v>7087246</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13538,7 +13538,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126836488</v>
+        <v>126836478</v>
       </c>
       <c r="B128" t="n">
         <v>79018</v>
@@ -13573,10 +13573,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>680655</v>
+        <v>680711</v>
       </c>
       <c r="R128" t="n">
-        <v>7087246</v>
+        <v>7087181</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13639,10 +13639,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126836478</v>
+        <v>126839970</v>
       </c>
       <c r="B129" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13650,21 +13650,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13674,10 +13674,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>680711</v>
+        <v>680772</v>
       </c>
       <c r="R129" t="n">
-        <v>7087181</v>
+        <v>7087124</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13724,12 +13724,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -13740,7 +13740,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126836467</v>
+        <v>126838826</v>
       </c>
       <c r="B130" t="n">
         <v>79018</v>
@@ -13771,14 +13771,14 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>680758</v>
+        <v>680675</v>
       </c>
       <c r="R130" t="n">
-        <v>7087267</v>
+        <v>7087310</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13825,12 +13825,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -13841,7 +13841,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126838827</v>
+        <v>126836467</v>
       </c>
       <c r="B131" t="n">
         <v>79018</v>
@@ -13872,14 +13872,14 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>680665</v>
+        <v>680758</v>
       </c>
       <c r="R131" t="n">
-        <v>7087288</v>
+        <v>7087267</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13926,12 +13926,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -13942,7 +13942,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126838826</v>
+        <v>126838827</v>
       </c>
       <c r="B132" t="n">
         <v>79018</v>
@@ -13977,10 +13977,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>680675</v>
+        <v>680665</v>
       </c>
       <c r="R132" t="n">
-        <v>7087310</v>
+        <v>7087288</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
